--- a/BC.MI.xlsx
+++ b/BC.MI.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\1.Finance\Anaylsen\Models\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3E1478C7-EC28-4669-B8B5-A9323F2150CA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DEBCAE61-34C0-4851-B38F-C34E6FBCBD42}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21060" activeTab="1" xr2:uid="{6AFCE97C-0CAA-47F0-9D92-585A8A3029EA}"/>
+    <workbookView xWindow="19095" yWindow="0" windowWidth="19410" windowHeight="20925" xr2:uid="{6AFCE97C-0CAA-47F0-9D92-585A8A3029EA}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="71">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="72">
   <si>
     <t>numbers in mio EUR</t>
   </si>
@@ -237,9 +237,6 @@
     <t>CEO &amp; CD</t>
   </si>
   <si>
-    <t>Q225</t>
-  </si>
-  <si>
     <t>H125</t>
   </si>
   <si>
@@ -251,6 +248,12 @@
   <si>
     <t>https://www.morpheus-research.com/cucinelli/</t>
   </si>
+  <si>
+    <t>FY25</t>
+  </si>
+  <si>
+    <t>Q425</t>
+  </si>
 </sst>
 </file>
 
@@ -259,13 +262,19 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="#,##0.0"/>
   </numFmts>
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
@@ -336,26 +345,29 @@
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="3" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="3" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="4" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="9" fontId="2" fillId="0" borderId="0" xfId="2" applyFont="1"/>
-    <xf numFmtId="9" fontId="5" fillId="0" borderId="0" xfId="2" applyFont="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="3" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="3" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="4" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="9" fontId="3" fillId="0" borderId="0" xfId="2" applyFont="1"/>
+    <xf numFmtId="9" fontId="6" fillId="0" borderId="0" xfId="2" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -767,7 +779,7 @@
         <v>1</v>
       </c>
       <c r="J2" s="2">
-        <v>93</v>
+        <v>86.1</v>
       </c>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.2">
@@ -777,8 +789,8 @@
       <c r="J3" s="8">
         <v>67.993675999999994</v>
       </c>
-      <c r="K3" s="3" t="s">
-        <v>66</v>
+      <c r="K3" s="14" t="s">
+        <v>71</v>
       </c>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.2">
@@ -790,7 +802,7 @@
       </c>
       <c r="J4" s="8">
         <f>+J2*J3</f>
-        <v>6323.4118679999992</v>
+        <v>5854.2555035999994</v>
       </c>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.2">
@@ -801,11 +813,11 @@
         <v>4</v>
       </c>
       <c r="J5" s="8">
-        <f>242.657+1.184</f>
-        <v>243.84100000000001</v>
-      </c>
-      <c r="K5" s="3" t="s">
-        <v>66</v>
+        <f>202.848+0.993</f>
+        <v>203.84100000000001</v>
+      </c>
+      <c r="K5" s="14" t="s">
+        <v>71</v>
       </c>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.2">
@@ -813,11 +825,11 @@
         <v>5</v>
       </c>
       <c r="J6" s="8">
-        <f>2.995+4.045</f>
-        <v>7.04</v>
-      </c>
-      <c r="K6" s="3" t="s">
-        <v>66</v>
+        <f>220.604+175.294+0.725</f>
+        <v>396.62300000000005</v>
+      </c>
+      <c r="K6" s="14" t="s">
+        <v>71</v>
       </c>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.2">
@@ -826,7 +838,7 @@
       </c>
       <c r="J7" s="8">
         <f>+J4+J6-J5</f>
-        <v>6086.6108679999988</v>
+        <v>6047.0375035999987</v>
       </c>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.2">
@@ -844,12 +856,12 @@
     </row>
     <row r="34" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B34" s="13" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="35" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B35" s="2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
   </sheetData>
@@ -896,10 +908,10 @@
         <v>14</v>
       </c>
       <c r="I2" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="J2" s="3" t="s">
         <v>67</v>
-      </c>
-      <c r="J2" s="3" t="s">
-        <v>68</v>
       </c>
       <c r="K2" s="3"/>
       <c r="L2" s="3" t="s">
@@ -922,6 +934,9 @@
       </c>
       <c r="R2" s="3" t="s">
         <v>21</v>
+      </c>
+      <c r="S2" s="14" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="3" spans="1:65" x14ac:dyDescent="0.2">
@@ -1588,7 +1603,9 @@
       <c r="R10" s="8">
         <v>315.666</v>
       </c>
-      <c r="S10" s="8"/>
+      <c r="S10" s="8">
+        <v>494.92</v>
+      </c>
       <c r="T10" s="8"/>
       <c r="U10" s="8"/>
       <c r="V10" s="8"/>
@@ -1677,7 +1694,9 @@
       <c r="R11" s="8">
         <v>140.92099999999999</v>
       </c>
-      <c r="S11" s="8"/>
+      <c r="S11" s="8">
+        <v>0</v>
+      </c>
       <c r="T11" s="8"/>
       <c r="U11" s="8"/>
       <c r="V11" s="8"/>
@@ -1768,7 +1787,9 @@
       <c r="R12" s="8">
         <v>476.55900000000003</v>
       </c>
-      <c r="S12" s="8"/>
+      <c r="S12" s="8">
+        <v>520.48800000000006</v>
+      </c>
       <c r="T12" s="8"/>
       <c r="U12" s="8"/>
       <c r="V12" s="8"/>
@@ -1860,7 +1881,9 @@
       <c r="R13" s="8">
         <v>345.39400000000001</v>
       </c>
-      <c r="S13" s="8"/>
+      <c r="S13" s="8">
+        <v>392.54300000000001</v>
+      </c>
       <c r="T13" s="8"/>
       <c r="U13" s="8"/>
       <c r="V13" s="8"/>
@@ -1951,7 +1974,9 @@
       <c r="R14" s="8">
         <v>851.24300000000005</v>
       </c>
-      <c r="S14" s="8"/>
+      <c r="S14" s="8">
+        <v>947.00900000000001</v>
+      </c>
       <c r="T14" s="8"/>
       <c r="U14" s="8"/>
       <c r="V14" s="8"/>
@@ -2043,7 +2068,9 @@
       <c r="R15" s="8">
         <v>427.29700000000003</v>
       </c>
-      <c r="S15" s="8"/>
+      <c r="S15" s="8">
+        <v>460.94200000000001</v>
+      </c>
       <c r="T15" s="8"/>
       <c r="U15" s="8"/>
       <c r="V15" s="8"/>
@@ -2149,7 +2176,9 @@
         <f>+R14+R15</f>
         <v>1278.54</v>
       </c>
-      <c r="S16" s="8"/>
+      <c r="S16" s="9">
+        <v>1407.951</v>
+      </c>
       <c r="T16" s="8"/>
       <c r="U16" s="8"/>
       <c r="V16" s="8"/>
@@ -2240,7 +2269,9 @@
       <c r="R17" s="8">
         <v>101.8</v>
       </c>
-      <c r="S17" s="8"/>
+      <c r="S17" s="8">
+        <v>121.099</v>
+      </c>
       <c r="T17" s="8"/>
       <c r="U17" s="8"/>
       <c r="V17" s="8"/>
@@ -2350,7 +2381,10 @@
         <f>+R16-R17</f>
         <v>1176.74</v>
       </c>
-      <c r="S18" s="8"/>
+      <c r="S18" s="8">
+        <f>+S16-S17</f>
+        <v>1286.8520000000001</v>
+      </c>
       <c r="T18" s="8"/>
       <c r="U18" s="8"/>
       <c r="V18" s="8"/>
@@ -2441,7 +2475,9 @@
       <c r="R19" s="8">
         <v>560.36099999999999</v>
       </c>
-      <c r="S19" s="8"/>
+      <c r="S19" s="8">
+        <v>595.73699999999997</v>
+      </c>
       <c r="T19" s="8"/>
       <c r="U19" s="8"/>
       <c r="V19" s="8"/>
@@ -2532,7 +2568,9 @@
       <c r="R20" s="8">
         <v>233.49199999999999</v>
       </c>
-      <c r="S20" s="8"/>
+      <c r="S20" s="8">
+        <v>255.36699999999999</v>
+      </c>
       <c r="T20" s="8"/>
       <c r="U20" s="8"/>
       <c r="V20" s="8"/>
@@ -2623,7 +2661,9 @@
       <c r="R21" s="8">
         <v>21.079000000000001</v>
       </c>
-      <c r="S21" s="8"/>
+      <c r="S21" s="8">
+        <v>25.614000000000001</v>
+      </c>
       <c r="T21" s="8"/>
       <c r="U21" s="8"/>
       <c r="V21" s="8"/>
@@ -2714,7 +2754,9 @@
       <c r="R22" s="8">
         <v>3.2709999999999999</v>
       </c>
-      <c r="S22" s="8"/>
+      <c r="S22" s="8">
+        <v>5.4039999999999999</v>
+      </c>
       <c r="T22" s="8"/>
       <c r="U22" s="8"/>
       <c r="V22" s="8"/>
@@ -2805,7 +2847,9 @@
       <c r="R23" s="8">
         <v>2.4169999999999998</v>
       </c>
-      <c r="S23" s="8"/>
+      <c r="S23" s="8">
+        <v>1.7350000000000001</v>
+      </c>
       <c r="T23" s="8"/>
       <c r="U23" s="8"/>
       <c r="V23" s="8"/>
@@ -2896,7 +2940,9 @@
       <c r="R24" s="8">
         <v>153.00399999999999</v>
       </c>
-      <c r="S24" s="8"/>
+      <c r="S24" s="8">
+        <v>180.61199999999999</v>
+      </c>
       <c r="T24" s="8"/>
       <c r="U24" s="8"/>
       <c r="V24" s="8"/>
@@ -2987,7 +3033,9 @@
       <c r="R25" s="8">
         <v>2.8210000000000002</v>
       </c>
-      <c r="S25" s="8"/>
+      <c r="S25" s="8">
+        <v>8.8770000000000007</v>
+      </c>
       <c r="T25" s="8"/>
       <c r="U25" s="8"/>
       <c r="V25" s="8"/>
@@ -3060,7 +3108,7 @@
         <v>104.58700000000006</v>
       </c>
       <c r="H26" s="8">
-        <f t="shared" ref="H26:R26" si="19">+H18-SUM(H19:H21)+H22+H23-H24-H25</f>
+        <f t="shared" ref="H26:S26" si="19">+H18-SUM(H19:H21)+H22+H23-H24-H25</f>
         <v>0</v>
       </c>
       <c r="I26" s="8">
@@ -3097,7 +3145,10 @@
         <f t="shared" si="19"/>
         <v>211.67100000000011</v>
       </c>
-      <c r="S26" s="8"/>
+      <c r="S26" s="8">
+        <f t="shared" si="19"/>
+        <v>227.78400000000013</v>
+      </c>
       <c r="T26" s="8"/>
       <c r="U26" s="8"/>
       <c r="V26" s="8"/>
@@ -3188,7 +3239,9 @@
       <c r="R27" s="8">
         <v>67.558999999999997</v>
       </c>
-      <c r="S27" s="8"/>
+      <c r="S27" s="8">
+        <v>84.634</v>
+      </c>
       <c r="T27" s="8"/>
       <c r="U27" s="8"/>
       <c r="V27" s="8"/>
@@ -3279,7 +3332,9 @@
       <c r="R28" s="8">
         <v>35.625</v>
       </c>
-      <c r="S28" s="8"/>
+      <c r="S28" s="8">
+        <v>55.545999999999999</v>
+      </c>
       <c r="T28" s="8"/>
       <c r="U28" s="8"/>
       <c r="V28" s="8"/>
@@ -3389,7 +3444,10 @@
         <f>+R26-R27+R28</f>
         <v>179.73700000000011</v>
       </c>
-      <c r="S29" s="8"/>
+      <c r="S29" s="8">
+        <f>+S26-S27+S28</f>
+        <v>198.69600000000014</v>
+      </c>
       <c r="T29" s="8"/>
       <c r="U29" s="8"/>
       <c r="V29" s="8"/>
@@ -3480,7 +3538,9 @@
       <c r="R30" s="8">
         <v>51.223999999999997</v>
       </c>
-      <c r="S30" s="8"/>
+      <c r="S30" s="8">
+        <v>56.707000000000001</v>
+      </c>
       <c r="T30" s="8"/>
       <c r="U30" s="8"/>
       <c r="V30" s="8"/>
@@ -3590,7 +3650,10 @@
         <f>+R29-R30</f>
         <v>128.51300000000012</v>
       </c>
-      <c r="S31" s="8"/>
+      <c r="S31" s="8">
+        <f>+S29-S30</f>
+        <v>141.98900000000015</v>
+      </c>
       <c r="T31" s="8"/>
       <c r="U31" s="8"/>
       <c r="V31" s="8"/>
@@ -3681,7 +3744,9 @@
       <c r="R32" s="8">
         <v>9.0340000000000007</v>
       </c>
-      <c r="S32" s="8"/>
+      <c r="S32" s="8">
+        <v>6.9550000000000001</v>
+      </c>
       <c r="T32" s="8"/>
       <c r="U32" s="8"/>
       <c r="V32" s="8"/>
@@ -3791,7 +3856,10 @@
         <f>+R31-R32</f>
         <v>119.47900000000011</v>
       </c>
-      <c r="S33" s="8"/>
+      <c r="S33" s="8">
+        <f>+S31-S32</f>
+        <v>135.03400000000013</v>
+      </c>
       <c r="T33" s="8"/>
       <c r="U33" s="8"/>
       <c r="V33" s="8"/>
@@ -3966,7 +4034,10 @@
         <f>+R33/R36</f>
         <v>1.7572738812070285</v>
       </c>
-      <c r="S35" s="8"/>
+      <c r="S35" s="7">
+        <f>+S33/S36</f>
+        <v>1.98605379418065</v>
+      </c>
       <c r="T35" s="8"/>
       <c r="U35" s="8"/>
       <c r="V35" s="8"/>
@@ -4056,7 +4127,9 @@
       <c r="R36" s="8">
         <v>67.991108999999994</v>
       </c>
-      <c r="S36" s="8"/>
+      <c r="S36" s="8">
+        <v>67.991108999999994</v>
+      </c>
       <c r="T36" s="8"/>
       <c r="U36" s="8"/>
       <c r="V36" s="8"/>
@@ -4207,7 +4280,10 @@
         <f>+R7/Q7-1</f>
         <v>-1</v>
       </c>
-      <c r="S38" s="8"/>
+      <c r="S38" s="10" t="e">
+        <f>+S7/R7-1</f>
+        <v>#DIV/0!</v>
+      </c>
       <c r="T38" s="8"/>
       <c r="U38" s="8"/>
       <c r="V38" s="8"/>
@@ -4293,7 +4369,10 @@
         <f>+R10/Q10-1</f>
         <v>5.4399091455675119E-2</v>
       </c>
-      <c r="S39" s="8"/>
+      <c r="S39" s="10">
+        <f>+S10/R10-1</f>
+        <v>0.56785969980929218</v>
+      </c>
       <c r="T39" s="8"/>
       <c r="U39" s="8"/>
       <c r="V39" s="8"/>
@@ -4372,14 +4451,17 @@
         <v>0.22001116084679961</v>
       </c>
       <c r="Q40" s="10">
-        <f t="shared" ref="Q40:R42" si="38">+Q11/P11-1</f>
+        <f t="shared" ref="Q40:S42" si="38">+Q11/P11-1</f>
         <v>0.25399745019610132</v>
       </c>
       <c r="R40" s="10">
         <f t="shared" si="38"/>
         <v>9.3665600844379471E-2</v>
       </c>
-      <c r="S40" s="8"/>
+      <c r="S40" s="10">
+        <f t="shared" si="38"/>
+        <v>-1</v>
+      </c>
       <c r="T40" s="8"/>
       <c r="U40" s="8"/>
       <c r="V40" s="8"/>
@@ -4465,7 +4547,10 @@
         <f t="shared" si="38"/>
         <v>0.17828029462014139</v>
       </c>
-      <c r="S41" s="8"/>
+      <c r="S41" s="10">
+        <f t="shared" si="38"/>
+        <v>9.2179562236784918E-2</v>
+      </c>
       <c r="T41" s="8"/>
       <c r="U41" s="8"/>
       <c r="V41" s="8"/>
@@ -4551,7 +4636,10 @@
         <f t="shared" si="38"/>
         <v>0.12603387288701962</v>
       </c>
-      <c r="S42" s="8"/>
+      <c r="S42" s="10">
+        <f t="shared" si="38"/>
+        <v>0.13650787216917482</v>
+      </c>
       <c r="T42" s="8"/>
       <c r="U42" s="8"/>
       <c r="V42" s="8"/>
@@ -4655,7 +4743,10 @@
         <f>+R16/Q16-1</f>
         <v>0.12209720735110841</v>
       </c>
-      <c r="S43" s="8"/>
+      <c r="S43" s="11">
+        <f>+S16/R16-1</f>
+        <v>0.10121779529776154</v>
+      </c>
       <c r="T43" s="8"/>
       <c r="U43" s="8"/>
       <c r="V43" s="8"/>
@@ -4768,7 +4859,10 @@
         <f>+R18/R16</f>
         <v>0.92037793107763544</v>
       </c>
-      <c r="S44" s="8"/>
+      <c r="S44" s="10">
+        <f>+S18/S16</f>
+        <v>0.9139891942262196</v>
+      </c>
       <c r="T44" s="8"/>
       <c r="U44" s="8"/>
       <c r="V44" s="8"/>
@@ -4881,7 +4975,10 @@
         <f>+R26/R16</f>
         <v>0.16555680698296504</v>
       </c>
-      <c r="S45" s="8"/>
+      <c r="S45" s="10">
+        <f>+S26/S16</f>
+        <v>0.16178403935932439</v>
+      </c>
       <c r="T45" s="8"/>
       <c r="U45" s="8"/>
       <c r="V45" s="8"/>
@@ -4994,7 +5091,10 @@
         <f>+R30/R29</f>
         <v>0.2849941859494704</v>
       </c>
-      <c r="S46" s="8"/>
+      <c r="S46" s="10">
+        <f>+S30/S29</f>
+        <v>0.28539578048878667</v>
+      </c>
       <c r="T46" s="8"/>
       <c r="U46" s="8"/>
       <c r="V46" s="8"/>

--- a/BC.MI.xlsx
+++ b/BC.MI.xlsx
@@ -1,7 +1,7 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DEBCAE61-34C0-4851-B38F-C34E6FBCBD42}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="19095" yWindow="0" windowWidth="19410" windowHeight="20925" xr2:uid="{6AFCE97C-0CAA-47F0-9D92-585A8A3029EA}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21060" activeTab="1" xr2:uid="{6AFCE97C-0CAA-47F0-9D92-585A8A3029EA}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="1" r:id="rId1"/>

--- a/BC.MI.xlsx
+++ b/BC.MI.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\1.Finance\Anaylsen\Models\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DEBCAE61-34C0-4851-B38F-C34E6FBCBD42}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C142BFBB-9A01-4D8F-8B62-9CCB1170960A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21060" activeTab="1" xr2:uid="{6AFCE97C-0CAA-47F0-9D92-585A8A3029EA}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{6AFCE97C-0CAA-47F0-9D92-585A8A3029EA}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="1" r:id="rId1"/>
@@ -779,7 +779,7 @@
         <v>1</v>
       </c>
       <c r="J2" s="2">
-        <v>86.1</v>
+        <v>81.2</v>
       </c>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.2">
@@ -802,7 +802,7 @@
       </c>
       <c r="J4" s="8">
         <f>+J2*J3</f>
-        <v>5854.2555035999994</v>
+        <v>5521.0864911999997</v>
       </c>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.2">
@@ -838,7 +838,7 @@
       </c>
       <c r="J7" s="8">
         <f>+J4+J6-J5</f>
-        <v>6047.0375035999987</v>
+        <v>5713.868491199999</v>
       </c>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.2">

--- a/BC.MI.xlsx
+++ b/BC.MI.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\1.Finance\Anaylsen\Models\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C142BFBB-9A01-4D8F-8B62-9CCB1170960A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{45421C9D-98E6-4156-AF49-6E609B834094}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{6AFCE97C-0CAA-47F0-9D92-585A8A3029EA}"/>
+    <workbookView xWindow="19095" yWindow="0" windowWidth="19410" windowHeight="20985" activeTab="1" xr2:uid="{6AFCE97C-0CAA-47F0-9D92-585A8A3029EA}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="72">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="75">
   <si>
     <t>numbers in mio EUR</t>
   </si>
@@ -234,9 +234,6 @@
     <t>Notes</t>
   </si>
   <si>
-    <t>CEO &amp; CD</t>
-  </si>
-  <si>
     <t>H125</t>
   </si>
   <si>
@@ -252,7 +249,19 @@
     <t>FY25</t>
   </si>
   <si>
-    <t>Q425</t>
+    <t>H126</t>
+  </si>
+  <si>
+    <t>H226</t>
+  </si>
+  <si>
+    <t>n.a.</t>
+  </si>
+  <si>
+    <t>Q226</t>
+  </si>
+  <si>
+    <t>CEO&amp;CD</t>
   </si>
 </sst>
 </file>
@@ -262,13 +271,19 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="#,##0.0"/>
   </numFmts>
-  <fonts count="9" x14ac:knownFonts="1">
+  <fonts count="10" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
@@ -345,29 +360,36 @@
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="3" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="3" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="4" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="9" fontId="3" fillId="0" borderId="0" xfId="2" applyFont="1"/>
-    <xf numFmtId="9" fontId="6" fillId="0" borderId="0" xfId="2" applyFont="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="3" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="3" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="4" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="9" fontId="4" fillId="0" borderId="0" xfId="2" applyFont="1"/>
+    <xf numFmtId="9" fontId="7" fillId="0" borderId="0" xfId="2" applyFont="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -779,7 +801,7 @@
         <v>1</v>
       </c>
       <c r="J2" s="2">
-        <v>81.2</v>
+        <v>87.92</v>
       </c>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.2">
@@ -789,8 +811,8 @@
       <c r="J3" s="8">
         <v>67.993675999999994</v>
       </c>
-      <c r="K3" s="14" t="s">
-        <v>71</v>
+      <c r="K3" s="15" t="s">
+        <v>73</v>
       </c>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.2">
@@ -802,7 +824,7 @@
       </c>
       <c r="J4" s="8">
         <f>+J2*J3</f>
-        <v>5521.0864911999997</v>
+        <v>5978.0039939199996</v>
       </c>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.2">
@@ -813,11 +835,11 @@
         <v>4</v>
       </c>
       <c r="J5" s="8">
-        <f>202.848+0.993</f>
-        <v>203.84100000000001</v>
-      </c>
-      <c r="K5" s="14" t="s">
-        <v>71</v>
+        <f>179.77+0.999</f>
+        <v>180.76900000000001</v>
+      </c>
+      <c r="K5" s="15" t="s">
+        <v>73</v>
       </c>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.2">
@@ -825,11 +847,11 @@
         <v>5</v>
       </c>
       <c r="J6" s="8">
-        <f>220.604+175.294+0.725</f>
-        <v>396.62300000000005</v>
-      </c>
-      <c r="K6" s="14" t="s">
-        <v>71</v>
+        <f>230.987+168.736</f>
+        <v>399.72299999999996</v>
+      </c>
+      <c r="K6" s="15" t="s">
+        <v>73</v>
       </c>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.2">
@@ -838,12 +860,12 @@
       </c>
       <c r="J7" s="8">
         <f>+J4+J6-J5</f>
-        <v>5713.868491199999</v>
+        <v>6196.9579939199994</v>
       </c>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="I9" s="2" t="s">
-        <v>65</v>
+      <c r="I9" s="17" t="s">
+        <v>74</v>
       </c>
       <c r="J9" s="2" t="s">
         <v>52</v>
@@ -856,12 +878,12 @@
     </row>
     <row r="34" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B34" s="13" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="35" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B35" s="2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
   </sheetData>
@@ -875,7 +897,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1334857E-06C9-4A6E-809B-B62D56C178F7}">
-  <dimension ref="A1:BM269"/>
+  <dimension ref="A1:BO269"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5.42578125" style="2" bestFit="1" customWidth="1"/>
@@ -883,12 +905,12 @@
     <col min="3" max="16384" width="9.140625" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:65" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:67" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:65" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:67" x14ac:dyDescent="0.2">
       <c r="C2" s="3" t="s">
         <v>9</v>
       </c>
@@ -908,38 +930,44 @@
         <v>14</v>
       </c>
       <c r="I2" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="J2" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="J2" s="3" t="s">
-        <v>67</v>
-      </c>
-      <c r="K2" s="3"/>
-      <c r="L2" s="3" t="s">
+      <c r="K2" s="15" t="s">
+        <v>70</v>
+      </c>
+      <c r="L2" s="15" t="s">
+        <v>71</v>
+      </c>
+      <c r="M2" s="3"/>
+      <c r="N2" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="M2" s="3" t="s">
+      <c r="O2" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="N2" s="3" t="s">
+      <c r="P2" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="O2" s="3" t="s">
+      <c r="Q2" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="P2" s="3" t="s">
+      <c r="R2" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="Q2" s="3" t="s">
+      <c r="S2" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="R2" s="3" t="s">
+      <c r="T2" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="S2" s="14" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="3" spans="1:65" x14ac:dyDescent="0.2">
+      <c r="U2" s="14" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="3" spans="1:67" x14ac:dyDescent="0.2">
       <c r="B3" s="2" t="s">
         <v>22</v>
       </c>
@@ -947,27 +975,23 @@
       <c r="D3" s="4"/>
       <c r="E3" s="4"/>
       <c r="F3" s="4">
-        <f>+Q3</f>
+        <f>+S3</f>
         <v>13</v>
       </c>
       <c r="G3" s="4">
         <v>13</v>
       </c>
       <c r="H3" s="4">
-        <f>+R3</f>
+        <f>+T3</f>
         <v>0</v>
       </c>
       <c r="I3" s="4"/>
       <c r="J3" s="4"/>
       <c r="K3" s="4"/>
-      <c r="L3" s="4">
+      <c r="L3" s="4"/>
+      <c r="M3" s="4"/>
+      <c r="N3" s="4">
         <v>15</v>
-      </c>
-      <c r="M3" s="4">
-        <v>14</v>
-      </c>
-      <c r="N3" s="4">
-        <v>14</v>
       </c>
       <c r="O3" s="4">
         <v>14</v>
@@ -976,10 +1000,14 @@
         <v>14</v>
       </c>
       <c r="Q3" s="4">
+        <v>14</v>
+      </c>
+      <c r="R3" s="4">
+        <v>14</v>
+      </c>
+      <c r="S3" s="4">
         <v>13</v>
       </c>
-      <c r="R3" s="4"/>
-      <c r="S3" s="4"/>
       <c r="T3" s="4"/>
       <c r="U3" s="4"/>
       <c r="V3" s="4"/>
@@ -1025,8 +1053,10 @@
       <c r="BJ3" s="4"/>
       <c r="BK3" s="4"/>
       <c r="BL3" s="4"/>
-    </row>
-    <row r="4" spans="1:65" x14ac:dyDescent="0.2">
+      <c r="BM3" s="4"/>
+      <c r="BN3" s="4"/>
+    </row>
+    <row r="4" spans="1:67" x14ac:dyDescent="0.2">
       <c r="B4" s="2" t="s">
         <v>23</v>
       </c>
@@ -1034,39 +1064,39 @@
       <c r="D4" s="4"/>
       <c r="E4" s="4"/>
       <c r="F4" s="4">
-        <f t="shared" ref="F4:F6" si="0">+Q4</f>
+        <f t="shared" ref="F4:F6" si="0">+S4</f>
         <v>46</v>
       </c>
       <c r="G4" s="4">
         <v>46</v>
       </c>
       <c r="H4" s="4">
-        <f t="shared" ref="H4:H6" si="1">+R4</f>
+        <f t="shared" ref="H4:H6" si="1">+T4</f>
         <v>0</v>
       </c>
       <c r="I4" s="4"/>
       <c r="J4" s="4"/>
       <c r="K4" s="4"/>
-      <c r="L4" s="4">
+      <c r="L4" s="4"/>
+      <c r="M4" s="4"/>
+      <c r="N4" s="4">
         <v>46</v>
       </c>
-      <c r="M4" s="4">
+      <c r="O4" s="4">
         <v>48</v>
       </c>
-      <c r="N4" s="4">
+      <c r="P4" s="4">
         <v>49</v>
-      </c>
-      <c r="O4" s="4">
-        <v>46</v>
-      </c>
-      <c r="P4" s="4">
-        <v>45</v>
       </c>
       <c r="Q4" s="4">
         <v>46</v>
       </c>
-      <c r="R4" s="4"/>
-      <c r="S4" s="4"/>
+      <c r="R4" s="4">
+        <v>45</v>
+      </c>
+      <c r="S4" s="4">
+        <v>46</v>
+      </c>
       <c r="T4" s="4"/>
       <c r="U4" s="4"/>
       <c r="V4" s="4"/>
@@ -1112,8 +1142,10 @@
       <c r="BJ4" s="4"/>
       <c r="BK4" s="4"/>
       <c r="BL4" s="4"/>
-    </row>
-    <row r="5" spans="1:65" x14ac:dyDescent="0.2">
+      <c r="BM4" s="4"/>
+      <c r="BN4" s="4"/>
+    </row>
+    <row r="5" spans="1:67" x14ac:dyDescent="0.2">
       <c r="B5" s="2" t="s">
         <v>24</v>
       </c>
@@ -1134,26 +1166,26 @@
       <c r="I5" s="4"/>
       <c r="J5" s="4"/>
       <c r="K5" s="4"/>
-      <c r="L5" s="4">
+      <c r="L5" s="4"/>
+      <c r="M5" s="4"/>
+      <c r="N5" s="4">
         <v>26</v>
       </c>
-      <c r="M5" s="4">
+      <c r="O5" s="4">
         <v>31</v>
       </c>
-      <c r="N5" s="4">
+      <c r="P5" s="4">
         <v>32</v>
       </c>
-      <c r="O5" s="4">
+      <c r="Q5" s="4">
         <v>36</v>
       </c>
-      <c r="P5" s="4">
+      <c r="R5" s="4">
         <v>38</v>
       </c>
-      <c r="Q5" s="4">
+      <c r="S5" s="4">
         <v>35</v>
       </c>
-      <c r="R5" s="4"/>
-      <c r="S5" s="4"/>
       <c r="T5" s="4"/>
       <c r="U5" s="4"/>
       <c r="V5" s="4"/>
@@ -1199,8 +1231,10 @@
       <c r="BJ5" s="4"/>
       <c r="BK5" s="4"/>
       <c r="BL5" s="4"/>
-    </row>
-    <row r="6" spans="1:65" x14ac:dyDescent="0.2">
+      <c r="BM5" s="4"/>
+      <c r="BN5" s="4"/>
+    </row>
+    <row r="6" spans="1:67" x14ac:dyDescent="0.2">
       <c r="B6" s="2" t="s">
         <v>25</v>
       </c>
@@ -1221,29 +1255,29 @@
       <c r="I6" s="4"/>
       <c r="J6" s="4"/>
       <c r="K6" s="4"/>
-      <c r="L6" s="4">
+      <c r="L6" s="4"/>
+      <c r="M6" s="4"/>
+      <c r="N6" s="4">
         <f>22+18</f>
         <v>40</v>
       </c>
-      <c r="M6" s="4">
+      <c r="O6" s="4">
         <f>24+19</f>
         <v>43</v>
       </c>
-      <c r="N6" s="4">
+      <c r="P6" s="4">
         <f>24+19</f>
         <v>43</v>
       </c>
-      <c r="O6" s="4">
+      <c r="Q6" s="4">
         <v>48</v>
       </c>
-      <c r="P6" s="4">
+      <c r="R6" s="4">
         <v>52</v>
       </c>
-      <c r="Q6" s="4">
+      <c r="S6" s="4">
         <v>58</v>
       </c>
-      <c r="R6" s="4"/>
-      <c r="S6" s="4"/>
       <c r="T6" s="4"/>
       <c r="U6" s="4"/>
       <c r="V6" s="4"/>
@@ -1289,8 +1323,10 @@
       <c r="BJ6" s="4"/>
       <c r="BK6" s="4"/>
       <c r="BL6" s="4"/>
-    </row>
-    <row r="7" spans="1:65" x14ac:dyDescent="0.2">
+      <c r="BM6" s="4"/>
+      <c r="BN6" s="4"/>
+    </row>
+    <row r="7" spans="1:67" x14ac:dyDescent="0.2">
       <c r="B7" s="5" t="s">
         <v>26</v>
       </c>
@@ -1321,33 +1357,33 @@
       <c r="I7" s="6"/>
       <c r="J7" s="6"/>
       <c r="K7" s="6"/>
-      <c r="L7" s="6">
-        <f t="shared" ref="L7:Q7" si="3">+SUM(L3:L6)</f>
+      <c r="L7" s="6"/>
+      <c r="M7" s="6"/>
+      <c r="N7" s="6">
+        <f t="shared" ref="N7:S7" si="3">+SUM(N3:N6)</f>
         <v>127</v>
       </c>
-      <c r="M7" s="6">
+      <c r="O7" s="6">
         <f t="shared" si="3"/>
         <v>136</v>
       </c>
-      <c r="N7" s="6">
+      <c r="P7" s="6">
         <f t="shared" si="3"/>
         <v>138</v>
       </c>
-      <c r="O7" s="6">
+      <c r="Q7" s="6">
         <f t="shared" si="3"/>
         <v>144</v>
       </c>
-      <c r="P7" s="6">
+      <c r="R7" s="6">
         <f t="shared" si="3"/>
         <v>149</v>
       </c>
-      <c r="Q7" s="6">
+      <c r="S7" s="6">
         <f t="shared" si="3"/>
         <v>152</v>
       </c>
-      <c r="R7" s="6"/>
-      <c r="S7" s="4"/>
-      <c r="T7" s="4"/>
+      <c r="T7" s="6"/>
       <c r="U7" s="4"/>
       <c r="V7" s="4"/>
       <c r="W7" s="4"/>
@@ -1392,8 +1428,10 @@
       <c r="BJ7" s="4"/>
       <c r="BK7" s="4"/>
       <c r="BL7" s="4"/>
-    </row>
-    <row r="8" spans="1:65" x14ac:dyDescent="0.2">
+      <c r="BM7" s="4"/>
+      <c r="BN7" s="4"/>
+    </row>
+    <row r="8" spans="1:67" x14ac:dyDescent="0.2">
       <c r="B8" s="2" t="s">
         <v>62</v>
       </c>
@@ -1423,34 +1461,34 @@
       </c>
       <c r="I8" s="7"/>
       <c r="J8" s="7"/>
-      <c r="K8" s="6"/>
-      <c r="L8" s="7">
-        <f t="shared" ref="L8:P8" si="10">+L16/L7</f>
+      <c r="K8" s="7"/>
+      <c r="L8" s="7"/>
+      <c r="M8" s="6"/>
+      <c r="N8" s="7">
+        <f t="shared" ref="N8:R8" si="10">+N16/N7</f>
         <v>4.3542992125984252</v>
       </c>
-      <c r="M8" s="7">
+      <c r="O8" s="7">
         <f t="shared" si="10"/>
         <v>4.4688308823529406</v>
       </c>
-      <c r="N8" s="7">
+      <c r="P8" s="7">
         <f t="shared" si="10"/>
         <v>3.9421231884057972</v>
       </c>
-      <c r="O8" s="7">
+      <c r="Q8" s="7">
         <f t="shared" si="10"/>
         <v>4.9456875000000009</v>
       </c>
-      <c r="P8" s="7">
+      <c r="R8" s="7">
         <f t="shared" si="10"/>
         <v>6.1725369127516787</v>
       </c>
-      <c r="Q8" s="7">
-        <f>+Q16/Q7</f>
+      <c r="S8" s="7">
+        <f>+S16/S7</f>
         <v>7.4961842105263159</v>
       </c>
-      <c r="R8" s="6"/>
-      <c r="S8" s="4"/>
-      <c r="T8" s="4"/>
+      <c r="T8" s="6"/>
       <c r="U8" s="4"/>
       <c r="V8" s="4"/>
       <c r="W8" s="4"/>
@@ -1495,8 +1533,10 @@
       <c r="BJ8" s="4"/>
       <c r="BK8" s="4"/>
       <c r="BL8" s="4"/>
-    </row>
-    <row r="9" spans="1:65" x14ac:dyDescent="0.2">
+      <c r="BM8" s="4"/>
+      <c r="BN8" s="4"/>
+    </row>
+    <row r="9" spans="1:67" x14ac:dyDescent="0.2">
       <c r="C9" s="4"/>
       <c r="D9" s="4"/>
       <c r="E9" s="4"/>
@@ -1559,8 +1599,10 @@
       <c r="BJ9" s="4"/>
       <c r="BK9" s="4"/>
       <c r="BL9" s="4"/>
-    </row>
-    <row r="10" spans="1:65" x14ac:dyDescent="0.2">
+      <c r="BM9" s="4"/>
+      <c r="BN9" s="4"/>
+    </row>
+    <row r="10" spans="1:67" x14ac:dyDescent="0.2">
       <c r="B10" s="2" t="s">
         <v>27</v>
       </c>
@@ -1570,7 +1612,7 @@
         <v>141.881</v>
       </c>
       <c r="F10" s="8">
-        <f>+Q10-E10</f>
+        <f>+S10-E10</f>
         <v>157.499</v>
       </c>
       <c r="G10" s="8">
@@ -1581,33 +1623,35 @@
         <v>243.21299999999999</v>
       </c>
       <c r="J10" s="8"/>
-      <c r="K10" s="8"/>
-      <c r="L10" s="8">
+      <c r="K10" s="8">
+        <v>255.58199999999999</v>
+      </c>
+      <c r="L10" s="8"/>
+      <c r="M10" s="8"/>
+      <c r="N10" s="8">
         <v>163.70699999999999</v>
       </c>
-      <c r="M10" s="8">
+      <c r="O10" s="8">
         <v>176.9</v>
       </c>
-      <c r="N10" s="8">
+      <c r="P10" s="8">
         <v>173.078</v>
       </c>
-      <c r="O10" s="8">
+      <c r="Q10" s="8">
         <v>219.15</v>
       </c>
-      <c r="P10" s="8">
+      <c r="R10" s="8">
         <v>263.81400000000002</v>
       </c>
-      <c r="Q10" s="8">
+      <c r="S10" s="8">
         <v>299.38</v>
       </c>
-      <c r="R10" s="8">
+      <c r="T10" s="8">
         <v>315.666</v>
       </c>
-      <c r="S10" s="8">
+      <c r="U10" s="8">
         <v>494.92</v>
       </c>
-      <c r="T10" s="8"/>
-      <c r="U10" s="8"/>
       <c r="V10" s="8"/>
       <c r="W10" s="8"/>
       <c r="X10" s="8"/>
@@ -1652,8 +1696,10 @@
       <c r="BK10" s="8"/>
       <c r="BL10" s="8"/>
       <c r="BM10" s="8"/>
-    </row>
-    <row r="11" spans="1:65" x14ac:dyDescent="0.2">
+      <c r="BN10" s="8"/>
+      <c r="BO10" s="8"/>
+    </row>
+    <row r="11" spans="1:67" x14ac:dyDescent="0.2">
       <c r="B11" s="2" t="s">
         <v>28</v>
       </c>
@@ -1663,42 +1709,46 @@
         <v>60.887999999999998</v>
       </c>
       <c r="F11" s="8">
-        <f t="shared" ref="F11:F32" si="11">+Q11-E11</f>
+        <f t="shared" ref="F11:F32" si="11">+S11-E11</f>
         <v>67.963999999999999</v>
       </c>
       <c r="G11" s="8">
         <v>68.093000000000004</v>
       </c>
       <c r="H11" s="8"/>
-      <c r="I11" s="8"/>
+      <c r="I11" s="16" t="s">
+        <v>72</v>
+      </c>
       <c r="J11" s="8"/>
-      <c r="K11" s="8"/>
-      <c r="L11" s="8">
+      <c r="K11" s="16" t="s">
+        <v>72</v>
+      </c>
+      <c r="L11" s="8"/>
+      <c r="M11" s="8"/>
+      <c r="N11" s="8">
         <v>88.22</v>
       </c>
-      <c r="M11" s="8">
+      <c r="O11" s="8">
         <v>89.72</v>
       </c>
-      <c r="N11" s="8">
+      <c r="P11" s="8">
         <v>68.322999999999993</v>
       </c>
-      <c r="O11" s="8">
+      <c r="Q11" s="8">
         <v>84.222999999999999</v>
       </c>
-      <c r="P11" s="8">
+      <c r="R11" s="8">
         <v>102.753</v>
       </c>
-      <c r="Q11" s="8">
+      <c r="S11" s="8">
         <v>128.852</v>
       </c>
-      <c r="R11" s="8">
+      <c r="T11" s="8">
         <v>140.92099999999999</v>
       </c>
-      <c r="S11" s="8">
+      <c r="U11" s="8">
         <v>0</v>
       </c>
-      <c r="T11" s="8"/>
-      <c r="U11" s="8"/>
       <c r="V11" s="8"/>
       <c r="W11" s="8"/>
       <c r="X11" s="8"/>
@@ -1743,8 +1793,10 @@
       <c r="BK11" s="8"/>
       <c r="BL11" s="8"/>
       <c r="BM11" s="8"/>
-    </row>
-    <row r="12" spans="1:65" x14ac:dyDescent="0.2">
+      <c r="BN11" s="8"/>
+      <c r="BO11" s="8"/>
+    </row>
+    <row r="12" spans="1:67" x14ac:dyDescent="0.2">
       <c r="B12" s="2" t="s">
         <v>29</v>
       </c>
@@ -1765,33 +1817,35 @@
         <v>245.23699999999999</v>
       </c>
       <c r="J12" s="8"/>
-      <c r="K12" s="8"/>
-      <c r="L12" s="8">
+      <c r="K12" s="8">
+        <v>278.67099999999999</v>
+      </c>
+      <c r="L12" s="8"/>
+      <c r="M12" s="8"/>
+      <c r="N12" s="8">
         <v>187.23599999999999</v>
       </c>
-      <c r="M12" s="8">
+      <c r="O12" s="8">
         <v>205.768</v>
       </c>
-      <c r="N12" s="8">
+      <c r="P12" s="8">
         <v>174.24199999999999</v>
       </c>
-      <c r="O12" s="8">
+      <c r="Q12" s="8">
         <v>238.238</v>
       </c>
-      <c r="P12" s="8">
+      <c r="R12" s="8">
         <v>334.69299999999998</v>
       </c>
-      <c r="Q12" s="8">
+      <c r="S12" s="8">
         <v>404.45299999999997</v>
       </c>
-      <c r="R12" s="8">
+      <c r="T12" s="8">
         <v>476.55900000000003</v>
       </c>
-      <c r="S12" s="8">
+      <c r="U12" s="8">
         <v>520.48800000000006</v>
       </c>
-      <c r="T12" s="8"/>
-      <c r="U12" s="8"/>
       <c r="V12" s="8"/>
       <c r="W12" s="8"/>
       <c r="X12" s="8"/>
@@ -1836,8 +1890,10 @@
       <c r="BK12" s="8"/>
       <c r="BL12" s="8"/>
       <c r="BM12" s="8"/>
-    </row>
-    <row r="13" spans="1:65" x14ac:dyDescent="0.2">
+      <c r="BN12" s="8"/>
+      <c r="BO12" s="8"/>
+    </row>
+    <row r="13" spans="1:67" x14ac:dyDescent="0.2">
       <c r="B13" s="2" t="s">
         <v>30</v>
       </c>
@@ -1858,34 +1914,36 @@
         <v>195.66200000000001</v>
       </c>
       <c r="J13" s="8"/>
-      <c r="K13" s="8"/>
-      <c r="L13" s="8">
+      <c r="K13" s="8">
+        <v>215.15799999999999</v>
+      </c>
+      <c r="L13" s="8"/>
+      <c r="M13" s="8"/>
+      <c r="N13" s="8">
         <f>54.887+58.946</f>
         <v>113.833</v>
       </c>
-      <c r="M13" s="8">
+      <c r="O13" s="8">
         <v>135.37299999999999</v>
       </c>
-      <c r="N13" s="8">
+      <c r="P13" s="8">
         <v>128.37</v>
       </c>
-      <c r="O13" s="8">
+      <c r="Q13" s="8">
         <v>170.56800000000001</v>
       </c>
-      <c r="P13" s="8">
+      <c r="R13" s="8">
         <v>218.44800000000001</v>
       </c>
-      <c r="Q13" s="8">
+      <c r="S13" s="8">
         <v>306.73500000000001</v>
       </c>
-      <c r="R13" s="8">
+      <c r="T13" s="8">
         <v>345.39400000000001</v>
       </c>
-      <c r="S13" s="8">
+      <c r="U13" s="8">
         <v>392.54300000000001</v>
       </c>
-      <c r="T13" s="8"/>
-      <c r="U13" s="8"/>
       <c r="V13" s="8"/>
       <c r="W13" s="8"/>
       <c r="X13" s="8"/>
@@ -1930,8 +1988,10 @@
       <c r="BK13" s="8"/>
       <c r="BL13" s="8"/>
       <c r="BM13" s="8"/>
-    </row>
-    <row r="14" spans="1:65" x14ac:dyDescent="0.2">
+      <c r="BN13" s="8"/>
+      <c r="BO13" s="8"/>
+    </row>
+    <row r="14" spans="1:67" x14ac:dyDescent="0.2">
       <c r="B14" s="2" t="s">
         <v>31</v>
       </c>
@@ -1952,33 +2012,35 @@
         <v>435.80599999999998</v>
       </c>
       <c r="J14" s="8"/>
-      <c r="K14" s="8"/>
-      <c r="L14" s="8">
+      <c r="K14" s="8">
+        <v>499.76499999999999</v>
+      </c>
+      <c r="L14" s="8"/>
+      <c r="M14" s="8"/>
+      <c r="N14" s="8">
         <v>296.26499999999999</v>
       </c>
-      <c r="M14" s="8">
+      <c r="O14" s="8">
         <v>339.435</v>
       </c>
-      <c r="N14" s="8">
+      <c r="P14" s="8">
         <v>268.77300000000002</v>
       </c>
-      <c r="O14" s="8">
+      <c r="Q14" s="8">
         <v>419.81700000000001</v>
       </c>
-      <c r="P14" s="8">
+      <c r="R14" s="8">
         <v>573.32000000000005</v>
       </c>
-      <c r="Q14" s="8">
+      <c r="S14" s="8">
         <v>746.81600000000003</v>
       </c>
-      <c r="R14" s="8">
+      <c r="T14" s="8">
         <v>851.24300000000005</v>
       </c>
-      <c r="S14" s="8">
+      <c r="U14" s="8">
         <v>947.00900000000001</v>
       </c>
-      <c r="T14" s="8"/>
-      <c r="U14" s="8"/>
       <c r="V14" s="8"/>
       <c r="W14" s="8"/>
       <c r="X14" s="8"/>
@@ -2023,8 +2085,10 @@
       <c r="BK14" s="8"/>
       <c r="BL14" s="8"/>
       <c r="BM14" s="8"/>
-    </row>
-    <row r="15" spans="1:65" x14ac:dyDescent="0.2">
+      <c r="BN14" s="8"/>
+      <c r="BO14" s="8"/>
+    </row>
+    <row r="15" spans="1:67" x14ac:dyDescent="0.2">
       <c r="B15" s="2" t="s">
         <v>32</v>
       </c>
@@ -2045,34 +2109,36 @@
         <v>248.24100000000001</v>
       </c>
       <c r="J15" s="8"/>
-      <c r="K15" s="8"/>
-      <c r="L15" s="8">
+      <c r="K15" s="8">
+        <v>249.64599999999999</v>
+      </c>
+      <c r="L15" s="8"/>
+      <c r="M15" s="8"/>
+      <c r="N15" s="8">
         <f>30.205+226.526</f>
         <v>256.73099999999999</v>
       </c>
-      <c r="M15" s="8">
+      <c r="O15" s="8">
         <v>268.32600000000002</v>
       </c>
-      <c r="N15" s="8">
+      <c r="P15" s="8">
         <v>275.24</v>
       </c>
-      <c r="O15" s="8">
+      <c r="Q15" s="8">
         <v>292.36200000000002</v>
       </c>
-      <c r="P15" s="8">
+      <c r="R15" s="8">
         <v>346.38799999999998</v>
       </c>
-      <c r="Q15" s="8">
+      <c r="S15" s="8">
         <v>392.60399999999998</v>
       </c>
-      <c r="R15" s="8">
+      <c r="T15" s="8">
         <v>427.29700000000003</v>
       </c>
-      <c r="S15" s="8">
+      <c r="U15" s="8">
         <v>460.94200000000001</v>
       </c>
-      <c r="T15" s="8"/>
-      <c r="U15" s="8"/>
       <c r="V15" s="8"/>
       <c r="W15" s="8"/>
       <c r="X15" s="8"/>
@@ -2117,8 +2183,10 @@
       <c r="BK15" s="8"/>
       <c r="BL15" s="8"/>
       <c r="BM15" s="8"/>
-    </row>
-    <row r="16" spans="1:65" x14ac:dyDescent="0.2">
+      <c r="BN15" s="8"/>
+      <c r="BO15" s="8"/>
+    </row>
+    <row r="16" spans="1:67" x14ac:dyDescent="0.2">
       <c r="B16" s="5" t="s">
         <v>33</v>
       </c>
@@ -2147,40 +2215,42 @@
         <v>684.13499999999999</v>
       </c>
       <c r="J16" s="9"/>
-      <c r="K16" s="8"/>
-      <c r="L16" s="9">
-        <f t="shared" ref="L16:P16" si="14">+L14+L15</f>
+      <c r="K16" s="9">
+        <v>749.41099999999994</v>
+      </c>
+      <c r="L16" s="9"/>
+      <c r="M16" s="8"/>
+      <c r="N16" s="9">
+        <f t="shared" ref="N16:R16" si="14">+N14+N15</f>
         <v>552.99599999999998</v>
       </c>
-      <c r="M16" s="9">
+      <c r="O16" s="9">
         <f t="shared" si="14"/>
         <v>607.76099999999997</v>
       </c>
-      <c r="N16" s="9">
+      <c r="P16" s="9">
         <f t="shared" si="14"/>
         <v>544.01300000000003</v>
       </c>
-      <c r="O16" s="9">
+      <c r="Q16" s="9">
         <f t="shared" si="14"/>
         <v>712.17900000000009</v>
       </c>
-      <c r="P16" s="9">
+      <c r="R16" s="9">
         <f t="shared" si="14"/>
         <v>919.70800000000008</v>
       </c>
-      <c r="Q16" s="9">
-        <f>+Q14+Q15</f>
+      <c r="S16" s="9">
+        <f>+S14+S15</f>
         <v>1139.42</v>
       </c>
-      <c r="R16" s="9">
-        <f>+R14+R15</f>
+      <c r="T16" s="9">
+        <f>+T14+T15</f>
         <v>1278.54</v>
       </c>
-      <c r="S16" s="9">
+      <c r="U16" s="9">
         <v>1407.951</v>
       </c>
-      <c r="T16" s="8"/>
-      <c r="U16" s="8"/>
       <c r="V16" s="8"/>
       <c r="W16" s="8"/>
       <c r="X16" s="8"/>
@@ -2225,8 +2295,10 @@
       <c r="BK16" s="8"/>
       <c r="BL16" s="8"/>
       <c r="BM16" s="8"/>
-    </row>
-    <row r="17" spans="2:65" x14ac:dyDescent="0.2">
+      <c r="BN16" s="8"/>
+      <c r="BO16" s="8"/>
+    </row>
+    <row r="17" spans="2:67" x14ac:dyDescent="0.2">
       <c r="B17" s="2" t="s">
         <v>34</v>
       </c>
@@ -2247,33 +2319,35 @@
         <v>58.384</v>
       </c>
       <c r="J17" s="8"/>
-      <c r="K17" s="8"/>
-      <c r="L17" s="8">
+      <c r="K17" s="8">
+        <v>68.566999999999993</v>
+      </c>
+      <c r="L17" s="8"/>
+      <c r="M17" s="8"/>
+      <c r="N17" s="8">
         <v>88.055999999999997</v>
       </c>
-      <c r="M17" s="8">
+      <c r="O17" s="8">
         <v>72.278999999999996</v>
       </c>
-      <c r="N17" s="8">
+      <c r="P17" s="8">
         <v>53.725000000000001</v>
       </c>
-      <c r="O17" s="8">
+      <c r="Q17" s="8">
         <v>113.61</v>
       </c>
-      <c r="P17" s="8">
+      <c r="R17" s="8">
         <v>95.537000000000006</v>
       </c>
-      <c r="Q17" s="8">
+      <c r="S17" s="8">
         <v>114.343</v>
       </c>
-      <c r="R17" s="8">
+      <c r="T17" s="8">
         <v>101.8</v>
       </c>
-      <c r="S17" s="8">
+      <c r="U17" s="8">
         <v>121.099</v>
       </c>
-      <c r="T17" s="8"/>
-      <c r="U17" s="8"/>
       <c r="V17" s="8"/>
       <c r="W17" s="8"/>
       <c r="X17" s="8"/>
@@ -2318,8 +2392,10 @@
       <c r="BK17" s="8"/>
       <c r="BL17" s="8"/>
       <c r="BM17" s="8"/>
-    </row>
-    <row r="18" spans="2:65" x14ac:dyDescent="0.2">
+      <c r="BN17" s="8"/>
+      <c r="BO17" s="8"/>
+    </row>
+    <row r="18" spans="2:67" x14ac:dyDescent="0.2">
       <c r="B18" s="2" t="s">
         <v>35</v>
       </c>
@@ -2344,49 +2420,55 @@
         <v>581.38600000000008</v>
       </c>
       <c r="H18" s="8">
-        <f t="shared" ref="H18:I18" si="16">+H16-H17</f>
+        <f t="shared" ref="H18:K18" si="16">+H16-H17</f>
         <v>0</v>
       </c>
       <c r="I18" s="8">
         <f t="shared" si="16"/>
         <v>625.75099999999998</v>
       </c>
-      <c r="J18" s="8"/>
-      <c r="K18" s="8"/>
-      <c r="L18" s="8">
-        <f t="shared" ref="L18:O18" si="17">+L16-L17</f>
+      <c r="J18" s="8">
+        <f t="shared" si="16"/>
+        <v>0</v>
+      </c>
+      <c r="K18" s="8">
+        <f t="shared" si="16"/>
+        <v>680.84399999999994</v>
+      </c>
+      <c r="L18" s="8"/>
+      <c r="M18" s="8"/>
+      <c r="N18" s="8">
+        <f t="shared" ref="N18:Q18" si="17">+N16-N17</f>
         <v>464.94</v>
       </c>
-      <c r="M18" s="8">
+      <c r="O18" s="8">
         <f t="shared" si="17"/>
         <v>535.48199999999997</v>
       </c>
-      <c r="N18" s="8">
+      <c r="P18" s="8">
         <f t="shared" si="17"/>
         <v>490.28800000000001</v>
       </c>
-      <c r="O18" s="8">
+      <c r="Q18" s="8">
         <f t="shared" si="17"/>
         <v>598.56900000000007</v>
       </c>
-      <c r="P18" s="8">
-        <f>+P16-P17</f>
-        <v>824.17100000000005</v>
-      </c>
-      <c r="Q18" s="8">
-        <f>+Q16-Q17</f>
-        <v>1025.077</v>
-      </c>
       <c r="R18" s="8">
         <f>+R16-R17</f>
-        <v>1176.74</v>
+        <v>824.17100000000005</v>
       </c>
       <c r="S18" s="8">
         <f>+S16-S17</f>
+        <v>1025.077</v>
+      </c>
+      <c r="T18" s="8">
+        <f>+T16-T17</f>
+        <v>1176.74</v>
+      </c>
+      <c r="U18" s="8">
+        <f>+U16-U17</f>
         <v>1286.8520000000001</v>
       </c>
-      <c r="T18" s="8"/>
-      <c r="U18" s="8"/>
       <c r="V18" s="8"/>
       <c r="W18" s="8"/>
       <c r="X18" s="8"/>
@@ -2431,8 +2513,10 @@
       <c r="BK18" s="8"/>
       <c r="BL18" s="8"/>
       <c r="BM18" s="8"/>
-    </row>
-    <row r="19" spans="2:65" x14ac:dyDescent="0.2">
+      <c r="BN18" s="8"/>
+      <c r="BO18" s="8"/>
+    </row>
+    <row r="19" spans="2:67" x14ac:dyDescent="0.2">
       <c r="B19" s="2" t="s">
         <v>36</v>
       </c>
@@ -2453,33 +2537,35 @@
         <v>291.43700000000001</v>
       </c>
       <c r="J19" s="8"/>
-      <c r="K19" s="8"/>
-      <c r="L19" s="8">
+      <c r="K19" s="8">
+        <v>303.24099999999999</v>
+      </c>
+      <c r="L19" s="8"/>
+      <c r="M19" s="8"/>
+      <c r="N19" s="8">
         <v>268.32799999999997</v>
       </c>
-      <c r="M19" s="8">
+      <c r="O19" s="8">
         <v>248.06700000000001</v>
       </c>
-      <c r="N19" s="8">
+      <c r="P19" s="8">
         <v>243.29599999999999</v>
       </c>
-      <c r="O19" s="8">
+      <c r="Q19" s="8">
         <v>271.084</v>
       </c>
-      <c r="P19" s="8">
+      <c r="R19" s="8">
         <v>372.22399999999999</v>
       </c>
-      <c r="Q19" s="8">
+      <c r="S19" s="8">
         <v>475.76900000000001</v>
       </c>
-      <c r="R19" s="8">
+      <c r="T19" s="8">
         <v>560.36099999999999</v>
       </c>
-      <c r="S19" s="8">
+      <c r="U19" s="8">
         <v>595.73699999999997</v>
       </c>
-      <c r="T19" s="8"/>
-      <c r="U19" s="8"/>
       <c r="V19" s="8"/>
       <c r="W19" s="8"/>
       <c r="X19" s="8"/>
@@ -2524,8 +2610,10 @@
       <c r="BK19" s="8"/>
       <c r="BL19" s="8"/>
       <c r="BM19" s="8"/>
-    </row>
-    <row r="20" spans="2:65" x14ac:dyDescent="0.2">
+      <c r="BN19" s="8"/>
+      <c r="BO19" s="8"/>
+    </row>
+    <row r="20" spans="2:67" x14ac:dyDescent="0.2">
       <c r="B20" s="2" t="s">
         <v>37</v>
       </c>
@@ -2546,33 +2634,35 @@
         <v>125.614</v>
       </c>
       <c r="J20" s="8"/>
-      <c r="K20" s="8"/>
-      <c r="L20" s="8">
+      <c r="K20" s="8">
+        <v>138.36699999999999</v>
+      </c>
+      <c r="L20" s="8"/>
+      <c r="M20" s="8"/>
+      <c r="N20" s="8">
         <v>98.328999999999994</v>
       </c>
-      <c r="M20" s="8">
+      <c r="O20" s="8">
         <v>112.199</v>
       </c>
-      <c r="N20" s="8">
+      <c r="P20" s="8">
         <v>119.569</v>
       </c>
-      <c r="O20" s="8">
+      <c r="Q20" s="8">
         <v>132.94800000000001</v>
       </c>
-      <c r="P20" s="8">
+      <c r="R20" s="8">
         <v>164.71299999999999</v>
       </c>
-      <c r="Q20" s="8">
+      <c r="S20" s="8">
         <v>194.96899999999999</v>
       </c>
-      <c r="R20" s="8">
+      <c r="T20" s="8">
         <v>233.49199999999999</v>
       </c>
-      <c r="S20" s="8">
+      <c r="U20" s="8">
         <v>255.36699999999999</v>
       </c>
-      <c r="T20" s="8"/>
-      <c r="U20" s="8"/>
       <c r="V20" s="8"/>
       <c r="W20" s="8"/>
       <c r="X20" s="8"/>
@@ -2617,8 +2707,10 @@
       <c r="BK20" s="8"/>
       <c r="BL20" s="8"/>
       <c r="BM20" s="8"/>
-    </row>
-    <row r="21" spans="2:65" x14ac:dyDescent="0.2">
+      <c r="BN20" s="8"/>
+      <c r="BO20" s="8"/>
+    </row>
+    <row r="21" spans="2:67" x14ac:dyDescent="0.2">
       <c r="B21" s="2" t="s">
         <v>38</v>
       </c>
@@ -2639,33 +2731,35 @@
         <v>8.9450000000000003</v>
       </c>
       <c r="J21" s="8"/>
-      <c r="K21" s="8"/>
-      <c r="L21" s="8">
+      <c r="K21" s="8">
+        <v>13.019</v>
+      </c>
+      <c r="L21" s="8"/>
+      <c r="M21" s="8"/>
+      <c r="N21" s="8">
         <v>5.9160000000000004</v>
       </c>
-      <c r="M21" s="8">
+      <c r="O21" s="8">
         <v>7.53</v>
       </c>
-      <c r="N21" s="8">
+      <c r="P21" s="8">
         <v>8.9019999999999992</v>
       </c>
-      <c r="O21" s="8">
+      <c r="Q21" s="8">
         <v>9.8130000000000006</v>
       </c>
-      <c r="P21" s="8">
+      <c r="R21" s="8">
         <v>16.491</v>
       </c>
-      <c r="Q21" s="8">
+      <c r="S21" s="8">
         <v>21.568999999999999</v>
       </c>
-      <c r="R21" s="8">
+      <c r="T21" s="8">
         <v>21.079000000000001</v>
       </c>
-      <c r="S21" s="8">
+      <c r="U21" s="8">
         <v>25.614000000000001</v>
       </c>
-      <c r="T21" s="8"/>
-      <c r="U21" s="8"/>
       <c r="V21" s="8"/>
       <c r="W21" s="8"/>
       <c r="X21" s="8"/>
@@ -2710,8 +2804,10 @@
       <c r="BK21" s="8"/>
       <c r="BL21" s="8"/>
       <c r="BM21" s="8"/>
-    </row>
-    <row r="22" spans="2:65" x14ac:dyDescent="0.2">
+      <c r="BN21" s="8"/>
+      <c r="BO21" s="8"/>
+    </row>
+    <row r="22" spans="2:67" x14ac:dyDescent="0.2">
       <c r="B22" s="2" t="s">
         <v>39</v>
       </c>
@@ -2732,33 +2828,35 @@
         <v>1.556</v>
       </c>
       <c r="J22" s="8"/>
-      <c r="K22" s="8"/>
-      <c r="L22" s="8">
+      <c r="K22" s="8">
+        <v>1.716</v>
+      </c>
+      <c r="L22" s="8"/>
+      <c r="M22" s="8"/>
+      <c r="N22" s="8">
         <v>1.448</v>
       </c>
-      <c r="M22" s="8">
+      <c r="O22" s="8">
         <v>0.82599999999999996</v>
       </c>
-      <c r="N22" s="8">
+      <c r="P22" s="8">
         <v>2.7719999999999998</v>
       </c>
-      <c r="O22" s="8">
+      <c r="Q22" s="8">
         <v>10.054</v>
       </c>
-      <c r="P22" s="8">
+      <c r="R22" s="8">
         <v>1.9470000000000001</v>
       </c>
-      <c r="Q22" s="8">
+      <c r="S22" s="8">
         <v>2.3690000000000002</v>
       </c>
-      <c r="R22" s="8">
+      <c r="T22" s="8">
         <v>3.2709999999999999</v>
       </c>
-      <c r="S22" s="8">
+      <c r="U22" s="8">
         <v>5.4039999999999999</v>
       </c>
-      <c r="T22" s="8"/>
-      <c r="U22" s="8"/>
       <c r="V22" s="8"/>
       <c r="W22" s="8"/>
       <c r="X22" s="8"/>
@@ -2803,8 +2901,10 @@
       <c r="BK22" s="8"/>
       <c r="BL22" s="8"/>
       <c r="BM22" s="8"/>
-    </row>
-    <row r="23" spans="2:65" x14ac:dyDescent="0.2">
+      <c r="BN22" s="8"/>
+      <c r="BO22" s="8"/>
+    </row>
+    <row r="23" spans="2:67" x14ac:dyDescent="0.2">
       <c r="B23" s="2" t="s">
         <v>40</v>
       </c>
@@ -2825,33 +2925,35 @@
         <v>0.82099999999999995</v>
       </c>
       <c r="J23" s="8"/>
-      <c r="K23" s="8"/>
-      <c r="L23" s="8">
+      <c r="K23" s="8">
+        <v>0.55800000000000005</v>
+      </c>
+      <c r="L23" s="8"/>
+      <c r="M23" s="8"/>
+      <c r="N23" s="8">
         <v>2.4700000000000002</v>
       </c>
-      <c r="M23" s="8">
+      <c r="O23" s="8">
         <v>2.3820000000000001</v>
       </c>
-      <c r="N23" s="8">
+      <c r="P23" s="8">
         <v>3.258</v>
       </c>
-      <c r="O23" s="8">
+      <c r="Q23" s="8">
         <v>3.4449999999999998</v>
       </c>
-      <c r="P23" s="8">
+      <c r="R23" s="8">
         <v>2.153</v>
       </c>
-      <c r="Q23" s="8">
+      <c r="S23" s="8">
         <v>2.4319999999999999</v>
       </c>
-      <c r="R23" s="8">
+      <c r="T23" s="8">
         <v>2.4169999999999998</v>
       </c>
-      <c r="S23" s="8">
+      <c r="U23" s="8">
         <v>1.7350000000000001</v>
       </c>
-      <c r="T23" s="8"/>
-      <c r="U23" s="8"/>
       <c r="V23" s="8"/>
       <c r="W23" s="8"/>
       <c r="X23" s="8"/>
@@ -2896,8 +2998,10 @@
       <c r="BK23" s="8"/>
       <c r="BL23" s="8"/>
       <c r="BM23" s="8"/>
-    </row>
-    <row r="24" spans="2:65" x14ac:dyDescent="0.2">
+      <c r="BN23" s="8"/>
+      <c r="BO23" s="8"/>
+    </row>
+    <row r="24" spans="2:67" x14ac:dyDescent="0.2">
       <c r="B24" s="2" t="s">
         <v>41</v>
       </c>
@@ -2918,33 +3022,35 @@
         <v>86.778000000000006</v>
       </c>
       <c r="J24" s="8"/>
-      <c r="K24" s="8"/>
-      <c r="L24" s="8">
+      <c r="K24" s="8">
+        <v>98.343000000000004</v>
+      </c>
+      <c r="L24" s="8"/>
+      <c r="M24" s="8"/>
+      <c r="N24" s="8">
         <v>25.605</v>
       </c>
-      <c r="M24" s="8">
+      <c r="O24" s="8">
         <v>86.25</v>
       </c>
-      <c r="N24" s="8">
+      <c r="P24" s="8">
         <v>104.28400000000001</v>
       </c>
-      <c r="O24" s="8">
+      <c r="Q24" s="8">
         <v>116.27500000000001</v>
       </c>
-      <c r="P24" s="8">
+      <c r="R24" s="8">
         <v>131.94499999999999</v>
       </c>
-      <c r="Q24" s="8">
+      <c r="S24" s="8">
         <v>138.845</v>
       </c>
-      <c r="R24" s="8">
+      <c r="T24" s="8">
         <v>153.00399999999999</v>
       </c>
-      <c r="S24" s="8">
+      <c r="U24" s="8">
         <v>180.61199999999999</v>
       </c>
-      <c r="T24" s="8"/>
-      <c r="U24" s="8"/>
       <c r="V24" s="8"/>
       <c r="W24" s="8"/>
       <c r="X24" s="8"/>
@@ -2989,8 +3095,10 @@
       <c r="BK24" s="8"/>
       <c r="BL24" s="8"/>
       <c r="BM24" s="8"/>
-    </row>
-    <row r="25" spans="2:65" x14ac:dyDescent="0.2">
+      <c r="BN24" s="8"/>
+      <c r="BO24" s="8"/>
+    </row>
+    <row r="25" spans="2:67" x14ac:dyDescent="0.2">
       <c r="B25" s="2" t="s">
         <v>42</v>
       </c>
@@ -3011,33 +3119,35 @@
         <v>1.5169999999999999</v>
       </c>
       <c r="J25" s="8"/>
-      <c r="K25" s="8"/>
-      <c r="L25" s="8">
+      <c r="K25" s="8">
+        <v>1.9490000000000001</v>
+      </c>
+      <c r="L25" s="8"/>
+      <c r="M25" s="8"/>
+      <c r="N25" s="8">
         <v>1.1419999999999999</v>
       </c>
-      <c r="M25" s="8">
+      <c r="O25" s="8">
         <v>1.268</v>
       </c>
-      <c r="N25" s="8">
+      <c r="P25" s="8">
         <v>35.085000000000001</v>
       </c>
-      <c r="O25" s="8">
+      <c r="Q25" s="8">
         <v>4.9119999999999999</v>
       </c>
-      <c r="P25" s="8">
+      <c r="R25" s="8">
         <v>8.4860000000000007</v>
       </c>
-      <c r="Q25" s="8">
+      <c r="S25" s="8">
         <v>11.32</v>
       </c>
-      <c r="R25" s="8">
+      <c r="T25" s="8">
         <v>2.8210000000000002</v>
       </c>
-      <c r="S25" s="8">
+      <c r="U25" s="8">
         <v>8.8770000000000007</v>
       </c>
-      <c r="T25" s="8"/>
-      <c r="U25" s="8"/>
       <c r="V25" s="8"/>
       <c r="W25" s="8"/>
       <c r="X25" s="8"/>
@@ -3082,8 +3192,10 @@
       <c r="BK25" s="8"/>
       <c r="BL25" s="8"/>
       <c r="BM25" s="8"/>
-    </row>
-    <row r="26" spans="2:65" x14ac:dyDescent="0.2">
+      <c r="BN25" s="8"/>
+      <c r="BO25" s="8"/>
+    </row>
+    <row r="26" spans="2:67" x14ac:dyDescent="0.2">
       <c r="B26" s="2" t="s">
         <v>43</v>
       </c>
@@ -3108,49 +3220,55 @@
         <v>104.58700000000006</v>
       </c>
       <c r="H26" s="8">
-        <f t="shared" ref="H26:S26" si="19">+H18-SUM(H19:H21)+H22+H23-H24-H25</f>
+        <f t="shared" ref="H26:U26" si="19">+H18-SUM(H19:H21)+H22+H23-H24-H25</f>
         <v>0</v>
       </c>
       <c r="I26" s="8">
         <f t="shared" si="19"/>
         <v>113.83699999999995</v>
       </c>
-      <c r="J26" s="8"/>
-      <c r="K26" s="8"/>
-      <c r="L26" s="8">
+      <c r="J26" s="8">
+        <f t="shared" si="19"/>
+        <v>0</v>
+      </c>
+      <c r="K26" s="8">
+        <f t="shared" si="19"/>
+        <v>128.19899999999996</v>
+      </c>
+      <c r="L26" s="8"/>
+      <c r="M26" s="8"/>
+      <c r="N26" s="8">
         <f t="shared" si="19"/>
         <v>69.538000000000011</v>
       </c>
-      <c r="M26" s="8">
+      <c r="O26" s="8">
         <f t="shared" si="19"/>
         <v>83.375999999999976</v>
       </c>
-      <c r="N26" s="8">
+      <c r="P26" s="8">
         <f t="shared" si="19"/>
         <v>-14.817999999999991</v>
       </c>
-      <c r="O26" s="8">
+      <c r="Q26" s="8">
         <f t="shared" si="19"/>
         <v>77.03600000000003</v>
       </c>
-      <c r="P26" s="8">
+      <c r="R26" s="8">
         <f t="shared" si="19"/>
         <v>134.41200000000009</v>
       </c>
-      <c r="Q26" s="8">
+      <c r="S26" s="8">
         <f t="shared" si="19"/>
         <v>187.40600000000003</v>
       </c>
-      <c r="R26" s="8">
+      <c r="T26" s="8">
         <f t="shared" si="19"/>
         <v>211.67100000000011</v>
       </c>
-      <c r="S26" s="8">
+      <c r="U26" s="8">
         <f t="shared" si="19"/>
         <v>227.78400000000013</v>
       </c>
-      <c r="T26" s="8"/>
-      <c r="U26" s="8"/>
       <c r="V26" s="8"/>
       <c r="W26" s="8"/>
       <c r="X26" s="8"/>
@@ -3195,8 +3313,10 @@
       <c r="BK26" s="8"/>
       <c r="BL26" s="8"/>
       <c r="BM26" s="8"/>
-    </row>
-    <row r="27" spans="2:65" x14ac:dyDescent="0.2">
+      <c r="BN26" s="8"/>
+      <c r="BO26" s="8"/>
+    </row>
+    <row r="27" spans="2:67" x14ac:dyDescent="0.2">
       <c r="B27" s="2" t="s">
         <v>44</v>
       </c>
@@ -3217,33 +3337,35 @@
         <v>53.683999999999997</v>
       </c>
       <c r="J27" s="8"/>
-      <c r="K27" s="8"/>
-      <c r="L27" s="8">
+      <c r="K27" s="8">
+        <v>40.207000000000001</v>
+      </c>
+      <c r="L27" s="8"/>
+      <c r="M27" s="8"/>
+      <c r="N27" s="8">
         <v>26.33</v>
       </c>
-      <c r="M27" s="8">
+      <c r="O27" s="8">
         <v>41.401000000000003</v>
       </c>
-      <c r="N27" s="8">
+      <c r="P27" s="8">
         <v>46.956000000000003</v>
       </c>
-      <c r="O27" s="8">
+      <c r="Q27" s="8">
         <v>34.908000000000001</v>
       </c>
-      <c r="P27" s="8">
+      <c r="R27" s="8">
         <v>80.917000000000002</v>
       </c>
-      <c r="Q27" s="8">
+      <c r="S27" s="8">
         <v>61.338000000000001</v>
       </c>
-      <c r="R27" s="8">
+      <c r="T27" s="8">
         <v>67.558999999999997</v>
       </c>
-      <c r="S27" s="8">
+      <c r="U27" s="8">
         <v>84.634</v>
       </c>
-      <c r="T27" s="8"/>
-      <c r="U27" s="8"/>
       <c r="V27" s="8"/>
       <c r="W27" s="8"/>
       <c r="X27" s="8"/>
@@ -3288,8 +3410,10 @@
       <c r="BK27" s="8"/>
       <c r="BL27" s="8"/>
       <c r="BM27" s="8"/>
-    </row>
-    <row r="28" spans="2:65" x14ac:dyDescent="0.2">
+      <c r="BN27" s="8"/>
+      <c r="BO27" s="8"/>
+    </row>
+    <row r="28" spans="2:67" x14ac:dyDescent="0.2">
       <c r="B28" s="2" t="s">
         <v>45</v>
       </c>
@@ -3310,33 +3434,35 @@
         <v>47.203000000000003</v>
       </c>
       <c r="J28" s="8"/>
-      <c r="K28" s="8"/>
-      <c r="L28" s="8">
+      <c r="K28" s="8">
+        <v>21.797000000000001</v>
+      </c>
+      <c r="L28" s="8"/>
+      <c r="M28" s="8"/>
+      <c r="N28" s="8">
         <v>22.074000000000002</v>
       </c>
-      <c r="M28" s="8">
+      <c r="O28" s="8">
         <v>27.201000000000001</v>
       </c>
-      <c r="N28" s="8">
+      <c r="P28" s="8">
         <v>27.992000000000001</v>
       </c>
-      <c r="O28" s="8">
+      <c r="Q28" s="8">
         <v>21.898</v>
       </c>
-      <c r="P28" s="8">
+      <c r="R28" s="8">
         <v>70.471999999999994</v>
       </c>
-      <c r="Q28" s="8">
+      <c r="S28" s="8">
         <v>47.273000000000003</v>
       </c>
-      <c r="R28" s="8">
+      <c r="T28" s="8">
         <v>35.625</v>
       </c>
-      <c r="S28" s="8">
+      <c r="U28" s="8">
         <v>55.545999999999999</v>
       </c>
-      <c r="T28" s="8"/>
-      <c r="U28" s="8"/>
       <c r="V28" s="8"/>
       <c r="W28" s="8"/>
       <c r="X28" s="8"/>
@@ -3381,8 +3507,10 @@
       <c r="BK28" s="8"/>
       <c r="BL28" s="8"/>
       <c r="BM28" s="8"/>
-    </row>
-    <row r="29" spans="2:65" x14ac:dyDescent="0.2">
+      <c r="BN28" s="8"/>
+      <c r="BO28" s="8"/>
+    </row>
+    <row r="29" spans="2:67" x14ac:dyDescent="0.2">
       <c r="B29" s="2" t="s">
         <v>46</v>
       </c>
@@ -3407,49 +3535,55 @@
         <v>95.247000000000043</v>
       </c>
       <c r="H29" s="8">
-        <f t="shared" ref="H29:I29" si="21">+H26-H27+H28</f>
+        <f t="shared" ref="H29:K29" si="21">+H26-H27+H28</f>
         <v>0</v>
       </c>
       <c r="I29" s="8">
         <f t="shared" si="21"/>
         <v>107.35599999999995</v>
       </c>
-      <c r="J29" s="8"/>
-      <c r="K29" s="8"/>
-      <c r="L29" s="8">
-        <f t="shared" ref="L29:P29" si="22">+L26-L27+L28</f>
+      <c r="J29" s="8">
+        <f t="shared" si="21"/>
+        <v>0</v>
+      </c>
+      <c r="K29" s="8">
+        <f t="shared" si="21"/>
+        <v>109.78899999999996</v>
+      </c>
+      <c r="L29" s="8"/>
+      <c r="M29" s="8"/>
+      <c r="N29" s="8">
+        <f t="shared" ref="N29:R29" si="22">+N26-N27+N28</f>
         <v>65.282000000000011</v>
       </c>
-      <c r="M29" s="8">
+      <c r="O29" s="8">
         <f t="shared" si="22"/>
         <v>69.175999999999974</v>
       </c>
-      <c r="N29" s="8">
+      <c r="P29" s="8">
         <f t="shared" si="22"/>
         <v>-33.781999999999996</v>
       </c>
-      <c r="O29" s="8">
+      <c r="Q29" s="8">
         <f t="shared" si="22"/>
         <v>64.026000000000025</v>
       </c>
-      <c r="P29" s="8">
+      <c r="R29" s="8">
         <f t="shared" si="22"/>
         <v>123.96700000000008</v>
       </c>
-      <c r="Q29" s="8">
-        <f>+Q26-Q27+Q28</f>
-        <v>173.34100000000004</v>
-      </c>
-      <c r="R29" s="8">
-        <f>+R26-R27+R28</f>
-        <v>179.73700000000011</v>
-      </c>
       <c r="S29" s="8">
         <f>+S26-S27+S28</f>
+        <v>173.34100000000004</v>
+      </c>
+      <c r="T29" s="8">
+        <f>+T26-T27+T28</f>
+        <v>179.73700000000011</v>
+      </c>
+      <c r="U29" s="8">
+        <f>+U26-U27+U28</f>
         <v>198.69600000000014</v>
       </c>
-      <c r="T29" s="8"/>
-      <c r="U29" s="8"/>
       <c r="V29" s="8"/>
       <c r="W29" s="8"/>
       <c r="X29" s="8"/>
@@ -3494,8 +3628,10 @@
       <c r="BK29" s="8"/>
       <c r="BL29" s="8"/>
       <c r="BM29" s="8"/>
-    </row>
-    <row r="30" spans="2:65" x14ac:dyDescent="0.2">
+      <c r="BN29" s="8"/>
+      <c r="BO29" s="8"/>
+    </row>
+    <row r="30" spans="2:67" x14ac:dyDescent="0.2">
       <c r="B30" s="2" t="s">
         <v>48</v>
       </c>
@@ -3516,33 +3652,35 @@
         <v>30.706</v>
       </c>
       <c r="J30" s="8"/>
-      <c r="K30" s="8"/>
-      <c r="L30" s="8">
+      <c r="K30" s="8">
+        <v>31.62</v>
+      </c>
+      <c r="L30" s="8"/>
+      <c r="M30" s="8"/>
+      <c r="N30" s="8">
         <v>14.24</v>
       </c>
-      <c r="M30" s="8">
+      <c r="O30" s="8">
         <v>16.093</v>
       </c>
-      <c r="N30" s="8">
+      <c r="P30" s="8">
         <v>-1.7130000000000001</v>
       </c>
-      <c r="O30" s="8">
+      <c r="Q30" s="8">
         <v>7.7309999999999999</v>
       </c>
-      <c r="P30" s="8">
+      <c r="R30" s="8">
         <v>36.762</v>
       </c>
-      <c r="Q30" s="8">
+      <c r="S30" s="8">
         <v>49.531999999999996</v>
       </c>
-      <c r="R30" s="8">
+      <c r="T30" s="8">
         <v>51.223999999999997</v>
       </c>
-      <c r="S30" s="8">
+      <c r="U30" s="8">
         <v>56.707000000000001</v>
       </c>
-      <c r="T30" s="8"/>
-      <c r="U30" s="8"/>
       <c r="V30" s="8"/>
       <c r="W30" s="8"/>
       <c r="X30" s="8"/>
@@ -3587,8 +3725,10 @@
       <c r="BK30" s="8"/>
       <c r="BL30" s="8"/>
       <c r="BM30" s="8"/>
-    </row>
-    <row r="31" spans="2:65" x14ac:dyDescent="0.2">
+      <c r="BN30" s="8"/>
+      <c r="BO30" s="8"/>
+    </row>
+    <row r="31" spans="2:67" x14ac:dyDescent="0.2">
       <c r="B31" s="2" t="s">
         <v>47</v>
       </c>
@@ -3613,49 +3753,55 @@
         <v>66.077000000000041</v>
       </c>
       <c r="H31" s="8">
-        <f t="shared" ref="H31:I31" si="24">+H29-H30</f>
+        <f t="shared" ref="H31:K31" si="24">+H29-H30</f>
         <v>0</v>
       </c>
       <c r="I31" s="8">
         <f t="shared" si="24"/>
         <v>76.649999999999949</v>
       </c>
-      <c r="J31" s="8"/>
-      <c r="K31" s="8"/>
-      <c r="L31" s="8">
-        <f t="shared" ref="L31:P31" si="25">+L29-L30</f>
+      <c r="J31" s="8">
+        <f t="shared" si="24"/>
+        <v>0</v>
+      </c>
+      <c r="K31" s="8">
+        <f t="shared" si="24"/>
+        <v>78.168999999999954</v>
+      </c>
+      <c r="L31" s="8"/>
+      <c r="M31" s="8"/>
+      <c r="N31" s="8">
+        <f t="shared" ref="N31:R31" si="25">+N29-N30</f>
         <v>51.042000000000009</v>
       </c>
-      <c r="M31" s="8">
+      <c r="O31" s="8">
         <f t="shared" si="25"/>
         <v>53.08299999999997</v>
       </c>
-      <c r="N31" s="8">
+      <c r="P31" s="8">
         <f t="shared" si="25"/>
         <v>-32.068999999999996</v>
       </c>
-      <c r="O31" s="8">
+      <c r="Q31" s="8">
         <f t="shared" si="25"/>
         <v>56.295000000000023</v>
       </c>
-      <c r="P31" s="8">
+      <c r="R31" s="8">
         <f t="shared" si="25"/>
         <v>87.205000000000084</v>
       </c>
-      <c r="Q31" s="8">
-        <f>+Q29-Q30</f>
-        <v>123.80900000000004</v>
-      </c>
-      <c r="R31" s="8">
-        <f>+R29-R30</f>
-        <v>128.51300000000012</v>
-      </c>
       <c r="S31" s="8">
         <f>+S29-S30</f>
+        <v>123.80900000000004</v>
+      </c>
+      <c r="T31" s="8">
+        <f>+T29-T30</f>
+        <v>128.51300000000012</v>
+      </c>
+      <c r="U31" s="8">
+        <f>+U29-U30</f>
         <v>141.98900000000015</v>
       </c>
-      <c r="T31" s="8"/>
-      <c r="U31" s="8"/>
       <c r="V31" s="8"/>
       <c r="W31" s="8"/>
       <c r="X31" s="8"/>
@@ -3700,8 +3846,10 @@
       <c r="BK31" s="8"/>
       <c r="BL31" s="8"/>
       <c r="BM31" s="8"/>
-    </row>
-    <row r="32" spans="2:65" x14ac:dyDescent="0.2">
+      <c r="BN31" s="8"/>
+      <c r="BO31" s="8"/>
+    </row>
+    <row r="32" spans="2:67" x14ac:dyDescent="0.2">
       <c r="B32" s="2" t="s">
         <v>49</v>
       </c>
@@ -3722,33 +3870,35 @@
         <v>3.387</v>
       </c>
       <c r="J32" s="8"/>
-      <c r="K32" s="8"/>
-      <c r="L32" s="8">
+      <c r="K32" s="8">
+        <v>2.0470000000000002</v>
+      </c>
+      <c r="L32" s="8"/>
+      <c r="M32" s="8"/>
+      <c r="N32" s="8">
         <v>0.35</v>
       </c>
-      <c r="M32" s="8">
+      <c r="O32" s="8">
         <v>0.53</v>
       </c>
-      <c r="N32" s="8">
+      <c r="P32" s="8">
         <v>1.147</v>
       </c>
-      <c r="O32" s="8">
+      <c r="Q32" s="8">
         <v>2.9729999999999999</v>
       </c>
-      <c r="P32" s="8">
+      <c r="R32" s="8">
         <v>6.6059999999999999</v>
       </c>
-      <c r="Q32" s="8">
+      <c r="S32" s="8">
         <v>9.1920000000000002</v>
       </c>
-      <c r="R32" s="8">
+      <c r="T32" s="8">
         <v>9.0340000000000007</v>
       </c>
-      <c r="S32" s="8">
+      <c r="U32" s="8">
         <v>6.9550000000000001</v>
       </c>
-      <c r="T32" s="8"/>
-      <c r="U32" s="8"/>
       <c r="V32" s="8"/>
       <c r="W32" s="8"/>
       <c r="X32" s="8"/>
@@ -3793,8 +3943,10 @@
       <c r="BK32" s="8"/>
       <c r="BL32" s="8"/>
       <c r="BM32" s="8"/>
-    </row>
-    <row r="33" spans="2:65" x14ac:dyDescent="0.2">
+      <c r="BN32" s="8"/>
+      <c r="BO32" s="8"/>
+    </row>
+    <row r="33" spans="2:67" x14ac:dyDescent="0.2">
       <c r="B33" s="2" t="s">
         <v>50</v>
       </c>
@@ -3819,49 +3971,55 @@
         <v>60.939000000000043</v>
       </c>
       <c r="H33" s="8">
-        <f t="shared" ref="H33:I33" si="27">+H31-H32</f>
+        <f t="shared" ref="H33:K33" si="27">+H31-H32</f>
         <v>0</v>
       </c>
       <c r="I33" s="8">
         <f t="shared" si="27"/>
         <v>73.262999999999948</v>
       </c>
-      <c r="J33" s="8"/>
-      <c r="K33" s="8"/>
-      <c r="L33" s="8">
-        <f t="shared" ref="L33:O33" si="28">+L31-L32</f>
+      <c r="J33" s="8">
+        <f t="shared" si="27"/>
+        <v>0</v>
+      </c>
+      <c r="K33" s="8">
+        <f t="shared" si="27"/>
+        <v>76.121999999999957</v>
+      </c>
+      <c r="L33" s="8"/>
+      <c r="M33" s="8"/>
+      <c r="N33" s="8">
+        <f t="shared" ref="N33:Q33" si="28">+N31-N32</f>
         <v>50.692000000000007</v>
       </c>
-      <c r="M33" s="8">
+      <c r="O33" s="8">
         <f t="shared" si="28"/>
         <v>52.552999999999969</v>
       </c>
-      <c r="N33" s="8">
-        <f>+N31-N32</f>
+      <c r="P33" s="8">
+        <f>+P31-P32</f>
         <v>-33.215999999999994</v>
       </c>
-      <c r="O33" s="8">
+      <c r="Q33" s="8">
         <f t="shared" si="28"/>
         <v>53.322000000000024</v>
       </c>
-      <c r="P33" s="8">
-        <f>+P31-P32</f>
-        <v>80.599000000000089</v>
-      </c>
-      <c r="Q33" s="8">
-        <f>+Q31-Q32</f>
-        <v>114.61700000000005</v>
-      </c>
       <c r="R33" s="8">
         <f>+R31-R32</f>
-        <v>119.47900000000011</v>
+        <v>80.599000000000089</v>
       </c>
       <c r="S33" s="8">
         <f>+S31-S32</f>
+        <v>114.61700000000005</v>
+      </c>
+      <c r="T33" s="8">
+        <f>+T31-T32</f>
+        <v>119.47900000000011</v>
+      </c>
+      <c r="U33" s="8">
+        <f>+U31-U32</f>
         <v>135.03400000000013</v>
       </c>
-      <c r="T33" s="8"/>
-      <c r="U33" s="8"/>
       <c r="V33" s="8"/>
       <c r="W33" s="8"/>
       <c r="X33" s="8"/>
@@ -3906,8 +4064,10 @@
       <c r="BK33" s="8"/>
       <c r="BL33" s="8"/>
       <c r="BM33" s="8"/>
-    </row>
-    <row r="34" spans="2:65" x14ac:dyDescent="0.2">
+      <c r="BN33" s="8"/>
+      <c r="BO33" s="8"/>
+    </row>
+    <row r="34" spans="2:67" x14ac:dyDescent="0.2">
       <c r="C34" s="8"/>
       <c r="D34" s="8"/>
       <c r="E34" s="8"/>
@@ -3971,8 +4131,10 @@
       <c r="BK34" s="8"/>
       <c r="BL34" s="8"/>
       <c r="BM34" s="8"/>
-    </row>
-    <row r="35" spans="2:65" x14ac:dyDescent="0.2">
+      <c r="BN34" s="8"/>
+      <c r="BO34" s="8"/>
+    </row>
+    <row r="35" spans="2:67" x14ac:dyDescent="0.2">
       <c r="B35" s="2" t="s">
         <v>51</v>
       </c>
@@ -3989,7 +4151,7 @@
         <v>0.90879845229778977</v>
       </c>
       <c r="F35" s="7">
-        <f t="shared" ref="F35:I35" si="30">+F33/F36</f>
+        <f t="shared" ref="F35:K35" si="30">+F33/F36</f>
         <v>0.77719022089206724</v>
       </c>
       <c r="G35" s="7">
@@ -4000,46 +4162,52 @@
         <f t="shared" si="30"/>
         <v>0</v>
       </c>
-      <c r="I35" s="7" t="e">
+      <c r="I35" s="7">
+        <f t="shared" si="30"/>
+        <v>1.0784489271565394</v>
+      </c>
+      <c r="J35" s="7" t="e">
         <f t="shared" si="30"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="J35" s="7"/>
-      <c r="K35" s="8"/>
-      <c r="L35" s="7">
-        <f t="shared" ref="L35" si="31">+L33/L36</f>
+      <c r="K35" s="7">
+        <f t="shared" si="30"/>
+        <v>1.1205340926935847</v>
+      </c>
+      <c r="L35" s="7"/>
+      <c r="M35" s="8"/>
+      <c r="N35" s="7">
+        <f t="shared" ref="N35" si="31">+N33/N36</f>
         <v>0.74547058823529422</v>
       </c>
-      <c r="M35" s="7">
-        <f t="shared" ref="M35" si="32">+M33/M36</f>
+      <c r="O35" s="7">
+        <f t="shared" ref="O35" si="32">+O33/O36</f>
         <v>0.77283823529411722</v>
       </c>
-      <c r="N35" s="7">
-        <f t="shared" ref="N35" si="33">+N33/N36</f>
+      <c r="P35" s="7">
+        <f t="shared" ref="P35" si="33">+P33/P36</f>
         <v>-0.48847058823529405</v>
       </c>
-      <c r="O35" s="7">
-        <f t="shared" ref="O35" si="34">+O33/O36</f>
+      <c r="Q35" s="7">
+        <f t="shared" ref="Q35" si="34">+Q33/Q36</f>
         <v>0.78414705882352975</v>
       </c>
-      <c r="P35" s="7">
-        <f t="shared" ref="P35" si="35">+P33/P36</f>
+      <c r="R35" s="7">
+        <f t="shared" ref="R35" si="35">+R33/R36</f>
         <v>1.1852794117647072</v>
-      </c>
-      <c r="Q35" s="7">
-        <f>+Q33/Q36</f>
-        <v>1.6857645313595349</v>
-      </c>
-      <c r="R35" s="7">
-        <f>+R33/R36</f>
-        <v>1.7572738812070285</v>
       </c>
       <c r="S35" s="7">
         <f>+S33/S36</f>
+        <v>1.6857645313595349</v>
+      </c>
+      <c r="T35" s="7">
+        <f>+T33/T36</f>
+        <v>1.7572738812070285</v>
+      </c>
+      <c r="U35" s="7">
+        <f>+U33/U36</f>
         <v>1.98605379418065</v>
       </c>
-      <c r="T35" s="8"/>
-      <c r="U35" s="8"/>
       <c r="V35" s="8"/>
       <c r="W35" s="8"/>
       <c r="X35" s="8"/>
@@ -4084,8 +4252,10 @@
       <c r="BK35" s="8"/>
       <c r="BL35" s="8"/>
       <c r="BM35" s="8"/>
-    </row>
-    <row r="36" spans="2:65" x14ac:dyDescent="0.2">
+      <c r="BN35" s="8"/>
+      <c r="BO35" s="8"/>
+    </row>
+    <row r="36" spans="2:67" x14ac:dyDescent="0.2">
       <c r="B36" s="2" t="s">
         <v>2</v>
       </c>
@@ -4103,15 +4273,15 @@
       <c r="H36" s="8">
         <v>67.933676000000006</v>
       </c>
-      <c r="I36" s="8"/>
+      <c r="I36" s="8">
+        <v>67.933676000000006</v>
+      </c>
       <c r="J36" s="8"/>
-      <c r="K36" s="8"/>
-      <c r="L36" s="8">
-        <v>68</v>
-      </c>
-      <c r="M36" s="8">
-        <v>68</v>
-      </c>
+      <c r="K36" s="8">
+        <v>67.933676000000006</v>
+      </c>
+      <c r="L36" s="8"/>
+      <c r="M36" s="8"/>
       <c r="N36" s="8">
         <v>68</v>
       </c>
@@ -4122,16 +4292,20 @@
         <v>68</v>
       </c>
       <c r="Q36" s="8">
-        <v>67.991108999999994</v>
+        <v>68</v>
       </c>
       <c r="R36" s="8">
-        <v>67.991108999999994</v>
+        <v>68</v>
       </c>
       <c r="S36" s="8">
         <v>67.991108999999994</v>
       </c>
-      <c r="T36" s="8"/>
-      <c r="U36" s="8"/>
+      <c r="T36" s="8">
+        <v>67.991108999999994</v>
+      </c>
+      <c r="U36" s="8">
+        <v>67.991108999999994</v>
+      </c>
       <c r="V36" s="8"/>
       <c r="W36" s="8"/>
       <c r="X36" s="8"/>
@@ -4176,8 +4350,10 @@
       <c r="BK36" s="8"/>
       <c r="BL36" s="8"/>
       <c r="BM36" s="8"/>
-    </row>
-    <row r="37" spans="2:65" x14ac:dyDescent="0.2">
+      <c r="BN36" s="8"/>
+      <c r="BO36" s="8"/>
+    </row>
+    <row r="37" spans="2:67" x14ac:dyDescent="0.2">
       <c r="C37" s="8"/>
       <c r="D37" s="8"/>
       <c r="E37" s="8"/>
@@ -4241,8 +4417,10 @@
       <c r="BK37" s="8"/>
       <c r="BL37" s="8"/>
       <c r="BM37" s="8"/>
-    </row>
-    <row r="38" spans="2:65" x14ac:dyDescent="0.2">
+      <c r="BN37" s="8"/>
+      <c r="BO37" s="8"/>
+    </row>
+    <row r="38" spans="2:67" x14ac:dyDescent="0.2">
       <c r="B38" s="2" t="s">
         <v>54</v>
       </c>
@@ -4256,36 +4434,36 @@
       <c r="J38" s="8"/>
       <c r="K38" s="8"/>
       <c r="L38" s="8"/>
-      <c r="M38" s="10">
-        <f t="shared" ref="M38:P38" si="36">+M7/L7-1</f>
+      <c r="M38" s="8"/>
+      <c r="N38" s="8"/>
+      <c r="O38" s="10">
+        <f t="shared" ref="O38:R38" si="36">+O7/N7-1</f>
         <v>7.0866141732283561E-2</v>
       </c>
-      <c r="N38" s="10">
+      <c r="P38" s="10">
         <f t="shared" si="36"/>
         <v>1.4705882352941124E-2</v>
       </c>
-      <c r="O38" s="10">
+      <c r="Q38" s="10">
         <f t="shared" si="36"/>
         <v>4.3478260869565188E-2</v>
       </c>
-      <c r="P38" s="10">
+      <c r="R38" s="10">
         <f t="shared" si="36"/>
         <v>3.4722222222222321E-2</v>
       </c>
-      <c r="Q38" s="10">
-        <f>+Q7/P7-1</f>
+      <c r="S38" s="10">
+        <f>+S7/R7-1</f>
         <v>2.0134228187919545E-2</v>
       </c>
-      <c r="R38" s="10">
-        <f>+R7/Q7-1</f>
+      <c r="T38" s="10">
+        <f>+T7/S7-1</f>
         <v>-1</v>
       </c>
-      <c r="S38" s="10" t="e">
-        <f>+S7/R7-1</f>
+      <c r="U38" s="10" t="e">
+        <f>+U7/T7-1</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="T38" s="8"/>
-      <c r="U38" s="8"/>
       <c r="V38" s="8"/>
       <c r="W38" s="8"/>
       <c r="X38" s="8"/>
@@ -4330,8 +4508,10 @@
       <c r="BK38" s="8"/>
       <c r="BL38" s="8"/>
       <c r="BM38" s="8"/>
-    </row>
-    <row r="39" spans="2:65" x14ac:dyDescent="0.2">
+      <c r="BN38" s="8"/>
+      <c r="BO38" s="8"/>
+    </row>
+    <row r="39" spans="2:67" x14ac:dyDescent="0.2">
       <c r="B39" s="2" t="s">
         <v>55</v>
       </c>
@@ -4345,36 +4525,36 @@
       <c r="J39" s="8"/>
       <c r="K39" s="8"/>
       <c r="L39" s="8"/>
-      <c r="M39" s="10">
-        <f t="shared" ref="M39:P42" si="37">+M10/L10-1</f>
+      <c r="M39" s="8"/>
+      <c r="N39" s="8"/>
+      <c r="O39" s="10">
+        <f t="shared" ref="O39:R42" si="37">+O10/N10-1</f>
         <v>8.0589101260178264E-2</v>
       </c>
-      <c r="N39" s="10">
+      <c r="P39" s="10">
         <f t="shared" si="37"/>
         <v>-2.1605426794799376E-2</v>
       </c>
-      <c r="O39" s="10">
+      <c r="Q39" s="10">
         <f t="shared" si="37"/>
         <v>0.26619212147124416</v>
       </c>
-      <c r="P39" s="10">
+      <c r="R39" s="10">
         <f t="shared" si="37"/>
         <v>0.20380561259411367</v>
       </c>
-      <c r="Q39" s="10">
-        <f>+Q10/P10-1</f>
-        <v>0.13481468003972474</v>
-      </c>
-      <c r="R39" s="10">
-        <f>+R10/Q10-1</f>
-        <v>5.4399091455675119E-2</v>
-      </c>
       <c r="S39" s="10">
         <f>+S10/R10-1</f>
+        <v>0.13481468003972474</v>
+      </c>
+      <c r="T39" s="10">
+        <f>+T10/S10-1</f>
+        <v>5.4399091455675119E-2</v>
+      </c>
+      <c r="U39" s="10">
+        <f>+U10/T10-1</f>
         <v>0.56785969980929218</v>
       </c>
-      <c r="T39" s="8"/>
-      <c r="U39" s="8"/>
       <c r="V39" s="8"/>
       <c r="W39" s="8"/>
       <c r="X39" s="8"/>
@@ -4419,8 +4599,10 @@
       <c r="BK39" s="8"/>
       <c r="BL39" s="8"/>
       <c r="BM39" s="8"/>
-    </row>
-    <row r="40" spans="2:65" x14ac:dyDescent="0.2">
+      <c r="BN39" s="8"/>
+      <c r="BO39" s="8"/>
+    </row>
+    <row r="40" spans="2:67" x14ac:dyDescent="0.2">
       <c r="B40" s="2" t="s">
         <v>56</v>
       </c>
@@ -4434,36 +4616,36 @@
       <c r="J40" s="8"/>
       <c r="K40" s="8"/>
       <c r="L40" s="8"/>
-      <c r="M40" s="10">
+      <c r="M40" s="8"/>
+      <c r="N40" s="8"/>
+      <c r="O40" s="10">
         <f t="shared" si="37"/>
         <v>1.700294717751083E-2</v>
       </c>
-      <c r="N40" s="10">
+      <c r="P40" s="10">
         <f t="shared" si="37"/>
         <v>-0.23848640213999117</v>
       </c>
-      <c r="O40" s="10">
+      <c r="Q40" s="10">
         <f t="shared" si="37"/>
         <v>0.2327181183496041</v>
       </c>
-      <c r="P40" s="10">
+      <c r="R40" s="10">
         <f t="shared" si="37"/>
         <v>0.22001116084679961</v>
       </c>
-      <c r="Q40" s="10">
-        <f t="shared" ref="Q40:S42" si="38">+Q11/P11-1</f>
+      <c r="S40" s="10">
+        <f t="shared" ref="S40:U42" si="38">+S11/R11-1</f>
         <v>0.25399745019610132</v>
       </c>
-      <c r="R40" s="10">
+      <c r="T40" s="10">
         <f t="shared" si="38"/>
         <v>9.3665600844379471E-2</v>
       </c>
-      <c r="S40" s="10">
+      <c r="U40" s="10">
         <f t="shared" si="38"/>
         <v>-1</v>
       </c>
-      <c r="T40" s="8"/>
-      <c r="U40" s="8"/>
       <c r="V40" s="8"/>
       <c r="W40" s="8"/>
       <c r="X40" s="8"/>
@@ -4508,8 +4690,10 @@
       <c r="BK40" s="8"/>
       <c r="BL40" s="8"/>
       <c r="BM40" s="8"/>
-    </row>
-    <row r="41" spans="2:65" x14ac:dyDescent="0.2">
+      <c r="BN40" s="8"/>
+      <c r="BO40" s="8"/>
+    </row>
+    <row r="41" spans="2:67" x14ac:dyDescent="0.2">
       <c r="B41" s="2" t="s">
         <v>57</v>
       </c>
@@ -4523,36 +4707,36 @@
       <c r="J41" s="8"/>
       <c r="K41" s="8"/>
       <c r="L41" s="8"/>
-      <c r="M41" s="10">
+      <c r="M41" s="8"/>
+      <c r="N41" s="8"/>
+      <c r="O41" s="10">
         <f t="shared" si="37"/>
         <v>9.8976692516396403E-2</v>
       </c>
-      <c r="N41" s="10">
+      <c r="P41" s="10">
         <f t="shared" si="37"/>
         <v>-0.15321138369425769</v>
       </c>
-      <c r="O41" s="10">
+      <c r="Q41" s="10">
         <f t="shared" si="37"/>
         <v>0.36728228555686915</v>
       </c>
-      <c r="P41" s="10">
+      <c r="R41" s="10">
         <f t="shared" si="37"/>
         <v>0.4048682410026947</v>
       </c>
-      <c r="Q41" s="10">
+      <c r="S41" s="10">
         <f t="shared" si="38"/>
         <v>0.20842981478548994</v>
       </c>
-      <c r="R41" s="10">
+      <c r="T41" s="10">
         <f t="shared" si="38"/>
         <v>0.17828029462014139</v>
       </c>
-      <c r="S41" s="10">
+      <c r="U41" s="10">
         <f t="shared" si="38"/>
         <v>9.2179562236784918E-2</v>
       </c>
-      <c r="T41" s="8"/>
-      <c r="U41" s="8"/>
       <c r="V41" s="8"/>
       <c r="W41" s="8"/>
       <c r="X41" s="8"/>
@@ -4597,8 +4781,10 @@
       <c r="BK41" s="8"/>
       <c r="BL41" s="8"/>
       <c r="BM41" s="8"/>
-    </row>
-    <row r="42" spans="2:65" x14ac:dyDescent="0.2">
+      <c r="BN41" s="8"/>
+      <c r="BO41" s="8"/>
+    </row>
+    <row r="42" spans="2:67" x14ac:dyDescent="0.2">
       <c r="B42" s="2" t="s">
         <v>58</v>
       </c>
@@ -4612,36 +4798,36 @@
       <c r="J42" s="8"/>
       <c r="K42" s="8"/>
       <c r="L42" s="8"/>
-      <c r="M42" s="10">
+      <c r="M42" s="8"/>
+      <c r="N42" s="8"/>
+      <c r="O42" s="10">
         <f t="shared" si="37"/>
         <v>0.18922456581132008</v>
       </c>
-      <c r="N42" s="10">
+      <c r="P42" s="10">
         <f t="shared" si="37"/>
         <v>-5.1731142842368794E-2</v>
       </c>
-      <c r="O42" s="10">
+      <c r="Q42" s="10">
         <f t="shared" si="37"/>
         <v>0.32872166394017288</v>
       </c>
-      <c r="P42" s="10">
+      <c r="R42" s="10">
         <f t="shared" si="37"/>
         <v>0.2807091599831153</v>
       </c>
-      <c r="Q42" s="10">
+      <c r="S42" s="10">
         <f t="shared" si="38"/>
         <v>0.40415568007031433</v>
       </c>
-      <c r="R42" s="10">
+      <c r="T42" s="10">
         <f t="shared" si="38"/>
         <v>0.12603387288701962</v>
       </c>
-      <c r="S42" s="10">
+      <c r="U42" s="10">
         <f t="shared" si="38"/>
         <v>0.13650787216917482</v>
       </c>
-      <c r="T42" s="8"/>
-      <c r="U42" s="8"/>
       <c r="V42" s="8"/>
       <c r="W42" s="8"/>
       <c r="X42" s="8"/>
@@ -4686,8 +4872,10 @@
       <c r="BK42" s="8"/>
       <c r="BL42" s="8"/>
       <c r="BM42" s="8"/>
-    </row>
-    <row r="43" spans="2:65" x14ac:dyDescent="0.2">
+      <c r="BN42" s="8"/>
+      <c r="BO42" s="8"/>
+    </row>
+    <row r="43" spans="2:67" x14ac:dyDescent="0.2">
       <c r="B43" s="5" t="s">
         <v>63</v>
       </c>
@@ -4714,41 +4902,44 @@
         <v>0.10226661210127252</v>
       </c>
       <c r="J43" s="11" t="e">
-        <f t="shared" ref="J43" si="42">+J16/H16-1</f>
+        <f t="shared" ref="J43:K43" si="42">+J16/H16-1</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="K43" s="9"/>
-      <c r="L43" s="9"/>
-      <c r="M43" s="11">
-        <f t="shared" ref="M43:Q43" si="43">+M16/L16-1</f>
+      <c r="K43" s="11">
+        <f t="shared" si="42"/>
+        <v>9.5413916843897661E-2</v>
+      </c>
+      <c r="L43" s="11"/>
+      <c r="M43" s="9"/>
+      <c r="N43" s="9"/>
+      <c r="O43" s="11">
+        <f t="shared" ref="O43:S43" si="43">+O16/N16-1</f>
         <v>9.9033266063407233E-2</v>
       </c>
-      <c r="N43" s="11">
+      <c r="P43" s="11">
         <f t="shared" si="43"/>
         <v>-0.10488991560827354</v>
       </c>
-      <c r="O43" s="11">
+      <c r="Q43" s="11">
         <f t="shared" si="43"/>
         <v>0.30912128938095229</v>
       </c>
-      <c r="P43" s="11">
+      <c r="R43" s="11">
         <f t="shared" si="43"/>
         <v>0.29140005532317015</v>
       </c>
-      <c r="Q43" s="11">
+      <c r="S43" s="11">
         <f t="shared" si="43"/>
         <v>0.23889321393311791</v>
       </c>
-      <c r="R43" s="11">
-        <f>+R16/Q16-1</f>
+      <c r="T43" s="11">
+        <f>+T16/S16-1</f>
         <v>0.12209720735110841</v>
       </c>
-      <c r="S43" s="11">
-        <f>+S16/R16-1</f>
+      <c r="U43" s="11">
+        <f>+U16/T16-1</f>
         <v>0.10121779529776154</v>
       </c>
-      <c r="T43" s="8"/>
-      <c r="U43" s="8"/>
       <c r="V43" s="8"/>
       <c r="W43" s="8"/>
       <c r="X43" s="8"/>
@@ -4793,8 +4984,10 @@
       <c r="BK43" s="8"/>
       <c r="BL43" s="8"/>
       <c r="BM43" s="8"/>
-    </row>
-    <row r="44" spans="2:65" x14ac:dyDescent="0.2">
+      <c r="BN43" s="8"/>
+      <c r="BO43" s="8"/>
+    </row>
+    <row r="44" spans="2:67" x14ac:dyDescent="0.2">
       <c r="B44" s="2" t="s">
         <v>61</v>
       </c>
@@ -4827,44 +5020,47 @@
         <v>0.91466011825151461</v>
       </c>
       <c r="J44" s="10" t="e">
-        <f t="shared" si="44"/>
+        <f t="shared" ref="J44:K44" si="45">+J18/J16</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="K44" s="8"/>
-      <c r="L44" s="10">
-        <f t="shared" ref="L44:P44" si="45">+L18/L16</f>
+      <c r="K44" s="10">
+        <f t="shared" si="45"/>
+        <v>0.90850547963667461</v>
+      </c>
+      <c r="L44" s="10"/>
+      <c r="M44" s="8"/>
+      <c r="N44" s="10">
+        <f t="shared" ref="N44:R44" si="46">+N18/N16</f>
         <v>0.84076557515786732</v>
       </c>
-      <c r="M44" s="10">
-        <f t="shared" si="45"/>
+      <c r="O44" s="10">
+        <f t="shared" si="46"/>
         <v>0.88107331664914335</v>
       </c>
-      <c r="N44" s="10">
-        <f t="shared" si="45"/>
+      <c r="P44" s="10">
+        <f t="shared" si="46"/>
         <v>0.90124316882133326</v>
       </c>
-      <c r="O44" s="10">
-        <f t="shared" si="45"/>
+      <c r="Q44" s="10">
+        <f t="shared" si="46"/>
         <v>0.8404754984350844</v>
       </c>
-      <c r="P44" s="10">
-        <f t="shared" si="45"/>
+      <c r="R44" s="10">
+        <f t="shared" si="46"/>
         <v>0.89612246495626868</v>
-      </c>
-      <c r="Q44" s="10">
-        <f>+Q18/Q16</f>
-        <v>0.8996480665601797</v>
-      </c>
-      <c r="R44" s="10">
-        <f>+R18/R16</f>
-        <v>0.92037793107763544</v>
       </c>
       <c r="S44" s="10">
         <f>+S18/S16</f>
+        <v>0.8996480665601797</v>
+      </c>
+      <c r="T44" s="10">
+        <f>+T18/T16</f>
+        <v>0.92037793107763544</v>
+      </c>
+      <c r="U44" s="10">
+        <f>+U18/U16</f>
         <v>0.9139891942262196</v>
       </c>
-      <c r="T44" s="8"/>
-      <c r="U44" s="8"/>
       <c r="V44" s="8"/>
       <c r="W44" s="8"/>
       <c r="X44" s="8"/>
@@ -4909,78 +5105,83 @@
       <c r="BK44" s="8"/>
       <c r="BL44" s="8"/>
       <c r="BM44" s="8"/>
-    </row>
-    <row r="45" spans="2:65" x14ac:dyDescent="0.2">
+      <c r="BN44" s="8"/>
+      <c r="BO44" s="8"/>
+    </row>
+    <row r="45" spans="2:67" x14ac:dyDescent="0.2">
       <c r="B45" s="2" t="s">
         <v>59</v>
       </c>
       <c r="C45" s="10" t="e">
-        <f t="shared" ref="C45:J45" si="46">+C26/C16</f>
+        <f t="shared" ref="C45:J45" si="47">+C26/C16</f>
         <v>#DIV/0!</v>
       </c>
       <c r="D45" s="10" t="e">
-        <f t="shared" si="46"/>
+        <f t="shared" si="47"/>
         <v>#DIV/0!</v>
       </c>
       <c r="E45" s="10">
-        <f t="shared" si="46"/>
+        <f t="shared" si="47"/>
         <v>0.16121755628357434</v>
       </c>
       <c r="F45" s="10">
-        <f t="shared" si="46"/>
+        <f t="shared" si="47"/>
         <v>0.16745035081060924</v>
       </c>
       <c r="G45" s="10">
-        <f t="shared" si="46"/>
+        <f t="shared" si="47"/>
         <v>0.16850878578034431</v>
       </c>
       <c r="H45" s="10" t="e">
-        <f t="shared" si="46"/>
+        <f t="shared" si="47"/>
         <v>#DIV/0!</v>
       </c>
       <c r="I45" s="10">
-        <f t="shared" si="46"/>
+        <f t="shared" si="47"/>
         <v>0.1663955213517799</v>
       </c>
       <c r="J45" s="10" t="e">
-        <f t="shared" si="46"/>
+        <f t="shared" ref="J45:K45" si="48">+J26/J16</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="K45" s="8"/>
-      <c r="L45" s="10">
-        <f t="shared" ref="L45:P45" si="47">+L26/L16</f>
+      <c r="K45" s="10">
+        <f t="shared" si="48"/>
+        <v>0.1710663441022349</v>
+      </c>
+      <c r="L45" s="10"/>
+      <c r="M45" s="8"/>
+      <c r="N45" s="10">
+        <f t="shared" ref="N45:R45" si="49">+N26/N16</f>
         <v>0.12574774501081384</v>
       </c>
-      <c r="M45" s="10">
-        <f t="shared" si="47"/>
+      <c r="O45" s="10">
+        <f t="shared" si="49"/>
         <v>0.13718550548653169</v>
       </c>
-      <c r="N45" s="10">
-        <f t="shared" si="47"/>
+      <c r="P45" s="10">
+        <f t="shared" si="49"/>
         <v>-2.7238319672507807E-2</v>
       </c>
-      <c r="O45" s="10">
-        <f t="shared" si="47"/>
+      <c r="Q45" s="10">
+        <f t="shared" si="49"/>
         <v>0.10816943493138666</v>
       </c>
-      <c r="P45" s="10">
-        <f t="shared" si="47"/>
+      <c r="R45" s="10">
+        <f t="shared" si="49"/>
         <v>0.14614638559194884</v>
-      </c>
-      <c r="Q45" s="10">
-        <f>+Q26/Q16</f>
-        <v>0.16447490828667219</v>
-      </c>
-      <c r="R45" s="10">
-        <f>+R26/R16</f>
-        <v>0.16555680698296504</v>
       </c>
       <c r="S45" s="10">
         <f>+S26/S16</f>
+        <v>0.16447490828667219</v>
+      </c>
+      <c r="T45" s="10">
+        <f>+T26/T16</f>
+        <v>0.16555680698296504</v>
+      </c>
+      <c r="U45" s="10">
+        <f>+U26/U16</f>
         <v>0.16178403935932439</v>
       </c>
-      <c r="T45" s="8"/>
-      <c r="U45" s="8"/>
       <c r="V45" s="8"/>
       <c r="W45" s="8"/>
       <c r="X45" s="8"/>
@@ -5025,78 +5226,83 @@
       <c r="BK45" s="8"/>
       <c r="BL45" s="8"/>
       <c r="BM45" s="8"/>
-    </row>
-    <row r="46" spans="2:65" x14ac:dyDescent="0.2">
+      <c r="BN45" s="8"/>
+      <c r="BO45" s="8"/>
+    </row>
+    <row r="46" spans="2:67" x14ac:dyDescent="0.2">
       <c r="B46" s="2" t="s">
         <v>60</v>
       </c>
       <c r="C46" s="10" t="e">
-        <f t="shared" ref="C46:J46" si="48">+C30/C29</f>
+        <f t="shared" ref="C46:J46" si="50">+C30/C29</f>
         <v>#DIV/0!</v>
       </c>
       <c r="D46" s="10" t="e">
-        <f t="shared" si="48"/>
+        <f t="shared" si="50"/>
         <v>#DIV/0!</v>
       </c>
       <c r="E46" s="10">
-        <f t="shared" si="48"/>
+        <f t="shared" si="50"/>
         <v>0.21787624319759807</v>
       </c>
       <c r="F46" s="10">
-        <f t="shared" si="48"/>
+        <f t="shared" si="50"/>
         <v>0.35145384152502929</v>
       </c>
       <c r="G46" s="10">
-        <f t="shared" si="48"/>
+        <f t="shared" si="50"/>
         <v>0.30625636502986958</v>
       </c>
       <c r="H46" s="10" t="e">
-        <f t="shared" si="48"/>
+        <f t="shared" si="50"/>
         <v>#DIV/0!</v>
       </c>
       <c r="I46" s="10">
-        <f t="shared" si="48"/>
+        <f t="shared" si="50"/>
         <v>0.28602034352993788</v>
       </c>
       <c r="J46" s="10" t="e">
-        <f t="shared" si="48"/>
+        <f t="shared" ref="J46:K46" si="51">+J30/J29</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="K46" s="8"/>
-      <c r="L46" s="10">
-        <f t="shared" ref="L46:P46" si="49">+L30/L29</f>
+      <c r="K46" s="10">
+        <f t="shared" si="51"/>
+        <v>0.28800699523631706</v>
+      </c>
+      <c r="L46" s="10"/>
+      <c r="M46" s="8"/>
+      <c r="N46" s="10">
+        <f t="shared" ref="N46:R46" si="52">+N30/N29</f>
         <v>0.21813057198002508</v>
       </c>
-      <c r="M46" s="10">
-        <f t="shared" si="49"/>
+      <c r="O46" s="10">
+        <f t="shared" si="52"/>
         <v>0.23263848733664863</v>
       </c>
-      <c r="N46" s="10">
-        <f t="shared" si="49"/>
+      <c r="P46" s="10">
+        <f t="shared" si="52"/>
         <v>5.0707477354804339E-2</v>
       </c>
-      <c r="O46" s="10">
-        <f t="shared" si="49"/>
+      <c r="Q46" s="10">
+        <f t="shared" si="52"/>
         <v>0.12074782119763841</v>
       </c>
-      <c r="P46" s="10">
-        <f t="shared" si="49"/>
+      <c r="R46" s="10">
+        <f t="shared" si="52"/>
         <v>0.29654666161155774</v>
-      </c>
-      <c r="Q46" s="10">
-        <f>+Q30/Q29</f>
-        <v>0.28574889956790367</v>
-      </c>
-      <c r="R46" s="10">
-        <f>+R30/R29</f>
-        <v>0.2849941859494704</v>
       </c>
       <c r="S46" s="10">
         <f>+S30/S29</f>
+        <v>0.28574889956790367</v>
+      </c>
+      <c r="T46" s="10">
+        <f>+T30/T29</f>
+        <v>0.2849941859494704</v>
+      </c>
+      <c r="U46" s="10">
+        <f>+U30/U29</f>
         <v>0.28539578048878667</v>
       </c>
-      <c r="T46" s="8"/>
-      <c r="U46" s="8"/>
       <c r="V46" s="8"/>
       <c r="W46" s="8"/>
       <c r="X46" s="8"/>
@@ -5141,8 +5347,10 @@
       <c r="BK46" s="8"/>
       <c r="BL46" s="8"/>
       <c r="BM46" s="8"/>
-    </row>
-    <row r="47" spans="2:65" x14ac:dyDescent="0.2">
+      <c r="BN46" s="8"/>
+      <c r="BO46" s="8"/>
+    </row>
+    <row r="47" spans="2:67" x14ac:dyDescent="0.2">
       <c r="C47" s="8"/>
       <c r="D47" s="8"/>
       <c r="E47" s="8"/>
@@ -5206,8 +5414,10 @@
       <c r="BK47" s="8"/>
       <c r="BL47" s="8"/>
       <c r="BM47" s="8"/>
-    </row>
-    <row r="48" spans="2:65" x14ac:dyDescent="0.2">
+      <c r="BN47" s="8"/>
+      <c r="BO47" s="8"/>
+    </row>
+    <row r="48" spans="2:67" x14ac:dyDescent="0.2">
       <c r="C48" s="8"/>
       <c r="D48" s="8"/>
       <c r="E48" s="8"/>
@@ -5271,8 +5481,10 @@
       <c r="BK48" s="8"/>
       <c r="BL48" s="8"/>
       <c r="BM48" s="8"/>
-    </row>
-    <row r="49" spans="3:65" x14ac:dyDescent="0.2">
+      <c r="BN48" s="8"/>
+      <c r="BO48" s="8"/>
+    </row>
+    <row r="49" spans="3:67" x14ac:dyDescent="0.2">
       <c r="C49" s="8"/>
       <c r="D49" s="8"/>
       <c r="E49" s="8"/>
@@ -5336,8 +5548,10 @@
       <c r="BK49" s="8"/>
       <c r="BL49" s="8"/>
       <c r="BM49" s="8"/>
-    </row>
-    <row r="50" spans="3:65" x14ac:dyDescent="0.2">
+      <c r="BN49" s="8"/>
+      <c r="BO49" s="8"/>
+    </row>
+    <row r="50" spans="3:67" x14ac:dyDescent="0.2">
       <c r="C50" s="8"/>
       <c r="D50" s="8"/>
       <c r="E50" s="8"/>
@@ -5401,8 +5615,10 @@
       <c r="BK50" s="8"/>
       <c r="BL50" s="8"/>
       <c r="BM50" s="8"/>
-    </row>
-    <row r="51" spans="3:65" x14ac:dyDescent="0.2">
+      <c r="BN50" s="8"/>
+      <c r="BO50" s="8"/>
+    </row>
+    <row r="51" spans="3:67" x14ac:dyDescent="0.2">
       <c r="C51" s="8"/>
       <c r="D51" s="8"/>
       <c r="E51" s="8"/>
@@ -5466,8 +5682,10 @@
       <c r="BK51" s="8"/>
       <c r="BL51" s="8"/>
       <c r="BM51" s="8"/>
-    </row>
-    <row r="52" spans="3:65" x14ac:dyDescent="0.2">
+      <c r="BN51" s="8"/>
+      <c r="BO51" s="8"/>
+    </row>
+    <row r="52" spans="3:67" x14ac:dyDescent="0.2">
       <c r="C52" s="8"/>
       <c r="D52" s="8"/>
       <c r="E52" s="8"/>
@@ -5531,8 +5749,10 @@
       <c r="BK52" s="8"/>
       <c r="BL52" s="8"/>
       <c r="BM52" s="8"/>
-    </row>
-    <row r="53" spans="3:65" x14ac:dyDescent="0.2">
+      <c r="BN52" s="8"/>
+      <c r="BO52" s="8"/>
+    </row>
+    <row r="53" spans="3:67" x14ac:dyDescent="0.2">
       <c r="C53" s="8"/>
       <c r="D53" s="8"/>
       <c r="E53" s="8"/>
@@ -5596,8 +5816,10 @@
       <c r="BK53" s="8"/>
       <c r="BL53" s="8"/>
       <c r="BM53" s="8"/>
-    </row>
-    <row r="54" spans="3:65" x14ac:dyDescent="0.2">
+      <c r="BN53" s="8"/>
+      <c r="BO53" s="8"/>
+    </row>
+    <row r="54" spans="3:67" x14ac:dyDescent="0.2">
       <c r="C54" s="8"/>
       <c r="D54" s="8"/>
       <c r="E54" s="8"/>
@@ -5661,8 +5883,10 @@
       <c r="BK54" s="8"/>
       <c r="BL54" s="8"/>
       <c r="BM54" s="8"/>
-    </row>
-    <row r="55" spans="3:65" x14ac:dyDescent="0.2">
+      <c r="BN54" s="8"/>
+      <c r="BO54" s="8"/>
+    </row>
+    <row r="55" spans="3:67" x14ac:dyDescent="0.2">
       <c r="C55" s="8"/>
       <c r="D55" s="8"/>
       <c r="E55" s="8"/>
@@ -5726,8 +5950,10 @@
       <c r="BK55" s="8"/>
       <c r="BL55" s="8"/>
       <c r="BM55" s="8"/>
-    </row>
-    <row r="56" spans="3:65" x14ac:dyDescent="0.2">
+      <c r="BN55" s="8"/>
+      <c r="BO55" s="8"/>
+    </row>
+    <row r="56" spans="3:67" x14ac:dyDescent="0.2">
       <c r="C56" s="8"/>
       <c r="D56" s="8"/>
       <c r="E56" s="8"/>
@@ -5791,8 +6017,10 @@
       <c r="BK56" s="8"/>
       <c r="BL56" s="8"/>
       <c r="BM56" s="8"/>
-    </row>
-    <row r="57" spans="3:65" x14ac:dyDescent="0.2">
+      <c r="BN56" s="8"/>
+      <c r="BO56" s="8"/>
+    </row>
+    <row r="57" spans="3:67" x14ac:dyDescent="0.2">
       <c r="C57" s="8"/>
       <c r="D57" s="8"/>
       <c r="E57" s="8"/>
@@ -5856,8 +6084,10 @@
       <c r="BK57" s="8"/>
       <c r="BL57" s="8"/>
       <c r="BM57" s="8"/>
-    </row>
-    <row r="58" spans="3:65" x14ac:dyDescent="0.2">
+      <c r="BN57" s="8"/>
+      <c r="BO57" s="8"/>
+    </row>
+    <row r="58" spans="3:67" x14ac:dyDescent="0.2">
       <c r="C58" s="8"/>
       <c r="D58" s="8"/>
       <c r="E58" s="8"/>
@@ -5921,8 +6151,10 @@
       <c r="BK58" s="8"/>
       <c r="BL58" s="8"/>
       <c r="BM58" s="8"/>
-    </row>
-    <row r="59" spans="3:65" x14ac:dyDescent="0.2">
+      <c r="BN58" s="8"/>
+      <c r="BO58" s="8"/>
+    </row>
+    <row r="59" spans="3:67" x14ac:dyDescent="0.2">
       <c r="C59" s="8"/>
       <c r="D59" s="8"/>
       <c r="E59" s="8"/>
@@ -5986,8 +6218,10 @@
       <c r="BK59" s="8"/>
       <c r="BL59" s="8"/>
       <c r="BM59" s="8"/>
-    </row>
-    <row r="60" spans="3:65" x14ac:dyDescent="0.2">
+      <c r="BN59" s="8"/>
+      <c r="BO59" s="8"/>
+    </row>
+    <row r="60" spans="3:67" x14ac:dyDescent="0.2">
       <c r="C60" s="8"/>
       <c r="D60" s="8"/>
       <c r="E60" s="8"/>
@@ -6051,8 +6285,10 @@
       <c r="BK60" s="8"/>
       <c r="BL60" s="8"/>
       <c r="BM60" s="8"/>
-    </row>
-    <row r="61" spans="3:65" x14ac:dyDescent="0.2">
+      <c r="BN60" s="8"/>
+      <c r="BO60" s="8"/>
+    </row>
+    <row r="61" spans="3:67" x14ac:dyDescent="0.2">
       <c r="C61" s="8"/>
       <c r="D61" s="8"/>
       <c r="E61" s="8"/>
@@ -6116,8 +6352,10 @@
       <c r="BK61" s="8"/>
       <c r="BL61" s="8"/>
       <c r="BM61" s="8"/>
-    </row>
-    <row r="62" spans="3:65" x14ac:dyDescent="0.2">
+      <c r="BN61" s="8"/>
+      <c r="BO61" s="8"/>
+    </row>
+    <row r="62" spans="3:67" x14ac:dyDescent="0.2">
       <c r="C62" s="8"/>
       <c r="D62" s="8"/>
       <c r="E62" s="8"/>
@@ -6181,8 +6419,10 @@
       <c r="BK62" s="8"/>
       <c r="BL62" s="8"/>
       <c r="BM62" s="8"/>
-    </row>
-    <row r="63" spans="3:65" x14ac:dyDescent="0.2">
+      <c r="BN62" s="8"/>
+      <c r="BO62" s="8"/>
+    </row>
+    <row r="63" spans="3:67" x14ac:dyDescent="0.2">
       <c r="C63" s="8"/>
       <c r="D63" s="8"/>
       <c r="E63" s="8"/>
@@ -6246,8 +6486,10 @@
       <c r="BK63" s="8"/>
       <c r="BL63" s="8"/>
       <c r="BM63" s="8"/>
-    </row>
-    <row r="64" spans="3:65" x14ac:dyDescent="0.2">
+      <c r="BN63" s="8"/>
+      <c r="BO63" s="8"/>
+    </row>
+    <row r="64" spans="3:67" x14ac:dyDescent="0.2">
       <c r="C64" s="8"/>
       <c r="D64" s="8"/>
       <c r="E64" s="8"/>
@@ -6311,8 +6553,10 @@
       <c r="BK64" s="8"/>
       <c r="BL64" s="8"/>
       <c r="BM64" s="8"/>
-    </row>
-    <row r="65" spans="3:65" x14ac:dyDescent="0.2">
+      <c r="BN64" s="8"/>
+      <c r="BO64" s="8"/>
+    </row>
+    <row r="65" spans="3:67" x14ac:dyDescent="0.2">
       <c r="C65" s="8"/>
       <c r="D65" s="8"/>
       <c r="E65" s="8"/>
@@ -6376,8 +6620,10 @@
       <c r="BK65" s="8"/>
       <c r="BL65" s="8"/>
       <c r="BM65" s="8"/>
-    </row>
-    <row r="66" spans="3:65" x14ac:dyDescent="0.2">
+      <c r="BN65" s="8"/>
+      <c r="BO65" s="8"/>
+    </row>
+    <row r="66" spans="3:67" x14ac:dyDescent="0.2">
       <c r="C66" s="8"/>
       <c r="D66" s="8"/>
       <c r="E66" s="8"/>
@@ -6441,8 +6687,10 @@
       <c r="BK66" s="8"/>
       <c r="BL66" s="8"/>
       <c r="BM66" s="8"/>
-    </row>
-    <row r="67" spans="3:65" x14ac:dyDescent="0.2">
+      <c r="BN66" s="8"/>
+      <c r="BO66" s="8"/>
+    </row>
+    <row r="67" spans="3:67" x14ac:dyDescent="0.2">
       <c r="C67" s="8"/>
       <c r="D67" s="8"/>
       <c r="E67" s="8"/>
@@ -6506,8 +6754,10 @@
       <c r="BK67" s="8"/>
       <c r="BL67" s="8"/>
       <c r="BM67" s="8"/>
-    </row>
-    <row r="68" spans="3:65" x14ac:dyDescent="0.2">
+      <c r="BN67" s="8"/>
+      <c r="BO67" s="8"/>
+    </row>
+    <row r="68" spans="3:67" x14ac:dyDescent="0.2">
       <c r="C68" s="8"/>
       <c r="D68" s="8"/>
       <c r="E68" s="8"/>
@@ -6571,8 +6821,10 @@
       <c r="BK68" s="8"/>
       <c r="BL68" s="8"/>
       <c r="BM68" s="8"/>
-    </row>
-    <row r="69" spans="3:65" x14ac:dyDescent="0.2">
+      <c r="BN68" s="8"/>
+      <c r="BO68" s="8"/>
+    </row>
+    <row r="69" spans="3:67" x14ac:dyDescent="0.2">
       <c r="C69" s="8"/>
       <c r="D69" s="8"/>
       <c r="E69" s="8"/>
@@ -6636,8 +6888,10 @@
       <c r="BK69" s="8"/>
       <c r="BL69" s="8"/>
       <c r="BM69" s="8"/>
-    </row>
-    <row r="70" spans="3:65" x14ac:dyDescent="0.2">
+      <c r="BN69" s="8"/>
+      <c r="BO69" s="8"/>
+    </row>
+    <row r="70" spans="3:67" x14ac:dyDescent="0.2">
       <c r="C70" s="8"/>
       <c r="D70" s="8"/>
       <c r="E70" s="8"/>
@@ -6701,8 +6955,10 @@
       <c r="BK70" s="8"/>
       <c r="BL70" s="8"/>
       <c r="BM70" s="8"/>
-    </row>
-    <row r="71" spans="3:65" x14ac:dyDescent="0.2">
+      <c r="BN70" s="8"/>
+      <c r="BO70" s="8"/>
+    </row>
+    <row r="71" spans="3:67" x14ac:dyDescent="0.2">
       <c r="C71" s="8"/>
       <c r="D71" s="8"/>
       <c r="E71" s="8"/>
@@ -6766,8 +7022,10 @@
       <c r="BK71" s="8"/>
       <c r="BL71" s="8"/>
       <c r="BM71" s="8"/>
-    </row>
-    <row r="72" spans="3:65" x14ac:dyDescent="0.2">
+      <c r="BN71" s="8"/>
+      <c r="BO71" s="8"/>
+    </row>
+    <row r="72" spans="3:67" x14ac:dyDescent="0.2">
       <c r="C72" s="8"/>
       <c r="D72" s="8"/>
       <c r="E72" s="8"/>
@@ -6831,8 +7089,10 @@
       <c r="BK72" s="8"/>
       <c r="BL72" s="8"/>
       <c r="BM72" s="8"/>
-    </row>
-    <row r="73" spans="3:65" x14ac:dyDescent="0.2">
+      <c r="BN72" s="8"/>
+      <c r="BO72" s="8"/>
+    </row>
+    <row r="73" spans="3:67" x14ac:dyDescent="0.2">
       <c r="C73" s="8"/>
       <c r="D73" s="8"/>
       <c r="E73" s="8"/>
@@ -6896,8 +7156,10 @@
       <c r="BK73" s="8"/>
       <c r="BL73" s="8"/>
       <c r="BM73" s="8"/>
-    </row>
-    <row r="74" spans="3:65" x14ac:dyDescent="0.2">
+      <c r="BN73" s="8"/>
+      <c r="BO73" s="8"/>
+    </row>
+    <row r="74" spans="3:67" x14ac:dyDescent="0.2">
       <c r="C74" s="8"/>
       <c r="D74" s="8"/>
       <c r="E74" s="8"/>
@@ -6961,8 +7223,10 @@
       <c r="BK74" s="8"/>
       <c r="BL74" s="8"/>
       <c r="BM74" s="8"/>
-    </row>
-    <row r="75" spans="3:65" x14ac:dyDescent="0.2">
+      <c r="BN74" s="8"/>
+      <c r="BO74" s="8"/>
+    </row>
+    <row r="75" spans="3:67" x14ac:dyDescent="0.2">
       <c r="C75" s="8"/>
       <c r="D75" s="8"/>
       <c r="E75" s="8"/>
@@ -7026,8 +7290,10 @@
       <c r="BK75" s="8"/>
       <c r="BL75" s="8"/>
       <c r="BM75" s="8"/>
-    </row>
-    <row r="76" spans="3:65" x14ac:dyDescent="0.2">
+      <c r="BN75" s="8"/>
+      <c r="BO75" s="8"/>
+    </row>
+    <row r="76" spans="3:67" x14ac:dyDescent="0.2">
       <c r="C76" s="8"/>
       <c r="D76" s="8"/>
       <c r="E76" s="8"/>
@@ -7091,8 +7357,10 @@
       <c r="BK76" s="8"/>
       <c r="BL76" s="8"/>
       <c r="BM76" s="8"/>
-    </row>
-    <row r="77" spans="3:65" x14ac:dyDescent="0.2">
+      <c r="BN76" s="8"/>
+      <c r="BO76" s="8"/>
+    </row>
+    <row r="77" spans="3:67" x14ac:dyDescent="0.2">
       <c r="C77" s="8"/>
       <c r="D77" s="8"/>
       <c r="E77" s="8"/>
@@ -7156,8 +7424,10 @@
       <c r="BK77" s="8"/>
       <c r="BL77" s="8"/>
       <c r="BM77" s="8"/>
-    </row>
-    <row r="78" spans="3:65" x14ac:dyDescent="0.2">
+      <c r="BN77" s="8"/>
+      <c r="BO77" s="8"/>
+    </row>
+    <row r="78" spans="3:67" x14ac:dyDescent="0.2">
       <c r="C78" s="8"/>
       <c r="D78" s="8"/>
       <c r="E78" s="8"/>
@@ -7221,8 +7491,10 @@
       <c r="BK78" s="8"/>
       <c r="BL78" s="8"/>
       <c r="BM78" s="8"/>
-    </row>
-    <row r="79" spans="3:65" x14ac:dyDescent="0.2">
+      <c r="BN78" s="8"/>
+      <c r="BO78" s="8"/>
+    </row>
+    <row r="79" spans="3:67" x14ac:dyDescent="0.2">
       <c r="C79" s="8"/>
       <c r="D79" s="8"/>
       <c r="E79" s="8"/>
@@ -7286,8 +7558,10 @@
       <c r="BK79" s="8"/>
       <c r="BL79" s="8"/>
       <c r="BM79" s="8"/>
-    </row>
-    <row r="80" spans="3:65" x14ac:dyDescent="0.2">
+      <c r="BN79" s="8"/>
+      <c r="BO79" s="8"/>
+    </row>
+    <row r="80" spans="3:67" x14ac:dyDescent="0.2">
       <c r="C80" s="8"/>
       <c r="D80" s="8"/>
       <c r="E80" s="8"/>
@@ -7351,8 +7625,10 @@
       <c r="BK80" s="8"/>
       <c r="BL80" s="8"/>
       <c r="BM80" s="8"/>
-    </row>
-    <row r="81" spans="3:65" x14ac:dyDescent="0.2">
+      <c r="BN80" s="8"/>
+      <c r="BO80" s="8"/>
+    </row>
+    <row r="81" spans="3:67" x14ac:dyDescent="0.2">
       <c r="C81" s="8"/>
       <c r="D81" s="8"/>
       <c r="E81" s="8"/>
@@ -7416,8 +7692,10 @@
       <c r="BK81" s="8"/>
       <c r="BL81" s="8"/>
       <c r="BM81" s="8"/>
-    </row>
-    <row r="82" spans="3:65" x14ac:dyDescent="0.2">
+      <c r="BN81" s="8"/>
+      <c r="BO81" s="8"/>
+    </row>
+    <row r="82" spans="3:67" x14ac:dyDescent="0.2">
       <c r="C82" s="8"/>
       <c r="D82" s="8"/>
       <c r="E82" s="8"/>
@@ -7481,8 +7759,10 @@
       <c r="BK82" s="8"/>
       <c r="BL82" s="8"/>
       <c r="BM82" s="8"/>
-    </row>
-    <row r="83" spans="3:65" x14ac:dyDescent="0.2">
+      <c r="BN82" s="8"/>
+      <c r="BO82" s="8"/>
+    </row>
+    <row r="83" spans="3:67" x14ac:dyDescent="0.2">
       <c r="C83" s="8"/>
       <c r="D83" s="8"/>
       <c r="E83" s="8"/>
@@ -7546,8 +7826,10 @@
       <c r="BK83" s="8"/>
       <c r="BL83" s="8"/>
       <c r="BM83" s="8"/>
-    </row>
-    <row r="84" spans="3:65" x14ac:dyDescent="0.2">
+      <c r="BN83" s="8"/>
+      <c r="BO83" s="8"/>
+    </row>
+    <row r="84" spans="3:67" x14ac:dyDescent="0.2">
       <c r="C84" s="8"/>
       <c r="D84" s="8"/>
       <c r="E84" s="8"/>
@@ -7611,8 +7893,10 @@
       <c r="BK84" s="8"/>
       <c r="BL84" s="8"/>
       <c r="BM84" s="8"/>
-    </row>
-    <row r="85" spans="3:65" x14ac:dyDescent="0.2">
+      <c r="BN84" s="8"/>
+      <c r="BO84" s="8"/>
+    </row>
+    <row r="85" spans="3:67" x14ac:dyDescent="0.2">
       <c r="C85" s="8"/>
       <c r="D85" s="8"/>
       <c r="E85" s="8"/>
@@ -7676,8 +7960,10 @@
       <c r="BK85" s="8"/>
       <c r="BL85" s="8"/>
       <c r="BM85" s="8"/>
-    </row>
-    <row r="86" spans="3:65" x14ac:dyDescent="0.2">
+      <c r="BN85" s="8"/>
+      <c r="BO85" s="8"/>
+    </row>
+    <row r="86" spans="3:67" x14ac:dyDescent="0.2">
       <c r="C86" s="8"/>
       <c r="D86" s="8"/>
       <c r="E86" s="8"/>
@@ -7741,8 +8027,10 @@
       <c r="BK86" s="8"/>
       <c r="BL86" s="8"/>
       <c r="BM86" s="8"/>
-    </row>
-    <row r="87" spans="3:65" x14ac:dyDescent="0.2">
+      <c r="BN86" s="8"/>
+      <c r="BO86" s="8"/>
+    </row>
+    <row r="87" spans="3:67" x14ac:dyDescent="0.2">
       <c r="C87" s="8"/>
       <c r="D87" s="8"/>
       <c r="E87" s="8"/>
@@ -7806,8 +8094,10 @@
       <c r="BK87" s="8"/>
       <c r="BL87" s="8"/>
       <c r="BM87" s="8"/>
-    </row>
-    <row r="88" spans="3:65" x14ac:dyDescent="0.2">
+      <c r="BN87" s="8"/>
+      <c r="BO87" s="8"/>
+    </row>
+    <row r="88" spans="3:67" x14ac:dyDescent="0.2">
       <c r="C88" s="8"/>
       <c r="D88" s="8"/>
       <c r="E88" s="8"/>
@@ -7871,8 +8161,10 @@
       <c r="BK88" s="8"/>
       <c r="BL88" s="8"/>
       <c r="BM88" s="8"/>
-    </row>
-    <row r="89" spans="3:65" x14ac:dyDescent="0.2">
+      <c r="BN88" s="8"/>
+      <c r="BO88" s="8"/>
+    </row>
+    <row r="89" spans="3:67" x14ac:dyDescent="0.2">
       <c r="C89" s="8"/>
       <c r="D89" s="8"/>
       <c r="E89" s="8"/>
@@ -7936,8 +8228,10 @@
       <c r="BK89" s="8"/>
       <c r="BL89" s="8"/>
       <c r="BM89" s="8"/>
-    </row>
-    <row r="90" spans="3:65" x14ac:dyDescent="0.2">
+      <c r="BN89" s="8"/>
+      <c r="BO89" s="8"/>
+    </row>
+    <row r="90" spans="3:67" x14ac:dyDescent="0.2">
       <c r="C90" s="8"/>
       <c r="D90" s="8"/>
       <c r="E90" s="8"/>
@@ -8001,8 +8295,10 @@
       <c r="BK90" s="8"/>
       <c r="BL90" s="8"/>
       <c r="BM90" s="8"/>
-    </row>
-    <row r="91" spans="3:65" x14ac:dyDescent="0.2">
+      <c r="BN90" s="8"/>
+      <c r="BO90" s="8"/>
+    </row>
+    <row r="91" spans="3:67" x14ac:dyDescent="0.2">
       <c r="C91" s="8"/>
       <c r="D91" s="8"/>
       <c r="E91" s="8"/>
@@ -8066,8 +8362,10 @@
       <c r="BK91" s="8"/>
       <c r="BL91" s="8"/>
       <c r="BM91" s="8"/>
-    </row>
-    <row r="92" spans="3:65" x14ac:dyDescent="0.2">
+      <c r="BN91" s="8"/>
+      <c r="BO91" s="8"/>
+    </row>
+    <row r="92" spans="3:67" x14ac:dyDescent="0.2">
       <c r="C92" s="8"/>
       <c r="D92" s="8"/>
       <c r="E92" s="8"/>
@@ -8131,8 +8429,10 @@
       <c r="BK92" s="8"/>
       <c r="BL92" s="8"/>
       <c r="BM92" s="8"/>
-    </row>
-    <row r="93" spans="3:65" x14ac:dyDescent="0.2">
+      <c r="BN92" s="8"/>
+      <c r="BO92" s="8"/>
+    </row>
+    <row r="93" spans="3:67" x14ac:dyDescent="0.2">
       <c r="C93" s="8"/>
       <c r="D93" s="8"/>
       <c r="E93" s="8"/>
@@ -8196,8 +8496,10 @@
       <c r="BK93" s="8"/>
       <c r="BL93" s="8"/>
       <c r="BM93" s="8"/>
-    </row>
-    <row r="94" spans="3:65" x14ac:dyDescent="0.2">
+      <c r="BN93" s="8"/>
+      <c r="BO93" s="8"/>
+    </row>
+    <row r="94" spans="3:67" x14ac:dyDescent="0.2">
       <c r="C94" s="8"/>
       <c r="D94" s="8"/>
       <c r="E94" s="8"/>
@@ -8261,8 +8563,10 @@
       <c r="BK94" s="8"/>
       <c r="BL94" s="8"/>
       <c r="BM94" s="8"/>
-    </row>
-    <row r="95" spans="3:65" x14ac:dyDescent="0.2">
+      <c r="BN94" s="8"/>
+      <c r="BO94" s="8"/>
+    </row>
+    <row r="95" spans="3:67" x14ac:dyDescent="0.2">
       <c r="C95" s="8"/>
       <c r="D95" s="8"/>
       <c r="E95" s="8"/>
@@ -8326,8 +8630,10 @@
       <c r="BK95" s="8"/>
       <c r="BL95" s="8"/>
       <c r="BM95" s="8"/>
-    </row>
-    <row r="96" spans="3:65" x14ac:dyDescent="0.2">
+      <c r="BN95" s="8"/>
+      <c r="BO95" s="8"/>
+    </row>
+    <row r="96" spans="3:67" x14ac:dyDescent="0.2">
       <c r="C96" s="8"/>
       <c r="D96" s="8"/>
       <c r="E96" s="8"/>
@@ -8391,8 +8697,10 @@
       <c r="BK96" s="8"/>
       <c r="BL96" s="8"/>
       <c r="BM96" s="8"/>
-    </row>
-    <row r="97" spans="3:65" x14ac:dyDescent="0.2">
+      <c r="BN96" s="8"/>
+      <c r="BO96" s="8"/>
+    </row>
+    <row r="97" spans="3:67" x14ac:dyDescent="0.2">
       <c r="C97" s="8"/>
       <c r="D97" s="8"/>
       <c r="E97" s="8"/>
@@ -8456,8 +8764,10 @@
       <c r="BK97" s="8"/>
       <c r="BL97" s="8"/>
       <c r="BM97" s="8"/>
-    </row>
-    <row r="98" spans="3:65" x14ac:dyDescent="0.2">
+      <c r="BN97" s="8"/>
+      <c r="BO97" s="8"/>
+    </row>
+    <row r="98" spans="3:67" x14ac:dyDescent="0.2">
       <c r="C98" s="8"/>
       <c r="D98" s="8"/>
       <c r="E98" s="8"/>
@@ -8521,8 +8831,10 @@
       <c r="BK98" s="8"/>
       <c r="BL98" s="8"/>
       <c r="BM98" s="8"/>
-    </row>
-    <row r="99" spans="3:65" x14ac:dyDescent="0.2">
+      <c r="BN98" s="8"/>
+      <c r="BO98" s="8"/>
+    </row>
+    <row r="99" spans="3:67" x14ac:dyDescent="0.2">
       <c r="C99" s="8"/>
       <c r="D99" s="8"/>
       <c r="E99" s="8"/>
@@ -8586,8 +8898,10 @@
       <c r="BK99" s="8"/>
       <c r="BL99" s="8"/>
       <c r="BM99" s="8"/>
-    </row>
-    <row r="100" spans="3:65" x14ac:dyDescent="0.2">
+      <c r="BN99" s="8"/>
+      <c r="BO99" s="8"/>
+    </row>
+    <row r="100" spans="3:67" x14ac:dyDescent="0.2">
       <c r="C100" s="8"/>
       <c r="D100" s="8"/>
       <c r="E100" s="8"/>
@@ -8651,8 +8965,10 @@
       <c r="BK100" s="8"/>
       <c r="BL100" s="8"/>
       <c r="BM100" s="8"/>
-    </row>
-    <row r="101" spans="3:65" x14ac:dyDescent="0.2">
+      <c r="BN100" s="8"/>
+      <c r="BO100" s="8"/>
+    </row>
+    <row r="101" spans="3:67" x14ac:dyDescent="0.2">
       <c r="C101" s="8"/>
       <c r="D101" s="8"/>
       <c r="E101" s="8"/>
@@ -8716,8 +9032,10 @@
       <c r="BK101" s="8"/>
       <c r="BL101" s="8"/>
       <c r="BM101" s="8"/>
-    </row>
-    <row r="102" spans="3:65" x14ac:dyDescent="0.2">
+      <c r="BN101" s="8"/>
+      <c r="BO101" s="8"/>
+    </row>
+    <row r="102" spans="3:67" x14ac:dyDescent="0.2">
       <c r="C102" s="8"/>
       <c r="D102" s="8"/>
       <c r="E102" s="8"/>
@@ -8781,8 +9099,10 @@
       <c r="BK102" s="8"/>
       <c r="BL102" s="8"/>
       <c r="BM102" s="8"/>
-    </row>
-    <row r="103" spans="3:65" x14ac:dyDescent="0.2">
+      <c r="BN102" s="8"/>
+      <c r="BO102" s="8"/>
+    </row>
+    <row r="103" spans="3:67" x14ac:dyDescent="0.2">
       <c r="C103" s="8"/>
       <c r="D103" s="8"/>
       <c r="E103" s="8"/>
@@ -8846,8 +9166,10 @@
       <c r="BK103" s="8"/>
       <c r="BL103" s="8"/>
       <c r="BM103" s="8"/>
-    </row>
-    <row r="104" spans="3:65" x14ac:dyDescent="0.2">
+      <c r="BN103" s="8"/>
+      <c r="BO103" s="8"/>
+    </row>
+    <row r="104" spans="3:67" x14ac:dyDescent="0.2">
       <c r="C104" s="8"/>
       <c r="D104" s="8"/>
       <c r="E104" s="8"/>
@@ -8911,8 +9233,10 @@
       <c r="BK104" s="8"/>
       <c r="BL104" s="8"/>
       <c r="BM104" s="8"/>
-    </row>
-    <row r="105" spans="3:65" x14ac:dyDescent="0.2">
+      <c r="BN104" s="8"/>
+      <c r="BO104" s="8"/>
+    </row>
+    <row r="105" spans="3:67" x14ac:dyDescent="0.2">
       <c r="C105" s="8"/>
       <c r="D105" s="8"/>
       <c r="E105" s="8"/>
@@ -8976,8 +9300,10 @@
       <c r="BK105" s="8"/>
       <c r="BL105" s="8"/>
       <c r="BM105" s="8"/>
-    </row>
-    <row r="106" spans="3:65" x14ac:dyDescent="0.2">
+      <c r="BN105" s="8"/>
+      <c r="BO105" s="8"/>
+    </row>
+    <row r="106" spans="3:67" x14ac:dyDescent="0.2">
       <c r="C106" s="8"/>
       <c r="D106" s="8"/>
       <c r="E106" s="8"/>
@@ -9041,8 +9367,10 @@
       <c r="BK106" s="8"/>
       <c r="BL106" s="8"/>
       <c r="BM106" s="8"/>
-    </row>
-    <row r="107" spans="3:65" x14ac:dyDescent="0.2">
+      <c r="BN106" s="8"/>
+      <c r="BO106" s="8"/>
+    </row>
+    <row r="107" spans="3:67" x14ac:dyDescent="0.2">
       <c r="C107" s="8"/>
       <c r="D107" s="8"/>
       <c r="E107" s="8"/>
@@ -9106,8 +9434,10 @@
       <c r="BK107" s="8"/>
       <c r="BL107" s="8"/>
       <c r="BM107" s="8"/>
-    </row>
-    <row r="108" spans="3:65" x14ac:dyDescent="0.2">
+      <c r="BN107" s="8"/>
+      <c r="BO107" s="8"/>
+    </row>
+    <row r="108" spans="3:67" x14ac:dyDescent="0.2">
       <c r="C108" s="8"/>
       <c r="D108" s="8"/>
       <c r="E108" s="8"/>
@@ -9171,8 +9501,10 @@
       <c r="BK108" s="8"/>
       <c r="BL108" s="8"/>
       <c r="BM108" s="8"/>
-    </row>
-    <row r="109" spans="3:65" x14ac:dyDescent="0.2">
+      <c r="BN108" s="8"/>
+      <c r="BO108" s="8"/>
+    </row>
+    <row r="109" spans="3:67" x14ac:dyDescent="0.2">
       <c r="C109" s="8"/>
       <c r="D109" s="8"/>
       <c r="E109" s="8"/>
@@ -9236,8 +9568,10 @@
       <c r="BK109" s="8"/>
       <c r="BL109" s="8"/>
       <c r="BM109" s="8"/>
-    </row>
-    <row r="110" spans="3:65" x14ac:dyDescent="0.2">
+      <c r="BN109" s="8"/>
+      <c r="BO109" s="8"/>
+    </row>
+    <row r="110" spans="3:67" x14ac:dyDescent="0.2">
       <c r="C110" s="8"/>
       <c r="D110" s="8"/>
       <c r="E110" s="8"/>
@@ -9301,8 +9635,10 @@
       <c r="BK110" s="8"/>
       <c r="BL110" s="8"/>
       <c r="BM110" s="8"/>
-    </row>
-    <row r="111" spans="3:65" x14ac:dyDescent="0.2">
+      <c r="BN110" s="8"/>
+      <c r="BO110" s="8"/>
+    </row>
+    <row r="111" spans="3:67" x14ac:dyDescent="0.2">
       <c r="C111" s="8"/>
       <c r="D111" s="8"/>
       <c r="E111" s="8"/>
@@ -9366,8 +9702,10 @@
       <c r="BK111" s="8"/>
       <c r="BL111" s="8"/>
       <c r="BM111" s="8"/>
-    </row>
-    <row r="112" spans="3:65" x14ac:dyDescent="0.2">
+      <c r="BN111" s="8"/>
+      <c r="BO111" s="8"/>
+    </row>
+    <row r="112" spans="3:67" x14ac:dyDescent="0.2">
       <c r="C112" s="8"/>
       <c r="D112" s="8"/>
       <c r="E112" s="8"/>
@@ -9431,8 +9769,10 @@
       <c r="BK112" s="8"/>
       <c r="BL112" s="8"/>
       <c r="BM112" s="8"/>
-    </row>
-    <row r="113" spans="3:65" x14ac:dyDescent="0.2">
+      <c r="BN112" s="8"/>
+      <c r="BO112" s="8"/>
+    </row>
+    <row r="113" spans="3:67" x14ac:dyDescent="0.2">
       <c r="C113" s="8"/>
       <c r="D113" s="8"/>
       <c r="E113" s="8"/>
@@ -9496,8 +9836,10 @@
       <c r="BK113" s="8"/>
       <c r="BL113" s="8"/>
       <c r="BM113" s="8"/>
-    </row>
-    <row r="114" spans="3:65" x14ac:dyDescent="0.2">
+      <c r="BN113" s="8"/>
+      <c r="BO113" s="8"/>
+    </row>
+    <row r="114" spans="3:67" x14ac:dyDescent="0.2">
       <c r="C114" s="8"/>
       <c r="D114" s="8"/>
       <c r="E114" s="8"/>
@@ -9561,8 +9903,10 @@
       <c r="BK114" s="8"/>
       <c r="BL114" s="8"/>
       <c r="BM114" s="8"/>
-    </row>
-    <row r="115" spans="3:65" x14ac:dyDescent="0.2">
+      <c r="BN114" s="8"/>
+      <c r="BO114" s="8"/>
+    </row>
+    <row r="115" spans="3:67" x14ac:dyDescent="0.2">
       <c r="C115" s="8"/>
       <c r="D115" s="8"/>
       <c r="E115" s="8"/>
@@ -9626,8 +9970,10 @@
       <c r="BK115" s="8"/>
       <c r="BL115" s="8"/>
       <c r="BM115" s="8"/>
-    </row>
-    <row r="116" spans="3:65" x14ac:dyDescent="0.2">
+      <c r="BN115" s="8"/>
+      <c r="BO115" s="8"/>
+    </row>
+    <row r="116" spans="3:67" x14ac:dyDescent="0.2">
       <c r="C116" s="8"/>
       <c r="D116" s="8"/>
       <c r="E116" s="8"/>
@@ -9691,8 +10037,10 @@
       <c r="BK116" s="8"/>
       <c r="BL116" s="8"/>
       <c r="BM116" s="8"/>
-    </row>
-    <row r="117" spans="3:65" x14ac:dyDescent="0.2">
+      <c r="BN116" s="8"/>
+      <c r="BO116" s="8"/>
+    </row>
+    <row r="117" spans="3:67" x14ac:dyDescent="0.2">
       <c r="C117" s="8"/>
       <c r="D117" s="8"/>
       <c r="E117" s="8"/>
@@ -9756,8 +10104,10 @@
       <c r="BK117" s="8"/>
       <c r="BL117" s="8"/>
       <c r="BM117" s="8"/>
-    </row>
-    <row r="118" spans="3:65" x14ac:dyDescent="0.2">
+      <c r="BN117" s="8"/>
+      <c r="BO117" s="8"/>
+    </row>
+    <row r="118" spans="3:67" x14ac:dyDescent="0.2">
       <c r="C118" s="8"/>
       <c r="D118" s="8"/>
       <c r="E118" s="8"/>
@@ -9821,8 +10171,10 @@
       <c r="BK118" s="8"/>
       <c r="BL118" s="8"/>
       <c r="BM118" s="8"/>
-    </row>
-    <row r="119" spans="3:65" x14ac:dyDescent="0.2">
+      <c r="BN118" s="8"/>
+      <c r="BO118" s="8"/>
+    </row>
+    <row r="119" spans="3:67" x14ac:dyDescent="0.2">
       <c r="C119" s="8"/>
       <c r="D119" s="8"/>
       <c r="E119" s="8"/>
@@ -9886,8 +10238,10 @@
       <c r="BK119" s="8"/>
       <c r="BL119" s="8"/>
       <c r="BM119" s="8"/>
-    </row>
-    <row r="120" spans="3:65" x14ac:dyDescent="0.2">
+      <c r="BN119" s="8"/>
+      <c r="BO119" s="8"/>
+    </row>
+    <row r="120" spans="3:67" x14ac:dyDescent="0.2">
       <c r="C120" s="8"/>
       <c r="D120" s="8"/>
       <c r="E120" s="8"/>
@@ -9951,8 +10305,10 @@
       <c r="BK120" s="8"/>
       <c r="BL120" s="8"/>
       <c r="BM120" s="8"/>
-    </row>
-    <row r="121" spans="3:65" x14ac:dyDescent="0.2">
+      <c r="BN120" s="8"/>
+      <c r="BO120" s="8"/>
+    </row>
+    <row r="121" spans="3:67" x14ac:dyDescent="0.2">
       <c r="C121" s="8"/>
       <c r="D121" s="8"/>
       <c r="E121" s="8"/>
@@ -10016,8 +10372,10 @@
       <c r="BK121" s="8"/>
       <c r="BL121" s="8"/>
       <c r="BM121" s="8"/>
-    </row>
-    <row r="122" spans="3:65" x14ac:dyDescent="0.2">
+      <c r="BN121" s="8"/>
+      <c r="BO121" s="8"/>
+    </row>
+    <row r="122" spans="3:67" x14ac:dyDescent="0.2">
       <c r="C122" s="8"/>
       <c r="D122" s="8"/>
       <c r="E122" s="8"/>
@@ -10081,8 +10439,10 @@
       <c r="BK122" s="8"/>
       <c r="BL122" s="8"/>
       <c r="BM122" s="8"/>
-    </row>
-    <row r="123" spans="3:65" x14ac:dyDescent="0.2">
+      <c r="BN122" s="8"/>
+      <c r="BO122" s="8"/>
+    </row>
+    <row r="123" spans="3:67" x14ac:dyDescent="0.2">
       <c r="C123" s="8"/>
       <c r="D123" s="8"/>
       <c r="E123" s="8"/>
@@ -10146,8 +10506,10 @@
       <c r="BK123" s="8"/>
       <c r="BL123" s="8"/>
       <c r="BM123" s="8"/>
-    </row>
-    <row r="124" spans="3:65" x14ac:dyDescent="0.2">
+      <c r="BN123" s="8"/>
+      <c r="BO123" s="8"/>
+    </row>
+    <row r="124" spans="3:67" x14ac:dyDescent="0.2">
       <c r="C124" s="8"/>
       <c r="D124" s="8"/>
       <c r="E124" s="8"/>
@@ -10211,8 +10573,10 @@
       <c r="BK124" s="8"/>
       <c r="BL124" s="8"/>
       <c r="BM124" s="8"/>
-    </row>
-    <row r="125" spans="3:65" x14ac:dyDescent="0.2">
+      <c r="BN124" s="8"/>
+      <c r="BO124" s="8"/>
+    </row>
+    <row r="125" spans="3:67" x14ac:dyDescent="0.2">
       <c r="C125" s="8"/>
       <c r="D125" s="8"/>
       <c r="E125" s="8"/>
@@ -10276,8 +10640,10 @@
       <c r="BK125" s="8"/>
       <c r="BL125" s="8"/>
       <c r="BM125" s="8"/>
-    </row>
-    <row r="126" spans="3:65" x14ac:dyDescent="0.2">
+      <c r="BN125" s="8"/>
+      <c r="BO125" s="8"/>
+    </row>
+    <row r="126" spans="3:67" x14ac:dyDescent="0.2">
       <c r="C126" s="8"/>
       <c r="D126" s="8"/>
       <c r="E126" s="8"/>
@@ -10341,8 +10707,10 @@
       <c r="BK126" s="8"/>
       <c r="BL126" s="8"/>
       <c r="BM126" s="8"/>
-    </row>
-    <row r="127" spans="3:65" x14ac:dyDescent="0.2">
+      <c r="BN126" s="8"/>
+      <c r="BO126" s="8"/>
+    </row>
+    <row r="127" spans="3:67" x14ac:dyDescent="0.2">
       <c r="C127" s="8"/>
       <c r="D127" s="8"/>
       <c r="E127" s="8"/>
@@ -10406,8 +10774,10 @@
       <c r="BK127" s="8"/>
       <c r="BL127" s="8"/>
       <c r="BM127" s="8"/>
-    </row>
-    <row r="128" spans="3:65" x14ac:dyDescent="0.2">
+      <c r="BN127" s="8"/>
+      <c r="BO127" s="8"/>
+    </row>
+    <row r="128" spans="3:67" x14ac:dyDescent="0.2">
       <c r="C128" s="8"/>
       <c r="D128" s="8"/>
       <c r="E128" s="8"/>
@@ -10471,8 +10841,10 @@
       <c r="BK128" s="8"/>
       <c r="BL128" s="8"/>
       <c r="BM128" s="8"/>
-    </row>
-    <row r="129" spans="3:65" x14ac:dyDescent="0.2">
+      <c r="BN128" s="8"/>
+      <c r="BO128" s="8"/>
+    </row>
+    <row r="129" spans="3:67" x14ac:dyDescent="0.2">
       <c r="C129" s="8"/>
       <c r="D129" s="8"/>
       <c r="E129" s="8"/>
@@ -10536,8 +10908,10 @@
       <c r="BK129" s="8"/>
       <c r="BL129" s="8"/>
       <c r="BM129" s="8"/>
-    </row>
-    <row r="130" spans="3:65" x14ac:dyDescent="0.2">
+      <c r="BN129" s="8"/>
+      <c r="BO129" s="8"/>
+    </row>
+    <row r="130" spans="3:67" x14ac:dyDescent="0.2">
       <c r="C130" s="8"/>
       <c r="D130" s="8"/>
       <c r="E130" s="8"/>
@@ -10601,8 +10975,10 @@
       <c r="BK130" s="8"/>
       <c r="BL130" s="8"/>
       <c r="BM130" s="8"/>
-    </row>
-    <row r="131" spans="3:65" x14ac:dyDescent="0.2">
+      <c r="BN130" s="8"/>
+      <c r="BO130" s="8"/>
+    </row>
+    <row r="131" spans="3:67" x14ac:dyDescent="0.2">
       <c r="C131" s="8"/>
       <c r="D131" s="8"/>
       <c r="E131" s="8"/>
@@ -10666,8 +11042,10 @@
       <c r="BK131" s="8"/>
       <c r="BL131" s="8"/>
       <c r="BM131" s="8"/>
-    </row>
-    <row r="132" spans="3:65" x14ac:dyDescent="0.2">
+      <c r="BN131" s="8"/>
+      <c r="BO131" s="8"/>
+    </row>
+    <row r="132" spans="3:67" x14ac:dyDescent="0.2">
       <c r="C132" s="8"/>
       <c r="D132" s="8"/>
       <c r="E132" s="8"/>
@@ -10731,8 +11109,10 @@
       <c r="BK132" s="8"/>
       <c r="BL132" s="8"/>
       <c r="BM132" s="8"/>
-    </row>
-    <row r="133" spans="3:65" x14ac:dyDescent="0.2">
+      <c r="BN132" s="8"/>
+      <c r="BO132" s="8"/>
+    </row>
+    <row r="133" spans="3:67" x14ac:dyDescent="0.2">
       <c r="C133" s="8"/>
       <c r="D133" s="8"/>
       <c r="E133" s="8"/>
@@ -10796,8 +11176,10 @@
       <c r="BK133" s="8"/>
       <c r="BL133" s="8"/>
       <c r="BM133" s="8"/>
-    </row>
-    <row r="134" spans="3:65" x14ac:dyDescent="0.2">
+      <c r="BN133" s="8"/>
+      <c r="BO133" s="8"/>
+    </row>
+    <row r="134" spans="3:67" x14ac:dyDescent="0.2">
       <c r="C134" s="8"/>
       <c r="D134" s="8"/>
       <c r="E134" s="8"/>
@@ -10861,8 +11243,10 @@
       <c r="BK134" s="8"/>
       <c r="BL134" s="8"/>
       <c r="BM134" s="8"/>
-    </row>
-    <row r="135" spans="3:65" x14ac:dyDescent="0.2">
+      <c r="BN134" s="8"/>
+      <c r="BO134" s="8"/>
+    </row>
+    <row r="135" spans="3:67" x14ac:dyDescent="0.2">
       <c r="C135" s="8"/>
       <c r="D135" s="8"/>
       <c r="E135" s="8"/>
@@ -10926,8 +11310,10 @@
       <c r="BK135" s="8"/>
       <c r="BL135" s="8"/>
       <c r="BM135" s="8"/>
-    </row>
-    <row r="136" spans="3:65" x14ac:dyDescent="0.2">
+      <c r="BN135" s="8"/>
+      <c r="BO135" s="8"/>
+    </row>
+    <row r="136" spans="3:67" x14ac:dyDescent="0.2">
       <c r="C136" s="8"/>
       <c r="D136" s="8"/>
       <c r="E136" s="8"/>
@@ -10991,8 +11377,10 @@
       <c r="BK136" s="8"/>
       <c r="BL136" s="8"/>
       <c r="BM136" s="8"/>
-    </row>
-    <row r="137" spans="3:65" x14ac:dyDescent="0.2">
+      <c r="BN136" s="8"/>
+      <c r="BO136" s="8"/>
+    </row>
+    <row r="137" spans="3:67" x14ac:dyDescent="0.2">
       <c r="C137" s="8"/>
       <c r="D137" s="8"/>
       <c r="E137" s="8"/>
@@ -11056,8 +11444,10 @@
       <c r="BK137" s="8"/>
       <c r="BL137" s="8"/>
       <c r="BM137" s="8"/>
-    </row>
-    <row r="138" spans="3:65" x14ac:dyDescent="0.2">
+      <c r="BN137" s="8"/>
+      <c r="BO137" s="8"/>
+    </row>
+    <row r="138" spans="3:67" x14ac:dyDescent="0.2">
       <c r="C138" s="8"/>
       <c r="D138" s="8"/>
       <c r="E138" s="8"/>
@@ -11121,8 +11511,10 @@
       <c r="BK138" s="8"/>
       <c r="BL138" s="8"/>
       <c r="BM138" s="8"/>
-    </row>
-    <row r="139" spans="3:65" x14ac:dyDescent="0.2">
+      <c r="BN138" s="8"/>
+      <c r="BO138" s="8"/>
+    </row>
+    <row r="139" spans="3:67" x14ac:dyDescent="0.2">
       <c r="C139" s="8"/>
       <c r="D139" s="8"/>
       <c r="E139" s="8"/>
@@ -11186,8 +11578,10 @@
       <c r="BK139" s="8"/>
       <c r="BL139" s="8"/>
       <c r="BM139" s="8"/>
-    </row>
-    <row r="140" spans="3:65" x14ac:dyDescent="0.2">
+      <c r="BN139" s="8"/>
+      <c r="BO139" s="8"/>
+    </row>
+    <row r="140" spans="3:67" x14ac:dyDescent="0.2">
       <c r="C140" s="8"/>
       <c r="D140" s="8"/>
       <c r="E140" s="8"/>
@@ -11251,8 +11645,10 @@
       <c r="BK140" s="8"/>
       <c r="BL140" s="8"/>
       <c r="BM140" s="8"/>
-    </row>
-    <row r="141" spans="3:65" x14ac:dyDescent="0.2">
+      <c r="BN140" s="8"/>
+      <c r="BO140" s="8"/>
+    </row>
+    <row r="141" spans="3:67" x14ac:dyDescent="0.2">
       <c r="C141" s="8"/>
       <c r="D141" s="8"/>
       <c r="E141" s="8"/>
@@ -11316,8 +11712,10 @@
       <c r="BK141" s="8"/>
       <c r="BL141" s="8"/>
       <c r="BM141" s="8"/>
-    </row>
-    <row r="142" spans="3:65" x14ac:dyDescent="0.2">
+      <c r="BN141" s="8"/>
+      <c r="BO141" s="8"/>
+    </row>
+    <row r="142" spans="3:67" x14ac:dyDescent="0.2">
       <c r="C142" s="8"/>
       <c r="D142" s="8"/>
       <c r="E142" s="8"/>
@@ -11381,8 +11779,10 @@
       <c r="BK142" s="8"/>
       <c r="BL142" s="8"/>
       <c r="BM142" s="8"/>
-    </row>
-    <row r="143" spans="3:65" x14ac:dyDescent="0.2">
+      <c r="BN142" s="8"/>
+      <c r="BO142" s="8"/>
+    </row>
+    <row r="143" spans="3:67" x14ac:dyDescent="0.2">
       <c r="C143" s="8"/>
       <c r="D143" s="8"/>
       <c r="E143" s="8"/>
@@ -11446,8 +11846,10 @@
       <c r="BK143" s="8"/>
       <c r="BL143" s="8"/>
       <c r="BM143" s="8"/>
-    </row>
-    <row r="144" spans="3:65" x14ac:dyDescent="0.2">
+      <c r="BN143" s="8"/>
+      <c r="BO143" s="8"/>
+    </row>
+    <row r="144" spans="3:67" x14ac:dyDescent="0.2">
       <c r="C144" s="8"/>
       <c r="D144" s="8"/>
       <c r="E144" s="8"/>
@@ -11511,8 +11913,10 @@
       <c r="BK144" s="8"/>
       <c r="BL144" s="8"/>
       <c r="BM144" s="8"/>
-    </row>
-    <row r="145" spans="3:65" x14ac:dyDescent="0.2">
+      <c r="BN144" s="8"/>
+      <c r="BO144" s="8"/>
+    </row>
+    <row r="145" spans="3:67" x14ac:dyDescent="0.2">
       <c r="C145" s="8"/>
       <c r="D145" s="8"/>
       <c r="E145" s="8"/>
@@ -11576,8 +11980,10 @@
       <c r="BK145" s="8"/>
       <c r="BL145" s="8"/>
       <c r="BM145" s="8"/>
-    </row>
-    <row r="146" spans="3:65" x14ac:dyDescent="0.2">
+      <c r="BN145" s="8"/>
+      <c r="BO145" s="8"/>
+    </row>
+    <row r="146" spans="3:67" x14ac:dyDescent="0.2">
       <c r="C146" s="8"/>
       <c r="D146" s="8"/>
       <c r="E146" s="8"/>
@@ -11641,8 +12047,10 @@
       <c r="BK146" s="8"/>
       <c r="BL146" s="8"/>
       <c r="BM146" s="8"/>
-    </row>
-    <row r="147" spans="3:65" x14ac:dyDescent="0.2">
+      <c r="BN146" s="8"/>
+      <c r="BO146" s="8"/>
+    </row>
+    <row r="147" spans="3:67" x14ac:dyDescent="0.2">
       <c r="C147" s="8"/>
       <c r="D147" s="8"/>
       <c r="E147" s="8"/>
@@ -11706,8 +12114,10 @@
       <c r="BK147" s="8"/>
       <c r="BL147" s="8"/>
       <c r="BM147" s="8"/>
-    </row>
-    <row r="148" spans="3:65" x14ac:dyDescent="0.2">
+      <c r="BN147" s="8"/>
+      <c r="BO147" s="8"/>
+    </row>
+    <row r="148" spans="3:67" x14ac:dyDescent="0.2">
       <c r="C148" s="8"/>
       <c r="D148" s="8"/>
       <c r="E148" s="8"/>
@@ -11771,8 +12181,10 @@
       <c r="BK148" s="8"/>
       <c r="BL148" s="8"/>
       <c r="BM148" s="8"/>
-    </row>
-    <row r="149" spans="3:65" x14ac:dyDescent="0.2">
+      <c r="BN148" s="8"/>
+      <c r="BO148" s="8"/>
+    </row>
+    <row r="149" spans="3:67" x14ac:dyDescent="0.2">
       <c r="C149" s="8"/>
       <c r="D149" s="8"/>
       <c r="E149" s="8"/>
@@ -11836,8 +12248,10 @@
       <c r="BK149" s="8"/>
       <c r="BL149" s="8"/>
       <c r="BM149" s="8"/>
-    </row>
-    <row r="150" spans="3:65" x14ac:dyDescent="0.2">
+      <c r="BN149" s="8"/>
+      <c r="BO149" s="8"/>
+    </row>
+    <row r="150" spans="3:67" x14ac:dyDescent="0.2">
       <c r="C150" s="8"/>
       <c r="D150" s="8"/>
       <c r="E150" s="8"/>
@@ -11901,8 +12315,10 @@
       <c r="BK150" s="8"/>
       <c r="BL150" s="8"/>
       <c r="BM150" s="8"/>
-    </row>
-    <row r="151" spans="3:65" x14ac:dyDescent="0.2">
+      <c r="BN150" s="8"/>
+      <c r="BO150" s="8"/>
+    </row>
+    <row r="151" spans="3:67" x14ac:dyDescent="0.2">
       <c r="C151" s="8"/>
       <c r="D151" s="8"/>
       <c r="E151" s="8"/>
@@ -11966,8 +12382,10 @@
       <c r="BK151" s="8"/>
       <c r="BL151" s="8"/>
       <c r="BM151" s="8"/>
-    </row>
-    <row r="152" spans="3:65" x14ac:dyDescent="0.2">
+      <c r="BN151" s="8"/>
+      <c r="BO151" s="8"/>
+    </row>
+    <row r="152" spans="3:67" x14ac:dyDescent="0.2">
       <c r="C152" s="8"/>
       <c r="D152" s="8"/>
       <c r="E152" s="8"/>
@@ -12031,8 +12449,10 @@
       <c r="BK152" s="8"/>
       <c r="BL152" s="8"/>
       <c r="BM152" s="8"/>
-    </row>
-    <row r="153" spans="3:65" x14ac:dyDescent="0.2">
+      <c r="BN152" s="8"/>
+      <c r="BO152" s="8"/>
+    </row>
+    <row r="153" spans="3:67" x14ac:dyDescent="0.2">
       <c r="C153" s="8"/>
       <c r="D153" s="8"/>
       <c r="E153" s="8"/>
@@ -12096,8 +12516,10 @@
       <c r="BK153" s="8"/>
       <c r="BL153" s="8"/>
       <c r="BM153" s="8"/>
-    </row>
-    <row r="154" spans="3:65" x14ac:dyDescent="0.2">
+      <c r="BN153" s="8"/>
+      <c r="BO153" s="8"/>
+    </row>
+    <row r="154" spans="3:67" x14ac:dyDescent="0.2">
       <c r="C154" s="8"/>
       <c r="D154" s="8"/>
       <c r="E154" s="8"/>
@@ -12161,8 +12583,10 @@
       <c r="BK154" s="8"/>
       <c r="BL154" s="8"/>
       <c r="BM154" s="8"/>
-    </row>
-    <row r="155" spans="3:65" x14ac:dyDescent="0.2">
+      <c r="BN154" s="8"/>
+      <c r="BO154" s="8"/>
+    </row>
+    <row r="155" spans="3:67" x14ac:dyDescent="0.2">
       <c r="C155" s="4"/>
       <c r="D155" s="4"/>
       <c r="E155" s="4"/>
@@ -12225,8 +12649,10 @@
       <c r="BJ155" s="4"/>
       <c r="BK155" s="4"/>
       <c r="BL155" s="4"/>
-    </row>
-    <row r="156" spans="3:65" x14ac:dyDescent="0.2">
+      <c r="BM155" s="4"/>
+      <c r="BN155" s="4"/>
+    </row>
+    <row r="156" spans="3:67" x14ac:dyDescent="0.2">
       <c r="C156" s="4"/>
       <c r="D156" s="4"/>
       <c r="E156" s="4"/>
@@ -12289,8 +12715,10 @@
       <c r="BJ156" s="4"/>
       <c r="BK156" s="4"/>
       <c r="BL156" s="4"/>
-    </row>
-    <row r="157" spans="3:65" x14ac:dyDescent="0.2">
+      <c r="BM156" s="4"/>
+      <c r="BN156" s="4"/>
+    </row>
+    <row r="157" spans="3:67" x14ac:dyDescent="0.2">
       <c r="C157" s="4"/>
       <c r="D157" s="4"/>
       <c r="E157" s="4"/>
@@ -12353,8 +12781,10 @@
       <c r="BJ157" s="4"/>
       <c r="BK157" s="4"/>
       <c r="BL157" s="4"/>
-    </row>
-    <row r="158" spans="3:65" x14ac:dyDescent="0.2">
+      <c r="BM157" s="4"/>
+      <c r="BN157" s="4"/>
+    </row>
+    <row r="158" spans="3:67" x14ac:dyDescent="0.2">
       <c r="C158" s="4"/>
       <c r="D158" s="4"/>
       <c r="E158" s="4"/>
@@ -12417,8 +12847,10 @@
       <c r="BJ158" s="4"/>
       <c r="BK158" s="4"/>
       <c r="BL158" s="4"/>
-    </row>
-    <row r="159" spans="3:65" x14ac:dyDescent="0.2">
+      <c r="BM158" s="4"/>
+      <c r="BN158" s="4"/>
+    </row>
+    <row r="159" spans="3:67" x14ac:dyDescent="0.2">
       <c r="C159" s="4"/>
       <c r="D159" s="4"/>
       <c r="E159" s="4"/>
@@ -12481,8 +12913,10 @@
       <c r="BJ159" s="4"/>
       <c r="BK159" s="4"/>
       <c r="BL159" s="4"/>
-    </row>
-    <row r="160" spans="3:65" x14ac:dyDescent="0.2">
+      <c r="BM159" s="4"/>
+      <c r="BN159" s="4"/>
+    </row>
+    <row r="160" spans="3:67" x14ac:dyDescent="0.2">
       <c r="C160" s="4"/>
       <c r="D160" s="4"/>
       <c r="E160" s="4"/>
@@ -12545,8 +12979,10 @@
       <c r="BJ160" s="4"/>
       <c r="BK160" s="4"/>
       <c r="BL160" s="4"/>
-    </row>
-    <row r="161" spans="3:64" x14ac:dyDescent="0.2">
+      <c r="BM160" s="4"/>
+      <c r="BN160" s="4"/>
+    </row>
+    <row r="161" spans="3:66" x14ac:dyDescent="0.2">
       <c r="C161" s="4"/>
       <c r="D161" s="4"/>
       <c r="E161" s="4"/>
@@ -12609,8 +13045,10 @@
       <c r="BJ161" s="4"/>
       <c r="BK161" s="4"/>
       <c r="BL161" s="4"/>
-    </row>
-    <row r="162" spans="3:64" x14ac:dyDescent="0.2">
+      <c r="BM161" s="4"/>
+      <c r="BN161" s="4"/>
+    </row>
+    <row r="162" spans="3:66" x14ac:dyDescent="0.2">
       <c r="C162" s="4"/>
       <c r="D162" s="4"/>
       <c r="E162" s="4"/>
@@ -12673,8 +13111,10 @@
       <c r="BJ162" s="4"/>
       <c r="BK162" s="4"/>
       <c r="BL162" s="4"/>
-    </row>
-    <row r="163" spans="3:64" x14ac:dyDescent="0.2">
+      <c r="BM162" s="4"/>
+      <c r="BN162" s="4"/>
+    </row>
+    <row r="163" spans="3:66" x14ac:dyDescent="0.2">
       <c r="C163" s="4"/>
       <c r="D163" s="4"/>
       <c r="E163" s="4"/>
@@ -12737,8 +13177,10 @@
       <c r="BJ163" s="4"/>
       <c r="BK163" s="4"/>
       <c r="BL163" s="4"/>
-    </row>
-    <row r="164" spans="3:64" x14ac:dyDescent="0.2">
+      <c r="BM163" s="4"/>
+      <c r="BN163" s="4"/>
+    </row>
+    <row r="164" spans="3:66" x14ac:dyDescent="0.2">
       <c r="C164" s="4"/>
       <c r="D164" s="4"/>
       <c r="E164" s="4"/>
@@ -12801,8 +13243,10 @@
       <c r="BJ164" s="4"/>
       <c r="BK164" s="4"/>
       <c r="BL164" s="4"/>
-    </row>
-    <row r="165" spans="3:64" x14ac:dyDescent="0.2">
+      <c r="BM164" s="4"/>
+      <c r="BN164" s="4"/>
+    </row>
+    <row r="165" spans="3:66" x14ac:dyDescent="0.2">
       <c r="C165" s="4"/>
       <c r="D165" s="4"/>
       <c r="E165" s="4"/>
@@ -12865,8 +13309,10 @@
       <c r="BJ165" s="4"/>
       <c r="BK165" s="4"/>
       <c r="BL165" s="4"/>
-    </row>
-    <row r="166" spans="3:64" x14ac:dyDescent="0.2">
+      <c r="BM165" s="4"/>
+      <c r="BN165" s="4"/>
+    </row>
+    <row r="166" spans="3:66" x14ac:dyDescent="0.2">
       <c r="C166" s="4"/>
       <c r="D166" s="4"/>
       <c r="E166" s="4"/>
@@ -12929,8 +13375,10 @@
       <c r="BJ166" s="4"/>
       <c r="BK166" s="4"/>
       <c r="BL166" s="4"/>
-    </row>
-    <row r="167" spans="3:64" x14ac:dyDescent="0.2">
+      <c r="BM166" s="4"/>
+      <c r="BN166" s="4"/>
+    </row>
+    <row r="167" spans="3:66" x14ac:dyDescent="0.2">
       <c r="C167" s="4"/>
       <c r="D167" s="4"/>
       <c r="E167" s="4"/>
@@ -12993,8 +13441,10 @@
       <c r="BJ167" s="4"/>
       <c r="BK167" s="4"/>
       <c r="BL167" s="4"/>
-    </row>
-    <row r="168" spans="3:64" x14ac:dyDescent="0.2">
+      <c r="BM167" s="4"/>
+      <c r="BN167" s="4"/>
+    </row>
+    <row r="168" spans="3:66" x14ac:dyDescent="0.2">
       <c r="C168" s="4"/>
       <c r="D168" s="4"/>
       <c r="E168" s="4"/>
@@ -13057,8 +13507,10 @@
       <c r="BJ168" s="4"/>
       <c r="BK168" s="4"/>
       <c r="BL168" s="4"/>
-    </row>
-    <row r="169" spans="3:64" x14ac:dyDescent="0.2">
+      <c r="BM168" s="4"/>
+      <c r="BN168" s="4"/>
+    </row>
+    <row r="169" spans="3:66" x14ac:dyDescent="0.2">
       <c r="C169" s="4"/>
       <c r="D169" s="4"/>
       <c r="E169" s="4"/>
@@ -13121,8 +13573,10 @@
       <c r="BJ169" s="4"/>
       <c r="BK169" s="4"/>
       <c r="BL169" s="4"/>
-    </row>
-    <row r="170" spans="3:64" x14ac:dyDescent="0.2">
+      <c r="BM169" s="4"/>
+      <c r="BN169" s="4"/>
+    </row>
+    <row r="170" spans="3:66" x14ac:dyDescent="0.2">
       <c r="C170" s="4"/>
       <c r="D170" s="4"/>
       <c r="E170" s="4"/>
@@ -13185,8 +13639,10 @@
       <c r="BJ170" s="4"/>
       <c r="BK170" s="4"/>
       <c r="BL170" s="4"/>
-    </row>
-    <row r="171" spans="3:64" x14ac:dyDescent="0.2">
+      <c r="BM170" s="4"/>
+      <c r="BN170" s="4"/>
+    </row>
+    <row r="171" spans="3:66" x14ac:dyDescent="0.2">
       <c r="C171" s="4"/>
       <c r="D171" s="4"/>
       <c r="E171" s="4"/>
@@ -13249,8 +13705,10 @@
       <c r="BJ171" s="4"/>
       <c r="BK171" s="4"/>
       <c r="BL171" s="4"/>
-    </row>
-    <row r="172" spans="3:64" x14ac:dyDescent="0.2">
+      <c r="BM171" s="4"/>
+      <c r="BN171" s="4"/>
+    </row>
+    <row r="172" spans="3:66" x14ac:dyDescent="0.2">
       <c r="C172" s="4"/>
       <c r="D172" s="4"/>
       <c r="E172" s="4"/>
@@ -13313,8 +13771,10 @@
       <c r="BJ172" s="4"/>
       <c r="BK172" s="4"/>
       <c r="BL172" s="4"/>
-    </row>
-    <row r="173" spans="3:64" x14ac:dyDescent="0.2">
+      <c r="BM172" s="4"/>
+      <c r="BN172" s="4"/>
+    </row>
+    <row r="173" spans="3:66" x14ac:dyDescent="0.2">
       <c r="C173" s="4"/>
       <c r="D173" s="4"/>
       <c r="E173" s="4"/>
@@ -13377,8 +13837,10 @@
       <c r="BJ173" s="4"/>
       <c r="BK173" s="4"/>
       <c r="BL173" s="4"/>
-    </row>
-    <row r="174" spans="3:64" x14ac:dyDescent="0.2">
+      <c r="BM173" s="4"/>
+      <c r="BN173" s="4"/>
+    </row>
+    <row r="174" spans="3:66" x14ac:dyDescent="0.2">
       <c r="C174" s="4"/>
       <c r="D174" s="4"/>
       <c r="E174" s="4"/>
@@ -13441,8 +13903,10 @@
       <c r="BJ174" s="4"/>
       <c r="BK174" s="4"/>
       <c r="BL174" s="4"/>
-    </row>
-    <row r="175" spans="3:64" x14ac:dyDescent="0.2">
+      <c r="BM174" s="4"/>
+      <c r="BN174" s="4"/>
+    </row>
+    <row r="175" spans="3:66" x14ac:dyDescent="0.2">
       <c r="C175" s="4"/>
       <c r="D175" s="4"/>
       <c r="E175" s="4"/>
@@ -13505,8 +13969,10 @@
       <c r="BJ175" s="4"/>
       <c r="BK175" s="4"/>
       <c r="BL175" s="4"/>
-    </row>
-    <row r="176" spans="3:64" x14ac:dyDescent="0.2">
+      <c r="BM175" s="4"/>
+      <c r="BN175" s="4"/>
+    </row>
+    <row r="176" spans="3:66" x14ac:dyDescent="0.2">
       <c r="C176" s="4"/>
       <c r="D176" s="4"/>
       <c r="E176" s="4"/>
@@ -13569,8 +14035,10 @@
       <c r="BJ176" s="4"/>
       <c r="BK176" s="4"/>
       <c r="BL176" s="4"/>
-    </row>
-    <row r="177" spans="3:64" x14ac:dyDescent="0.2">
+      <c r="BM176" s="4"/>
+      <c r="BN176" s="4"/>
+    </row>
+    <row r="177" spans="3:66" x14ac:dyDescent="0.2">
       <c r="C177" s="4"/>
       <c r="D177" s="4"/>
       <c r="E177" s="4"/>
@@ -13633,8 +14101,10 @@
       <c r="BJ177" s="4"/>
       <c r="BK177" s="4"/>
       <c r="BL177" s="4"/>
-    </row>
-    <row r="178" spans="3:64" x14ac:dyDescent="0.2">
+      <c r="BM177" s="4"/>
+      <c r="BN177" s="4"/>
+    </row>
+    <row r="178" spans="3:66" x14ac:dyDescent="0.2">
       <c r="C178" s="4"/>
       <c r="D178" s="4"/>
       <c r="E178" s="4"/>
@@ -13697,8 +14167,10 @@
       <c r="BJ178" s="4"/>
       <c r="BK178" s="4"/>
       <c r="BL178" s="4"/>
-    </row>
-    <row r="179" spans="3:64" x14ac:dyDescent="0.2">
+      <c r="BM178" s="4"/>
+      <c r="BN178" s="4"/>
+    </row>
+    <row r="179" spans="3:66" x14ac:dyDescent="0.2">
       <c r="C179" s="4"/>
       <c r="D179" s="4"/>
       <c r="E179" s="4"/>
@@ -13761,8 +14233,10 @@
       <c r="BJ179" s="4"/>
       <c r="BK179" s="4"/>
       <c r="BL179" s="4"/>
-    </row>
-    <row r="180" spans="3:64" x14ac:dyDescent="0.2">
+      <c r="BM179" s="4"/>
+      <c r="BN179" s="4"/>
+    </row>
+    <row r="180" spans="3:66" x14ac:dyDescent="0.2">
       <c r="C180" s="4"/>
       <c r="D180" s="4"/>
       <c r="E180" s="4"/>
@@ -13825,8 +14299,10 @@
       <c r="BJ180" s="4"/>
       <c r="BK180" s="4"/>
       <c r="BL180" s="4"/>
-    </row>
-    <row r="181" spans="3:64" x14ac:dyDescent="0.2">
+      <c r="BM180" s="4"/>
+      <c r="BN180" s="4"/>
+    </row>
+    <row r="181" spans="3:66" x14ac:dyDescent="0.2">
       <c r="C181" s="4"/>
       <c r="D181" s="4"/>
       <c r="E181" s="4"/>
@@ -13889,8 +14365,10 @@
       <c r="BJ181" s="4"/>
       <c r="BK181" s="4"/>
       <c r="BL181" s="4"/>
-    </row>
-    <row r="182" spans="3:64" x14ac:dyDescent="0.2">
+      <c r="BM181" s="4"/>
+      <c r="BN181" s="4"/>
+    </row>
+    <row r="182" spans="3:66" x14ac:dyDescent="0.2">
       <c r="C182" s="4"/>
       <c r="D182" s="4"/>
       <c r="E182" s="4"/>
@@ -13953,8 +14431,10 @@
       <c r="BJ182" s="4"/>
       <c r="BK182" s="4"/>
       <c r="BL182" s="4"/>
-    </row>
-    <row r="183" spans="3:64" x14ac:dyDescent="0.2">
+      <c r="BM182" s="4"/>
+      <c r="BN182" s="4"/>
+    </row>
+    <row r="183" spans="3:66" x14ac:dyDescent="0.2">
       <c r="C183" s="4"/>
       <c r="D183" s="4"/>
       <c r="E183" s="4"/>
@@ -14017,8 +14497,10 @@
       <c r="BJ183" s="4"/>
       <c r="BK183" s="4"/>
       <c r="BL183" s="4"/>
-    </row>
-    <row r="184" spans="3:64" x14ac:dyDescent="0.2">
+      <c r="BM183" s="4"/>
+      <c r="BN183" s="4"/>
+    </row>
+    <row r="184" spans="3:66" x14ac:dyDescent="0.2">
       <c r="C184" s="4"/>
       <c r="D184" s="4"/>
       <c r="E184" s="4"/>
@@ -14081,8 +14563,10 @@
       <c r="BJ184" s="4"/>
       <c r="BK184" s="4"/>
       <c r="BL184" s="4"/>
-    </row>
-    <row r="185" spans="3:64" x14ac:dyDescent="0.2">
+      <c r="BM184" s="4"/>
+      <c r="BN184" s="4"/>
+    </row>
+    <row r="185" spans="3:66" x14ac:dyDescent="0.2">
       <c r="C185" s="4"/>
       <c r="D185" s="4"/>
       <c r="E185" s="4"/>
@@ -14145,8 +14629,10 @@
       <c r="BJ185" s="4"/>
       <c r="BK185" s="4"/>
       <c r="BL185" s="4"/>
-    </row>
-    <row r="186" spans="3:64" x14ac:dyDescent="0.2">
+      <c r="BM185" s="4"/>
+      <c r="BN185" s="4"/>
+    </row>
+    <row r="186" spans="3:66" x14ac:dyDescent="0.2">
       <c r="C186" s="4"/>
       <c r="D186" s="4"/>
       <c r="E186" s="4"/>
@@ -14209,8 +14695,10 @@
       <c r="BJ186" s="4"/>
       <c r="BK186" s="4"/>
       <c r="BL186" s="4"/>
-    </row>
-    <row r="187" spans="3:64" x14ac:dyDescent="0.2">
+      <c r="BM186" s="4"/>
+      <c r="BN186" s="4"/>
+    </row>
+    <row r="187" spans="3:66" x14ac:dyDescent="0.2">
       <c r="C187" s="4"/>
       <c r="D187" s="4"/>
       <c r="E187" s="4"/>
@@ -14273,8 +14761,10 @@
       <c r="BJ187" s="4"/>
       <c r="BK187" s="4"/>
       <c r="BL187" s="4"/>
-    </row>
-    <row r="188" spans="3:64" x14ac:dyDescent="0.2">
+      <c r="BM187" s="4"/>
+      <c r="BN187" s="4"/>
+    </row>
+    <row r="188" spans="3:66" x14ac:dyDescent="0.2">
       <c r="C188" s="4"/>
       <c r="D188" s="4"/>
       <c r="E188" s="4"/>
@@ -14337,8 +14827,10 @@
       <c r="BJ188" s="4"/>
       <c r="BK188" s="4"/>
       <c r="BL188" s="4"/>
-    </row>
-    <row r="189" spans="3:64" x14ac:dyDescent="0.2">
+      <c r="BM188" s="4"/>
+      <c r="BN188" s="4"/>
+    </row>
+    <row r="189" spans="3:66" x14ac:dyDescent="0.2">
       <c r="C189" s="4"/>
       <c r="D189" s="4"/>
       <c r="E189" s="4"/>
@@ -14401,8 +14893,10 @@
       <c r="BJ189" s="4"/>
       <c r="BK189" s="4"/>
       <c r="BL189" s="4"/>
-    </row>
-    <row r="190" spans="3:64" x14ac:dyDescent="0.2">
+      <c r="BM189" s="4"/>
+      <c r="BN189" s="4"/>
+    </row>
+    <row r="190" spans="3:66" x14ac:dyDescent="0.2">
       <c r="C190" s="4"/>
       <c r="D190" s="4"/>
       <c r="E190" s="4"/>
@@ -14465,8 +14959,10 @@
       <c r="BJ190" s="4"/>
       <c r="BK190" s="4"/>
       <c r="BL190" s="4"/>
-    </row>
-    <row r="191" spans="3:64" x14ac:dyDescent="0.2">
+      <c r="BM190" s="4"/>
+      <c r="BN190" s="4"/>
+    </row>
+    <row r="191" spans="3:66" x14ac:dyDescent="0.2">
       <c r="C191" s="4"/>
       <c r="D191" s="4"/>
       <c r="E191" s="4"/>
@@ -14529,8 +15025,10 @@
       <c r="BJ191" s="4"/>
       <c r="BK191" s="4"/>
       <c r="BL191" s="4"/>
-    </row>
-    <row r="192" spans="3:64" x14ac:dyDescent="0.2">
+      <c r="BM191" s="4"/>
+      <c r="BN191" s="4"/>
+    </row>
+    <row r="192" spans="3:66" x14ac:dyDescent="0.2">
       <c r="C192" s="4"/>
       <c r="D192" s="4"/>
       <c r="E192" s="4"/>
@@ -14593,8 +15091,10 @@
       <c r="BJ192" s="4"/>
       <c r="BK192" s="4"/>
       <c r="BL192" s="4"/>
-    </row>
-    <row r="193" spans="3:64" x14ac:dyDescent="0.2">
+      <c r="BM192" s="4"/>
+      <c r="BN192" s="4"/>
+    </row>
+    <row r="193" spans="3:66" x14ac:dyDescent="0.2">
       <c r="C193" s="4"/>
       <c r="D193" s="4"/>
       <c r="E193" s="4"/>
@@ -14657,8 +15157,10 @@
       <c r="BJ193" s="4"/>
       <c r="BK193" s="4"/>
       <c r="BL193" s="4"/>
-    </row>
-    <row r="194" spans="3:64" x14ac:dyDescent="0.2">
+      <c r="BM193" s="4"/>
+      <c r="BN193" s="4"/>
+    </row>
+    <row r="194" spans="3:66" x14ac:dyDescent="0.2">
       <c r="C194" s="4"/>
       <c r="D194" s="4"/>
       <c r="E194" s="4"/>
@@ -14721,8 +15223,10 @@
       <c r="BJ194" s="4"/>
       <c r="BK194" s="4"/>
       <c r="BL194" s="4"/>
-    </row>
-    <row r="195" spans="3:64" x14ac:dyDescent="0.2">
+      <c r="BM194" s="4"/>
+      <c r="BN194" s="4"/>
+    </row>
+    <row r="195" spans="3:66" x14ac:dyDescent="0.2">
       <c r="C195" s="4"/>
       <c r="D195" s="4"/>
       <c r="E195" s="4"/>
@@ -14785,8 +15289,10 @@
       <c r="BJ195" s="4"/>
       <c r="BK195" s="4"/>
       <c r="BL195" s="4"/>
-    </row>
-    <row r="196" spans="3:64" x14ac:dyDescent="0.2">
+      <c r="BM195" s="4"/>
+      <c r="BN195" s="4"/>
+    </row>
+    <row r="196" spans="3:66" x14ac:dyDescent="0.2">
       <c r="C196" s="4"/>
       <c r="D196" s="4"/>
       <c r="E196" s="4"/>
@@ -14849,8 +15355,10 @@
       <c r="BJ196" s="4"/>
       <c r="BK196" s="4"/>
       <c r="BL196" s="4"/>
-    </row>
-    <row r="197" spans="3:64" x14ac:dyDescent="0.2">
+      <c r="BM196" s="4"/>
+      <c r="BN196" s="4"/>
+    </row>
+    <row r="197" spans="3:66" x14ac:dyDescent="0.2">
       <c r="C197" s="4"/>
       <c r="D197" s="4"/>
       <c r="E197" s="4"/>
@@ -14913,8 +15421,10 @@
       <c r="BJ197" s="4"/>
       <c r="BK197" s="4"/>
       <c r="BL197" s="4"/>
-    </row>
-    <row r="198" spans="3:64" x14ac:dyDescent="0.2">
+      <c r="BM197" s="4"/>
+      <c r="BN197" s="4"/>
+    </row>
+    <row r="198" spans="3:66" x14ac:dyDescent="0.2">
       <c r="C198" s="4"/>
       <c r="D198" s="4"/>
       <c r="E198" s="4"/>
@@ -14977,8 +15487,10 @@
       <c r="BJ198" s="4"/>
       <c r="BK198" s="4"/>
       <c r="BL198" s="4"/>
-    </row>
-    <row r="199" spans="3:64" x14ac:dyDescent="0.2">
+      <c r="BM198" s="4"/>
+      <c r="BN198" s="4"/>
+    </row>
+    <row r="199" spans="3:66" x14ac:dyDescent="0.2">
       <c r="C199" s="4"/>
       <c r="D199" s="4"/>
       <c r="E199" s="4"/>
@@ -15041,8 +15553,10 @@
       <c r="BJ199" s="4"/>
       <c r="BK199" s="4"/>
       <c r="BL199" s="4"/>
-    </row>
-    <row r="200" spans="3:64" x14ac:dyDescent="0.2">
+      <c r="BM199" s="4"/>
+      <c r="BN199" s="4"/>
+    </row>
+    <row r="200" spans="3:66" x14ac:dyDescent="0.2">
       <c r="C200" s="4"/>
       <c r="D200" s="4"/>
       <c r="E200" s="4"/>
@@ -15105,8 +15619,10 @@
       <c r="BJ200" s="4"/>
       <c r="BK200" s="4"/>
       <c r="BL200" s="4"/>
-    </row>
-    <row r="201" spans="3:64" x14ac:dyDescent="0.2">
+      <c r="BM200" s="4"/>
+      <c r="BN200" s="4"/>
+    </row>
+    <row r="201" spans="3:66" x14ac:dyDescent="0.2">
       <c r="C201" s="4"/>
       <c r="D201" s="4"/>
       <c r="E201" s="4"/>
@@ -15169,8 +15685,10 @@
       <c r="BJ201" s="4"/>
       <c r="BK201" s="4"/>
       <c r="BL201" s="4"/>
-    </row>
-    <row r="202" spans="3:64" x14ac:dyDescent="0.2">
+      <c r="BM201" s="4"/>
+      <c r="BN201" s="4"/>
+    </row>
+    <row r="202" spans="3:66" x14ac:dyDescent="0.2">
       <c r="C202" s="4"/>
       <c r="D202" s="4"/>
       <c r="E202" s="4"/>
@@ -15233,8 +15751,10 @@
       <c r="BJ202" s="4"/>
       <c r="BK202" s="4"/>
       <c r="BL202" s="4"/>
-    </row>
-    <row r="203" spans="3:64" x14ac:dyDescent="0.2">
+      <c r="BM202" s="4"/>
+      <c r="BN202" s="4"/>
+    </row>
+    <row r="203" spans="3:66" x14ac:dyDescent="0.2">
       <c r="C203" s="4"/>
       <c r="D203" s="4"/>
       <c r="E203" s="4"/>
@@ -15297,8 +15817,10 @@
       <c r="BJ203" s="4"/>
       <c r="BK203" s="4"/>
       <c r="BL203" s="4"/>
-    </row>
-    <row r="204" spans="3:64" x14ac:dyDescent="0.2">
+      <c r="BM203" s="4"/>
+      <c r="BN203" s="4"/>
+    </row>
+    <row r="204" spans="3:66" x14ac:dyDescent="0.2">
       <c r="C204" s="4"/>
       <c r="D204" s="4"/>
       <c r="E204" s="4"/>
@@ -15361,8 +15883,10 @@
       <c r="BJ204" s="4"/>
       <c r="BK204" s="4"/>
       <c r="BL204" s="4"/>
-    </row>
-    <row r="205" spans="3:64" x14ac:dyDescent="0.2">
+      <c r="BM204" s="4"/>
+      <c r="BN204" s="4"/>
+    </row>
+    <row r="205" spans="3:66" x14ac:dyDescent="0.2">
       <c r="C205" s="4"/>
       <c r="D205" s="4"/>
       <c r="E205" s="4"/>
@@ -15425,8 +15949,10 @@
       <c r="BJ205" s="4"/>
       <c r="BK205" s="4"/>
       <c r="BL205" s="4"/>
-    </row>
-    <row r="206" spans="3:64" x14ac:dyDescent="0.2">
+      <c r="BM205" s="4"/>
+      <c r="BN205" s="4"/>
+    </row>
+    <row r="206" spans="3:66" x14ac:dyDescent="0.2">
       <c r="C206" s="4"/>
       <c r="D206" s="4"/>
       <c r="E206" s="4"/>
@@ -15489,8 +16015,10 @@
       <c r="BJ206" s="4"/>
       <c r="BK206" s="4"/>
       <c r="BL206" s="4"/>
-    </row>
-    <row r="207" spans="3:64" x14ac:dyDescent="0.2">
+      <c r="BM206" s="4"/>
+      <c r="BN206" s="4"/>
+    </row>
+    <row r="207" spans="3:66" x14ac:dyDescent="0.2">
       <c r="C207" s="4"/>
       <c r="D207" s="4"/>
       <c r="E207" s="4"/>
@@ -15553,8 +16081,10 @@
       <c r="BJ207" s="4"/>
       <c r="BK207" s="4"/>
       <c r="BL207" s="4"/>
-    </row>
-    <row r="208" spans="3:64" x14ac:dyDescent="0.2">
+      <c r="BM207" s="4"/>
+      <c r="BN207" s="4"/>
+    </row>
+    <row r="208" spans="3:66" x14ac:dyDescent="0.2">
       <c r="C208" s="4"/>
       <c r="D208" s="4"/>
       <c r="E208" s="4"/>
@@ -15617,8 +16147,10 @@
       <c r="BJ208" s="4"/>
       <c r="BK208" s="4"/>
       <c r="BL208" s="4"/>
-    </row>
-    <row r="209" spans="3:64" x14ac:dyDescent="0.2">
+      <c r="BM208" s="4"/>
+      <c r="BN208" s="4"/>
+    </row>
+    <row r="209" spans="3:66" x14ac:dyDescent="0.2">
       <c r="C209" s="4"/>
       <c r="D209" s="4"/>
       <c r="E209" s="4"/>
@@ -15681,8 +16213,10 @@
       <c r="BJ209" s="4"/>
       <c r="BK209" s="4"/>
       <c r="BL209" s="4"/>
-    </row>
-    <row r="210" spans="3:64" x14ac:dyDescent="0.2">
+      <c r="BM209" s="4"/>
+      <c r="BN209" s="4"/>
+    </row>
+    <row r="210" spans="3:66" x14ac:dyDescent="0.2">
       <c r="C210" s="4"/>
       <c r="D210" s="4"/>
       <c r="E210" s="4"/>
@@ -15745,8 +16279,10 @@
       <c r="BJ210" s="4"/>
       <c r="BK210" s="4"/>
       <c r="BL210" s="4"/>
-    </row>
-    <row r="211" spans="3:64" x14ac:dyDescent="0.2">
+      <c r="BM210" s="4"/>
+      <c r="BN210" s="4"/>
+    </row>
+    <row r="211" spans="3:66" x14ac:dyDescent="0.2">
       <c r="C211" s="4"/>
       <c r="D211" s="4"/>
       <c r="E211" s="4"/>
@@ -15809,8 +16345,10 @@
       <c r="BJ211" s="4"/>
       <c r="BK211" s="4"/>
       <c r="BL211" s="4"/>
-    </row>
-    <row r="212" spans="3:64" x14ac:dyDescent="0.2">
+      <c r="BM211" s="4"/>
+      <c r="BN211" s="4"/>
+    </row>
+    <row r="212" spans="3:66" x14ac:dyDescent="0.2">
       <c r="C212" s="4"/>
       <c r="D212" s="4"/>
       <c r="E212" s="4"/>
@@ -15873,8 +16411,10 @@
       <c r="BJ212" s="4"/>
       <c r="BK212" s="4"/>
       <c r="BL212" s="4"/>
-    </row>
-    <row r="213" spans="3:64" x14ac:dyDescent="0.2">
+      <c r="BM212" s="4"/>
+      <c r="BN212" s="4"/>
+    </row>
+    <row r="213" spans="3:66" x14ac:dyDescent="0.2">
       <c r="C213" s="4"/>
       <c r="D213" s="4"/>
       <c r="E213" s="4"/>
@@ -15937,8 +16477,10 @@
       <c r="BJ213" s="4"/>
       <c r="BK213" s="4"/>
       <c r="BL213" s="4"/>
-    </row>
-    <row r="214" spans="3:64" x14ac:dyDescent="0.2">
+      <c r="BM213" s="4"/>
+      <c r="BN213" s="4"/>
+    </row>
+    <row r="214" spans="3:66" x14ac:dyDescent="0.2">
       <c r="C214" s="4"/>
       <c r="D214" s="4"/>
       <c r="E214" s="4"/>
@@ -16001,8 +16543,10 @@
       <c r="BJ214" s="4"/>
       <c r="BK214" s="4"/>
       <c r="BL214" s="4"/>
-    </row>
-    <row r="215" spans="3:64" x14ac:dyDescent="0.2">
+      <c r="BM214" s="4"/>
+      <c r="BN214" s="4"/>
+    </row>
+    <row r="215" spans="3:66" x14ac:dyDescent="0.2">
       <c r="C215" s="4"/>
       <c r="D215" s="4"/>
       <c r="E215" s="4"/>
@@ -16065,8 +16609,10 @@
       <c r="BJ215" s="4"/>
       <c r="BK215" s="4"/>
       <c r="BL215" s="4"/>
-    </row>
-    <row r="216" spans="3:64" x14ac:dyDescent="0.2">
+      <c r="BM215" s="4"/>
+      <c r="BN215" s="4"/>
+    </row>
+    <row r="216" spans="3:66" x14ac:dyDescent="0.2">
       <c r="C216" s="4"/>
       <c r="D216" s="4"/>
       <c r="E216" s="4"/>
@@ -16129,8 +16675,10 @@
       <c r="BJ216" s="4"/>
       <c r="BK216" s="4"/>
       <c r="BL216" s="4"/>
-    </row>
-    <row r="217" spans="3:64" x14ac:dyDescent="0.2">
+      <c r="BM216" s="4"/>
+      <c r="BN216" s="4"/>
+    </row>
+    <row r="217" spans="3:66" x14ac:dyDescent="0.2">
       <c r="C217" s="4"/>
       <c r="D217" s="4"/>
       <c r="E217" s="4"/>
@@ -16193,8 +16741,10 @@
       <c r="BJ217" s="4"/>
       <c r="BK217" s="4"/>
       <c r="BL217" s="4"/>
-    </row>
-    <row r="218" spans="3:64" x14ac:dyDescent="0.2">
+      <c r="BM217" s="4"/>
+      <c r="BN217" s="4"/>
+    </row>
+    <row r="218" spans="3:66" x14ac:dyDescent="0.2">
       <c r="C218" s="4"/>
       <c r="D218" s="4"/>
       <c r="E218" s="4"/>
@@ -16257,8 +16807,10 @@
       <c r="BJ218" s="4"/>
       <c r="BK218" s="4"/>
       <c r="BL218" s="4"/>
-    </row>
-    <row r="219" spans="3:64" x14ac:dyDescent="0.2">
+      <c r="BM218" s="4"/>
+      <c r="BN218" s="4"/>
+    </row>
+    <row r="219" spans="3:66" x14ac:dyDescent="0.2">
       <c r="C219" s="4"/>
       <c r="D219" s="4"/>
       <c r="E219" s="4"/>
@@ -16321,8 +16873,10 @@
       <c r="BJ219" s="4"/>
       <c r="BK219" s="4"/>
       <c r="BL219" s="4"/>
-    </row>
-    <row r="220" spans="3:64" x14ac:dyDescent="0.2">
+      <c r="BM219" s="4"/>
+      <c r="BN219" s="4"/>
+    </row>
+    <row r="220" spans="3:66" x14ac:dyDescent="0.2">
       <c r="C220" s="4"/>
       <c r="D220" s="4"/>
       <c r="E220" s="4"/>
@@ -16385,8 +16939,10 @@
       <c r="BJ220" s="4"/>
       <c r="BK220" s="4"/>
       <c r="BL220" s="4"/>
-    </row>
-    <row r="221" spans="3:64" x14ac:dyDescent="0.2">
+      <c r="BM220" s="4"/>
+      <c r="BN220" s="4"/>
+    </row>
+    <row r="221" spans="3:66" x14ac:dyDescent="0.2">
       <c r="C221" s="4"/>
       <c r="D221" s="4"/>
       <c r="E221" s="4"/>
@@ -16449,8 +17005,10 @@
       <c r="BJ221" s="4"/>
       <c r="BK221" s="4"/>
       <c r="BL221" s="4"/>
-    </row>
-    <row r="222" spans="3:64" x14ac:dyDescent="0.2">
+      <c r="BM221" s="4"/>
+      <c r="BN221" s="4"/>
+    </row>
+    <row r="222" spans="3:66" x14ac:dyDescent="0.2">
       <c r="C222" s="4"/>
       <c r="D222" s="4"/>
       <c r="E222" s="4"/>
@@ -16513,8 +17071,10 @@
       <c r="BJ222" s="4"/>
       <c r="BK222" s="4"/>
       <c r="BL222" s="4"/>
-    </row>
-    <row r="223" spans="3:64" x14ac:dyDescent="0.2">
+      <c r="BM222" s="4"/>
+      <c r="BN222" s="4"/>
+    </row>
+    <row r="223" spans="3:66" x14ac:dyDescent="0.2">
       <c r="C223" s="4"/>
       <c r="D223" s="4"/>
       <c r="E223" s="4"/>
@@ -16577,8 +17137,10 @@
       <c r="BJ223" s="4"/>
       <c r="BK223" s="4"/>
       <c r="BL223" s="4"/>
-    </row>
-    <row r="224" spans="3:64" x14ac:dyDescent="0.2">
+      <c r="BM223" s="4"/>
+      <c r="BN223" s="4"/>
+    </row>
+    <row r="224" spans="3:66" x14ac:dyDescent="0.2">
       <c r="C224" s="4"/>
       <c r="D224" s="4"/>
       <c r="E224" s="4"/>
@@ -16641,8 +17203,10 @@
       <c r="BJ224" s="4"/>
       <c r="BK224" s="4"/>
       <c r="BL224" s="4"/>
-    </row>
-    <row r="225" spans="3:64" x14ac:dyDescent="0.2">
+      <c r="BM224" s="4"/>
+      <c r="BN224" s="4"/>
+    </row>
+    <row r="225" spans="3:66" x14ac:dyDescent="0.2">
       <c r="C225" s="4"/>
       <c r="D225" s="4"/>
       <c r="E225" s="4"/>
@@ -16705,8 +17269,10 @@
       <c r="BJ225" s="4"/>
       <c r="BK225" s="4"/>
       <c r="BL225" s="4"/>
-    </row>
-    <row r="226" spans="3:64" x14ac:dyDescent="0.2">
+      <c r="BM225" s="4"/>
+      <c r="BN225" s="4"/>
+    </row>
+    <row r="226" spans="3:66" x14ac:dyDescent="0.2">
       <c r="C226" s="4"/>
       <c r="D226" s="4"/>
       <c r="E226" s="4"/>
@@ -16769,8 +17335,10 @@
       <c r="BJ226" s="4"/>
       <c r="BK226" s="4"/>
       <c r="BL226" s="4"/>
-    </row>
-    <row r="227" spans="3:64" x14ac:dyDescent="0.2">
+      <c r="BM226" s="4"/>
+      <c r="BN226" s="4"/>
+    </row>
+    <row r="227" spans="3:66" x14ac:dyDescent="0.2">
       <c r="C227" s="4"/>
       <c r="D227" s="4"/>
       <c r="E227" s="4"/>
@@ -16833,8 +17401,10 @@
       <c r="BJ227" s="4"/>
       <c r="BK227" s="4"/>
       <c r="BL227" s="4"/>
-    </row>
-    <row r="228" spans="3:64" x14ac:dyDescent="0.2">
+      <c r="BM227" s="4"/>
+      <c r="BN227" s="4"/>
+    </row>
+    <row r="228" spans="3:66" x14ac:dyDescent="0.2">
       <c r="C228" s="4"/>
       <c r="D228" s="4"/>
       <c r="E228" s="4"/>
@@ -16897,8 +17467,10 @@
       <c r="BJ228" s="4"/>
       <c r="BK228" s="4"/>
       <c r="BL228" s="4"/>
-    </row>
-    <row r="229" spans="3:64" x14ac:dyDescent="0.2">
+      <c r="BM228" s="4"/>
+      <c r="BN228" s="4"/>
+    </row>
+    <row r="229" spans="3:66" x14ac:dyDescent="0.2">
       <c r="C229" s="4"/>
       <c r="D229" s="4"/>
       <c r="E229" s="4"/>
@@ -16961,8 +17533,10 @@
       <c r="BJ229" s="4"/>
       <c r="BK229" s="4"/>
       <c r="BL229" s="4"/>
-    </row>
-    <row r="230" spans="3:64" x14ac:dyDescent="0.2">
+      <c r="BM229" s="4"/>
+      <c r="BN229" s="4"/>
+    </row>
+    <row r="230" spans="3:66" x14ac:dyDescent="0.2">
       <c r="C230" s="4"/>
       <c r="D230" s="4"/>
       <c r="E230" s="4"/>
@@ -17025,8 +17599,10 @@
       <c r="BJ230" s="4"/>
       <c r="BK230" s="4"/>
       <c r="BL230" s="4"/>
-    </row>
-    <row r="231" spans="3:64" x14ac:dyDescent="0.2">
+      <c r="BM230" s="4"/>
+      <c r="BN230" s="4"/>
+    </row>
+    <row r="231" spans="3:66" x14ac:dyDescent="0.2">
       <c r="C231" s="4"/>
       <c r="D231" s="4"/>
       <c r="E231" s="4"/>
@@ -17089,8 +17665,10 @@
       <c r="BJ231" s="4"/>
       <c r="BK231" s="4"/>
       <c r="BL231" s="4"/>
-    </row>
-    <row r="232" spans="3:64" x14ac:dyDescent="0.2">
+      <c r="BM231" s="4"/>
+      <c r="BN231" s="4"/>
+    </row>
+    <row r="232" spans="3:66" x14ac:dyDescent="0.2">
       <c r="C232" s="4"/>
       <c r="D232" s="4"/>
       <c r="E232" s="4"/>
@@ -17153,8 +17731,10 @@
       <c r="BJ232" s="4"/>
       <c r="BK232" s="4"/>
       <c r="BL232" s="4"/>
-    </row>
-    <row r="233" spans="3:64" x14ac:dyDescent="0.2">
+      <c r="BM232" s="4"/>
+      <c r="BN232" s="4"/>
+    </row>
+    <row r="233" spans="3:66" x14ac:dyDescent="0.2">
       <c r="C233" s="4"/>
       <c r="D233" s="4"/>
       <c r="E233" s="4"/>
@@ -17217,8 +17797,10 @@
       <c r="BJ233" s="4"/>
       <c r="BK233" s="4"/>
       <c r="BL233" s="4"/>
-    </row>
-    <row r="234" spans="3:64" x14ac:dyDescent="0.2">
+      <c r="BM233" s="4"/>
+      <c r="BN233" s="4"/>
+    </row>
+    <row r="234" spans="3:66" x14ac:dyDescent="0.2">
       <c r="C234" s="4"/>
       <c r="D234" s="4"/>
       <c r="E234" s="4"/>
@@ -17281,8 +17863,10 @@
       <c r="BJ234" s="4"/>
       <c r="BK234" s="4"/>
       <c r="BL234" s="4"/>
-    </row>
-    <row r="235" spans="3:64" x14ac:dyDescent="0.2">
+      <c r="BM234" s="4"/>
+      <c r="BN234" s="4"/>
+    </row>
+    <row r="235" spans="3:66" x14ac:dyDescent="0.2">
       <c r="C235" s="4"/>
       <c r="D235" s="4"/>
       <c r="E235" s="4"/>
@@ -17345,8 +17929,10 @@
       <c r="BJ235" s="4"/>
       <c r="BK235" s="4"/>
       <c r="BL235" s="4"/>
-    </row>
-    <row r="236" spans="3:64" x14ac:dyDescent="0.2">
+      <c r="BM235" s="4"/>
+      <c r="BN235" s="4"/>
+    </row>
+    <row r="236" spans="3:66" x14ac:dyDescent="0.2">
       <c r="C236" s="4"/>
       <c r="D236" s="4"/>
       <c r="E236" s="4"/>
@@ -17409,8 +17995,10 @@
       <c r="BJ236" s="4"/>
       <c r="BK236" s="4"/>
       <c r="BL236" s="4"/>
-    </row>
-    <row r="237" spans="3:64" x14ac:dyDescent="0.2">
+      <c r="BM236" s="4"/>
+      <c r="BN236" s="4"/>
+    </row>
+    <row r="237" spans="3:66" x14ac:dyDescent="0.2">
       <c r="C237" s="4"/>
       <c r="D237" s="4"/>
       <c r="E237" s="4"/>
@@ -17473,8 +18061,10 @@
       <c r="BJ237" s="4"/>
       <c r="BK237" s="4"/>
       <c r="BL237" s="4"/>
-    </row>
-    <row r="238" spans="3:64" x14ac:dyDescent="0.2">
+      <c r="BM237" s="4"/>
+      <c r="BN237" s="4"/>
+    </row>
+    <row r="238" spans="3:66" x14ac:dyDescent="0.2">
       <c r="C238" s="4"/>
       <c r="D238" s="4"/>
       <c r="E238" s="4"/>
@@ -17537,8 +18127,10 @@
       <c r="BJ238" s="4"/>
       <c r="BK238" s="4"/>
       <c r="BL238" s="4"/>
-    </row>
-    <row r="239" spans="3:64" x14ac:dyDescent="0.2">
+      <c r="BM238" s="4"/>
+      <c r="BN238" s="4"/>
+    </row>
+    <row r="239" spans="3:66" x14ac:dyDescent="0.2">
       <c r="C239" s="4"/>
       <c r="D239" s="4"/>
       <c r="E239" s="4"/>
@@ -17601,8 +18193,10 @@
       <c r="BJ239" s="4"/>
       <c r="BK239" s="4"/>
       <c r="BL239" s="4"/>
-    </row>
-    <row r="240" spans="3:64" x14ac:dyDescent="0.2">
+      <c r="BM239" s="4"/>
+      <c r="BN239" s="4"/>
+    </row>
+    <row r="240" spans="3:66" x14ac:dyDescent="0.2">
       <c r="C240" s="4"/>
       <c r="D240" s="4"/>
       <c r="E240" s="4"/>
@@ -17665,8 +18259,10 @@
       <c r="BJ240" s="4"/>
       <c r="BK240" s="4"/>
       <c r="BL240" s="4"/>
-    </row>
-    <row r="241" spans="3:64" x14ac:dyDescent="0.2">
+      <c r="BM240" s="4"/>
+      <c r="BN240" s="4"/>
+    </row>
+    <row r="241" spans="3:66" x14ac:dyDescent="0.2">
       <c r="C241" s="4"/>
       <c r="D241" s="4"/>
       <c r="E241" s="4"/>
@@ -17729,8 +18325,10 @@
       <c r="BJ241" s="4"/>
       <c r="BK241" s="4"/>
       <c r="BL241" s="4"/>
-    </row>
-    <row r="242" spans="3:64" x14ac:dyDescent="0.2">
+      <c r="BM241" s="4"/>
+      <c r="BN241" s="4"/>
+    </row>
+    <row r="242" spans="3:66" x14ac:dyDescent="0.2">
       <c r="C242" s="4"/>
       <c r="D242" s="4"/>
       <c r="E242" s="4"/>
@@ -17793,8 +18391,10 @@
       <c r="BJ242" s="4"/>
       <c r="BK242" s="4"/>
       <c r="BL242" s="4"/>
-    </row>
-    <row r="243" spans="3:64" x14ac:dyDescent="0.2">
+      <c r="BM242" s="4"/>
+      <c r="BN242" s="4"/>
+    </row>
+    <row r="243" spans="3:66" x14ac:dyDescent="0.2">
       <c r="C243" s="4"/>
       <c r="D243" s="4"/>
       <c r="E243" s="4"/>
@@ -17857,8 +18457,10 @@
       <c r="BJ243" s="4"/>
       <c r="BK243" s="4"/>
       <c r="BL243" s="4"/>
-    </row>
-    <row r="244" spans="3:64" x14ac:dyDescent="0.2">
+      <c r="BM243" s="4"/>
+      <c r="BN243" s="4"/>
+    </row>
+    <row r="244" spans="3:66" x14ac:dyDescent="0.2">
       <c r="C244" s="4"/>
       <c r="D244" s="4"/>
       <c r="E244" s="4"/>
@@ -17921,8 +18523,10 @@
       <c r="BJ244" s="4"/>
       <c r="BK244" s="4"/>
       <c r="BL244" s="4"/>
-    </row>
-    <row r="245" spans="3:64" x14ac:dyDescent="0.2">
+      <c r="BM244" s="4"/>
+      <c r="BN244" s="4"/>
+    </row>
+    <row r="245" spans="3:66" x14ac:dyDescent="0.2">
       <c r="C245" s="4"/>
       <c r="D245" s="4"/>
       <c r="E245" s="4"/>
@@ -17985,8 +18589,10 @@
       <c r="BJ245" s="4"/>
       <c r="BK245" s="4"/>
       <c r="BL245" s="4"/>
-    </row>
-    <row r="246" spans="3:64" x14ac:dyDescent="0.2">
+      <c r="BM245" s="4"/>
+      <c r="BN245" s="4"/>
+    </row>
+    <row r="246" spans="3:66" x14ac:dyDescent="0.2">
       <c r="C246" s="4"/>
       <c r="D246" s="4"/>
       <c r="E246" s="4"/>
@@ -18049,8 +18655,10 @@
       <c r="BJ246" s="4"/>
       <c r="BK246" s="4"/>
       <c r="BL246" s="4"/>
-    </row>
-    <row r="247" spans="3:64" x14ac:dyDescent="0.2">
+      <c r="BM246" s="4"/>
+      <c r="BN246" s="4"/>
+    </row>
+    <row r="247" spans="3:66" x14ac:dyDescent="0.2">
       <c r="C247" s="4"/>
       <c r="D247" s="4"/>
       <c r="E247" s="4"/>
@@ -18113,8 +18721,10 @@
       <c r="BJ247" s="4"/>
       <c r="BK247" s="4"/>
       <c r="BL247" s="4"/>
-    </row>
-    <row r="248" spans="3:64" x14ac:dyDescent="0.2">
+      <c r="BM247" s="4"/>
+      <c r="BN247" s="4"/>
+    </row>
+    <row r="248" spans="3:66" x14ac:dyDescent="0.2">
       <c r="C248" s="4"/>
       <c r="D248" s="4"/>
       <c r="E248" s="4"/>
@@ -18177,8 +18787,10 @@
       <c r="BJ248" s="4"/>
       <c r="BK248" s="4"/>
       <c r="BL248" s="4"/>
-    </row>
-    <row r="249" spans="3:64" x14ac:dyDescent="0.2">
+      <c r="BM248" s="4"/>
+      <c r="BN248" s="4"/>
+    </row>
+    <row r="249" spans="3:66" x14ac:dyDescent="0.2">
       <c r="C249" s="4"/>
       <c r="D249" s="4"/>
       <c r="E249" s="4"/>
@@ -18241,8 +18853,10 @@
       <c r="BJ249" s="4"/>
       <c r="BK249" s="4"/>
       <c r="BL249" s="4"/>
-    </row>
-    <row r="250" spans="3:64" x14ac:dyDescent="0.2">
+      <c r="BM249" s="4"/>
+      <c r="BN249" s="4"/>
+    </row>
+    <row r="250" spans="3:66" x14ac:dyDescent="0.2">
       <c r="C250" s="4"/>
       <c r="D250" s="4"/>
       <c r="E250" s="4"/>
@@ -18305,8 +18919,10 @@
       <c r="BJ250" s="4"/>
       <c r="BK250" s="4"/>
       <c r="BL250" s="4"/>
-    </row>
-    <row r="251" spans="3:64" x14ac:dyDescent="0.2">
+      <c r="BM250" s="4"/>
+      <c r="BN250" s="4"/>
+    </row>
+    <row r="251" spans="3:66" x14ac:dyDescent="0.2">
       <c r="C251" s="4"/>
       <c r="D251" s="4"/>
       <c r="E251" s="4"/>
@@ -18369,8 +18985,10 @@
       <c r="BJ251" s="4"/>
       <c r="BK251" s="4"/>
       <c r="BL251" s="4"/>
-    </row>
-    <row r="252" spans="3:64" x14ac:dyDescent="0.2">
+      <c r="BM251" s="4"/>
+      <c r="BN251" s="4"/>
+    </row>
+    <row r="252" spans="3:66" x14ac:dyDescent="0.2">
       <c r="C252" s="4"/>
       <c r="D252" s="4"/>
       <c r="E252" s="4"/>
@@ -18433,8 +19051,10 @@
       <c r="BJ252" s="4"/>
       <c r="BK252" s="4"/>
       <c r="BL252" s="4"/>
-    </row>
-    <row r="253" spans="3:64" x14ac:dyDescent="0.2">
+      <c r="BM252" s="4"/>
+      <c r="BN252" s="4"/>
+    </row>
+    <row r="253" spans="3:66" x14ac:dyDescent="0.2">
       <c r="C253" s="4"/>
       <c r="D253" s="4"/>
       <c r="E253" s="4"/>
@@ -18497,8 +19117,10 @@
       <c r="BJ253" s="4"/>
       <c r="BK253" s="4"/>
       <c r="BL253" s="4"/>
-    </row>
-    <row r="254" spans="3:64" x14ac:dyDescent="0.2">
+      <c r="BM253" s="4"/>
+      <c r="BN253" s="4"/>
+    </row>
+    <row r="254" spans="3:66" x14ac:dyDescent="0.2">
       <c r="C254" s="4"/>
       <c r="D254" s="4"/>
       <c r="E254" s="4"/>
@@ -18561,8 +19183,10 @@
       <c r="BJ254" s="4"/>
       <c r="BK254" s="4"/>
       <c r="BL254" s="4"/>
-    </row>
-    <row r="255" spans="3:64" x14ac:dyDescent="0.2">
+      <c r="BM254" s="4"/>
+      <c r="BN254" s="4"/>
+    </row>
+    <row r="255" spans="3:66" x14ac:dyDescent="0.2">
       <c r="C255" s="4"/>
       <c r="D255" s="4"/>
       <c r="E255" s="4"/>
@@ -18625,8 +19249,10 @@
       <c r="BJ255" s="4"/>
       <c r="BK255" s="4"/>
       <c r="BL255" s="4"/>
-    </row>
-    <row r="256" spans="3:64" x14ac:dyDescent="0.2">
+      <c r="BM255" s="4"/>
+      <c r="BN255" s="4"/>
+    </row>
+    <row r="256" spans="3:66" x14ac:dyDescent="0.2">
       <c r="C256" s="4"/>
       <c r="D256" s="4"/>
       <c r="E256" s="4"/>
@@ -18689,8 +19315,10 @@
       <c r="BJ256" s="4"/>
       <c r="BK256" s="4"/>
       <c r="BL256" s="4"/>
-    </row>
-    <row r="257" spans="3:64" x14ac:dyDescent="0.2">
+      <c r="BM256" s="4"/>
+      <c r="BN256" s="4"/>
+    </row>
+    <row r="257" spans="3:66" x14ac:dyDescent="0.2">
       <c r="C257" s="4"/>
       <c r="D257" s="4"/>
       <c r="E257" s="4"/>
@@ -18753,8 +19381,10 @@
       <c r="BJ257" s="4"/>
       <c r="BK257" s="4"/>
       <c r="BL257" s="4"/>
-    </row>
-    <row r="258" spans="3:64" x14ac:dyDescent="0.2">
+      <c r="BM257" s="4"/>
+      <c r="BN257" s="4"/>
+    </row>
+    <row r="258" spans="3:66" x14ac:dyDescent="0.2">
       <c r="C258" s="4"/>
       <c r="D258" s="4"/>
       <c r="E258" s="4"/>
@@ -18817,8 +19447,10 @@
       <c r="BJ258" s="4"/>
       <c r="BK258" s="4"/>
       <c r="BL258" s="4"/>
-    </row>
-    <row r="259" spans="3:64" x14ac:dyDescent="0.2">
+      <c r="BM258" s="4"/>
+      <c r="BN258" s="4"/>
+    </row>
+    <row r="259" spans="3:66" x14ac:dyDescent="0.2">
       <c r="C259" s="4"/>
       <c r="D259" s="4"/>
       <c r="E259" s="4"/>
@@ -18881,8 +19513,10 @@
       <c r="BJ259" s="4"/>
       <c r="BK259" s="4"/>
       <c r="BL259" s="4"/>
-    </row>
-    <row r="260" spans="3:64" x14ac:dyDescent="0.2">
+      <c r="BM259" s="4"/>
+      <c r="BN259" s="4"/>
+    </row>
+    <row r="260" spans="3:66" x14ac:dyDescent="0.2">
       <c r="C260" s="4"/>
       <c r="D260" s="4"/>
       <c r="E260" s="4"/>
@@ -18945,8 +19579,10 @@
       <c r="BJ260" s="4"/>
       <c r="BK260" s="4"/>
       <c r="BL260" s="4"/>
-    </row>
-    <row r="261" spans="3:64" x14ac:dyDescent="0.2">
+      <c r="BM260" s="4"/>
+      <c r="BN260" s="4"/>
+    </row>
+    <row r="261" spans="3:66" x14ac:dyDescent="0.2">
       <c r="C261" s="4"/>
       <c r="D261" s="4"/>
       <c r="E261" s="4"/>
@@ -19009,8 +19645,10 @@
       <c r="BJ261" s="4"/>
       <c r="BK261" s="4"/>
       <c r="BL261" s="4"/>
-    </row>
-    <row r="262" spans="3:64" x14ac:dyDescent="0.2">
+      <c r="BM261" s="4"/>
+      <c r="BN261" s="4"/>
+    </row>
+    <row r="262" spans="3:66" x14ac:dyDescent="0.2">
       <c r="C262" s="4"/>
       <c r="D262" s="4"/>
       <c r="E262" s="4"/>
@@ -19073,8 +19711,10 @@
       <c r="BJ262" s="4"/>
       <c r="BK262" s="4"/>
       <c r="BL262" s="4"/>
-    </row>
-    <row r="263" spans="3:64" x14ac:dyDescent="0.2">
+      <c r="BM262" s="4"/>
+      <c r="BN262" s="4"/>
+    </row>
+    <row r="263" spans="3:66" x14ac:dyDescent="0.2">
       <c r="C263" s="4"/>
       <c r="D263" s="4"/>
       <c r="E263" s="4"/>
@@ -19137,8 +19777,10 @@
       <c r="BJ263" s="4"/>
       <c r="BK263" s="4"/>
       <c r="BL263" s="4"/>
-    </row>
-    <row r="264" spans="3:64" x14ac:dyDescent="0.2">
+      <c r="BM263" s="4"/>
+      <c r="BN263" s="4"/>
+    </row>
+    <row r="264" spans="3:66" x14ac:dyDescent="0.2">
       <c r="C264" s="4"/>
       <c r="D264" s="4"/>
       <c r="E264" s="4"/>
@@ -19201,8 +19843,10 @@
       <c r="BJ264" s="4"/>
       <c r="BK264" s="4"/>
       <c r="BL264" s="4"/>
-    </row>
-    <row r="265" spans="3:64" x14ac:dyDescent="0.2">
+      <c r="BM264" s="4"/>
+      <c r="BN264" s="4"/>
+    </row>
+    <row r="265" spans="3:66" x14ac:dyDescent="0.2">
       <c r="C265" s="4"/>
       <c r="D265" s="4"/>
       <c r="E265" s="4"/>
@@ -19265,8 +19909,10 @@
       <c r="BJ265" s="4"/>
       <c r="BK265" s="4"/>
       <c r="BL265" s="4"/>
-    </row>
-    <row r="266" spans="3:64" x14ac:dyDescent="0.2">
+      <c r="BM265" s="4"/>
+      <c r="BN265" s="4"/>
+    </row>
+    <row r="266" spans="3:66" x14ac:dyDescent="0.2">
       <c r="C266" s="4"/>
       <c r="D266" s="4"/>
       <c r="E266" s="4"/>
@@ -19329,8 +19975,10 @@
       <c r="BJ266" s="4"/>
       <c r="BK266" s="4"/>
       <c r="BL266" s="4"/>
-    </row>
-    <row r="267" spans="3:64" x14ac:dyDescent="0.2">
+      <c r="BM266" s="4"/>
+      <c r="BN266" s="4"/>
+    </row>
+    <row r="267" spans="3:66" x14ac:dyDescent="0.2">
       <c r="C267" s="4"/>
       <c r="D267" s="4"/>
       <c r="E267" s="4"/>
@@ -19393,8 +20041,10 @@
       <c r="BJ267" s="4"/>
       <c r="BK267" s="4"/>
       <c r="BL267" s="4"/>
-    </row>
-    <row r="268" spans="3:64" x14ac:dyDescent="0.2">
+      <c r="BM267" s="4"/>
+      <c r="BN267" s="4"/>
+    </row>
+    <row r="268" spans="3:66" x14ac:dyDescent="0.2">
       <c r="C268" s="4"/>
       <c r="D268" s="4"/>
       <c r="E268" s="4"/>
@@ -19457,8 +20107,10 @@
       <c r="BJ268" s="4"/>
       <c r="BK268" s="4"/>
       <c r="BL268" s="4"/>
-    </row>
-    <row r="269" spans="3:64" x14ac:dyDescent="0.2">
+      <c r="BM268" s="4"/>
+      <c r="BN268" s="4"/>
+    </row>
+    <row r="269" spans="3:66" x14ac:dyDescent="0.2">
       <c r="C269" s="4"/>
       <c r="D269" s="4"/>
       <c r="E269" s="4"/>
@@ -19521,6 +20173,8 @@
       <c r="BJ269" s="4"/>
       <c r="BK269" s="4"/>
       <c r="BL269" s="4"/>
+      <c r="BM269" s="4"/>
+      <c r="BN269" s="4"/>
     </row>
   </sheetData>
   <hyperlinks>

--- a/BC.MI.xlsx
+++ b/BC.MI.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\1.Finance\Anaylsen\Models\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{45421C9D-98E6-4156-AF49-6E609B834094}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6F04CD7B-779B-4176-8F3F-C6A61921F131}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="19095" yWindow="0" windowWidth="19410" windowHeight="20985" activeTab="1" xr2:uid="{6AFCE97C-0CAA-47F0-9D92-585A8A3029EA}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="75">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="83" uniqueCount="77">
   <si>
     <t>numbers in mio EUR</t>
   </si>
@@ -263,6 +263,12 @@
   <si>
     <t>CEO&amp;CD</t>
   </si>
+  <si>
+    <t>Retail Boutiques</t>
+  </si>
+  <si>
+    <t>Wholesale</t>
+  </si>
 </sst>
 </file>
 
@@ -271,13 +277,19 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="#,##0.0"/>
   </numFmts>
-  <fonts count="10" x14ac:knownFonts="1">
+  <fonts count="11" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
@@ -360,36 +372,41 @@
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="3" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="3" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="4" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="9" fontId="4" fillId="0" borderId="0" xfId="2" applyFont="1"/>
-    <xf numFmtId="9" fontId="7" fillId="0" borderId="0" xfId="2" applyFont="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="3" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="3" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="4" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="9" fontId="5" fillId="0" borderId="0" xfId="2" applyFont="1"/>
+    <xf numFmtId="9" fontId="8" fillId="0" borderId="0" xfId="2" applyFont="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="3" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="3" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -897,7 +914,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1334857E-06C9-4A6E-809B-B62D56C178F7}">
-  <dimension ref="A1:BO269"/>
+  <dimension ref="A1:BO271"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5.42578125" style="2" bestFit="1" customWidth="1"/>
@@ -1009,7 +1026,9 @@
         <v>13</v>
       </c>
       <c r="T3" s="4"/>
-      <c r="U3" s="4"/>
+      <c r="U3" s="20" t="s">
+        <v>72</v>
+      </c>
       <c r="V3" s="4"/>
       <c r="W3" s="4"/>
       <c r="X3" s="4"/>
@@ -1098,7 +1117,9 @@
         <v>46</v>
       </c>
       <c r="T4" s="4"/>
-      <c r="U4" s="4"/>
+      <c r="U4" s="4">
+        <v>60</v>
+      </c>
       <c r="V4" s="4"/>
       <c r="W4" s="4"/>
       <c r="X4" s="4"/>
@@ -1187,7 +1208,9 @@
         <v>35</v>
       </c>
       <c r="T5" s="4"/>
-      <c r="U5" s="4"/>
+      <c r="U5" s="4">
+        <v>39</v>
+      </c>
       <c r="V5" s="4"/>
       <c r="W5" s="4"/>
       <c r="X5" s="4"/>
@@ -1279,7 +1302,9 @@
         <v>58</v>
       </c>
       <c r="T6" s="4"/>
-      <c r="U6" s="4"/>
+      <c r="U6" s="4">
+        <v>65</v>
+      </c>
       <c r="V6" s="4"/>
       <c r="W6" s="4"/>
       <c r="X6" s="4"/>
@@ -1327,64 +1352,36 @@
       <c r="BN6" s="4"/>
     </row>
     <row r="7" spans="1:67" x14ac:dyDescent="0.2">
-      <c r="B7" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="C7" s="6">
-        <f t="shared" ref="C7:F7" si="2">+SUM(C3:C6)</f>
-        <v>0</v>
-      </c>
-      <c r="D7" s="6">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="E7" s="6">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="F7" s="6">
-        <f t="shared" si="2"/>
-        <v>152</v>
-      </c>
-      <c r="G7" s="6">
-        <f>+SUM(G3:G6)</f>
-        <v>153</v>
-      </c>
-      <c r="H7" s="6">
-        <f>+SUM(H3:H6)</f>
-        <v>0</v>
-      </c>
-      <c r="I7" s="6"/>
-      <c r="J7" s="6"/>
-      <c r="K7" s="6"/>
-      <c r="L7" s="6"/>
-      <c r="M7" s="6"/>
-      <c r="N7" s="6">
-        <f t="shared" ref="N7:S7" si="3">+SUM(N3:N6)</f>
-        <v>127</v>
-      </c>
-      <c r="O7" s="6">
-        <f t="shared" si="3"/>
+      <c r="B7" s="18" t="s">
+        <v>75</v>
+      </c>
+      <c r="C7" s="4"/>
+      <c r="D7" s="4"/>
+      <c r="E7" s="4"/>
+      <c r="F7" s="4"/>
+      <c r="G7" s="4"/>
+      <c r="H7" s="4"/>
+      <c r="I7" s="4"/>
+      <c r="J7" s="6">
         <v>136</v>
       </c>
-      <c r="P7" s="6">
-        <f t="shared" si="3"/>
-        <v>138</v>
-      </c>
-      <c r="Q7" s="6">
-        <f t="shared" si="3"/>
-        <v>144</v>
-      </c>
-      <c r="R7" s="6">
-        <f t="shared" si="3"/>
-        <v>149</v>
-      </c>
-      <c r="S7" s="6">
-        <f t="shared" si="3"/>
-        <v>152</v>
-      </c>
-      <c r="T7" s="6"/>
-      <c r="U7" s="4"/>
+      <c r="K7" s="6">
+        <v>141</v>
+      </c>
+      <c r="L7" s="4"/>
+      <c r="M7" s="4"/>
+      <c r="N7" s="4"/>
+      <c r="O7" s="4"/>
+      <c r="P7" s="4"/>
+      <c r="Q7" s="4"/>
+      <c r="R7" s="4"/>
+      <c r="S7" s="4"/>
+      <c r="T7" s="4">
+        <v>130</v>
+      </c>
+      <c r="U7" s="4">
+        <v>136</v>
+      </c>
       <c r="V7" s="4"/>
       <c r="W7" s="4"/>
       <c r="X7" s="4"/>
@@ -1432,64 +1429,32 @@
       <c r="BN7" s="4"/>
     </row>
     <row r="8" spans="1:67" x14ac:dyDescent="0.2">
-      <c r="B8" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="C8" s="7" t="e">
-        <f t="shared" ref="C8" si="4">+C16/C7</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="D8" s="7" t="e">
-        <f t="shared" ref="D8" si="5">+D16/D7</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="E8" s="7" t="e">
-        <f t="shared" ref="E8" si="6">+E16/E7</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="F8" s="7">
-        <f t="shared" ref="F8" si="7">+F16/F7</f>
-        <v>3.9176184210526315</v>
-      </c>
-      <c r="G8" s="7">
-        <f t="shared" ref="G8" si="8">+G16/G7</f>
-        <v>4.0566143790849676</v>
-      </c>
-      <c r="H8" s="7" t="e">
-        <f t="shared" ref="H8" si="9">+H16/H7</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="I8" s="7"/>
-      <c r="J8" s="7"/>
-      <c r="K8" s="7"/>
-      <c r="L8" s="7"/>
-      <c r="M8" s="6"/>
-      <c r="N8" s="7">
-        <f t="shared" ref="N8:R8" si="10">+N16/N7</f>
-        <v>4.3542992125984252</v>
-      </c>
-      <c r="O8" s="7">
-        <f t="shared" si="10"/>
-        <v>4.4688308823529406</v>
-      </c>
-      <c r="P8" s="7">
-        <f t="shared" si="10"/>
-        <v>3.9421231884057972</v>
-      </c>
-      <c r="Q8" s="7">
-        <f t="shared" si="10"/>
-        <v>4.9456875000000009</v>
-      </c>
-      <c r="R8" s="7">
-        <f t="shared" si="10"/>
-        <v>6.1725369127516787</v>
-      </c>
-      <c r="S8" s="7">
-        <f>+S16/S7</f>
-        <v>7.4961842105263159</v>
-      </c>
-      <c r="T8" s="6"/>
-      <c r="U8" s="4"/>
+      <c r="B8" s="18" t="s">
+        <v>76</v>
+      </c>
+      <c r="C8" s="4"/>
+      <c r="D8" s="4"/>
+      <c r="E8" s="4"/>
+      <c r="F8" s="4"/>
+      <c r="G8" s="4"/>
+      <c r="H8" s="4"/>
+      <c r="I8" s="4"/>
+      <c r="J8" s="4"/>
+      <c r="K8" s="4"/>
+      <c r="L8" s="4"/>
+      <c r="M8" s="4"/>
+      <c r="N8" s="4"/>
+      <c r="O8" s="4"/>
+      <c r="P8" s="4"/>
+      <c r="Q8" s="4"/>
+      <c r="R8" s="4"/>
+      <c r="S8" s="4"/>
+      <c r="T8" s="4">
+        <v>27</v>
+      </c>
+      <c r="U8" s="4">
+        <v>28</v>
+      </c>
       <c r="V8" s="4"/>
       <c r="W8" s="4"/>
       <c r="X8" s="4"/>
@@ -1537,25 +1502,68 @@
       <c r="BN8" s="4"/>
     </row>
     <row r="9" spans="1:67" x14ac:dyDescent="0.2">
-      <c r="C9" s="4"/>
-      <c r="D9" s="4"/>
-      <c r="E9" s="4"/>
-      <c r="F9" s="4"/>
-      <c r="G9" s="4"/>
-      <c r="H9" s="4"/>
-      <c r="I9" s="4"/>
-      <c r="J9" s="4"/>
-      <c r="K9" s="4"/>
+      <c r="B9" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="C9" s="6">
+        <f t="shared" ref="C9:F9" si="2">+SUM(C3:C6)</f>
+        <v>0</v>
+      </c>
+      <c r="D9" s="6">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="E9" s="6">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="F9" s="6">
+        <f t="shared" si="2"/>
+        <v>152</v>
+      </c>
+      <c r="G9" s="6">
+        <f>+SUM(G3:G6)</f>
+        <v>153</v>
+      </c>
+      <c r="H9" s="6">
+        <f>+SUM(H3:H6)</f>
+        <v>0</v>
+      </c>
+      <c r="I9" s="6"/>
+      <c r="J9" s="19"/>
+      <c r="K9" s="6"/>
       <c r="L9" s="4"/>
-      <c r="M9" s="4"/>
-      <c r="N9" s="4"/>
-      <c r="O9" s="4"/>
-      <c r="P9" s="4"/>
-      <c r="Q9" s="4"/>
-      <c r="R9" s="4"/>
-      <c r="S9" s="4"/>
-      <c r="T9" s="4"/>
-      <c r="U9" s="4"/>
+      <c r="M9" s="6"/>
+      <c r="N9" s="6">
+        <f t="shared" ref="N9:S9" si="3">+SUM(N3:N6)</f>
+        <v>127</v>
+      </c>
+      <c r="O9" s="6">
+        <f t="shared" si="3"/>
+        <v>136</v>
+      </c>
+      <c r="P9" s="6">
+        <f t="shared" si="3"/>
+        <v>138</v>
+      </c>
+      <c r="Q9" s="6">
+        <f t="shared" si="3"/>
+        <v>144</v>
+      </c>
+      <c r="R9" s="6">
+        <f t="shared" si="3"/>
+        <v>149</v>
+      </c>
+      <c r="S9" s="6">
+        <f t="shared" si="3"/>
+        <v>152</v>
+      </c>
+      <c r="T9" s="6">
+        <v>157</v>
+      </c>
+      <c r="U9" s="6">
+        <v>164</v>
+      </c>
       <c r="V9" s="4"/>
       <c r="W9" s="4"/>
       <c r="X9" s="4"/>
@@ -1604,247 +1612,230 @@
     </row>
     <row r="10" spans="1:67" x14ac:dyDescent="0.2">
       <c r="B10" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="C10" s="8"/>
-      <c r="D10" s="8"/>
-      <c r="E10" s="8">
-        <v>141.881</v>
-      </c>
-      <c r="F10" s="8">
-        <f>+S10-E10</f>
-        <v>157.499</v>
-      </c>
-      <c r="G10" s="8">
-        <v>152.959</v>
-      </c>
-      <c r="H10" s="8"/>
-      <c r="I10" s="8">
-        <v>243.21299999999999</v>
-      </c>
-      <c r="J10" s="8"/>
-      <c r="K10" s="8">
-        <v>255.58199999999999</v>
-      </c>
-      <c r="L10" s="8"/>
-      <c r="M10" s="8"/>
-      <c r="N10" s="8">
-        <v>163.70699999999999</v>
-      </c>
-      <c r="O10" s="8">
-        <v>176.9</v>
-      </c>
-      <c r="P10" s="8">
-        <v>173.078</v>
-      </c>
-      <c r="Q10" s="8">
-        <v>219.15</v>
-      </c>
-      <c r="R10" s="8">
-        <v>263.81400000000002</v>
-      </c>
-      <c r="S10" s="8">
-        <v>299.38</v>
-      </c>
-      <c r="T10" s="8">
-        <v>315.666</v>
-      </c>
-      <c r="U10" s="8">
-        <v>494.92</v>
-      </c>
-      <c r="V10" s="8"/>
-      <c r="W10" s="8"/>
-      <c r="X10" s="8"/>
-      <c r="Y10" s="8"/>
-      <c r="Z10" s="8"/>
-      <c r="AA10" s="8"/>
-      <c r="AB10" s="8"/>
-      <c r="AC10" s="8"/>
-      <c r="AD10" s="8"/>
-      <c r="AE10" s="8"/>
-      <c r="AF10" s="8"/>
-      <c r="AG10" s="8"/>
-      <c r="AH10" s="8"/>
-      <c r="AI10" s="8"/>
-      <c r="AJ10" s="8"/>
-      <c r="AK10" s="8"/>
-      <c r="AL10" s="8"/>
-      <c r="AM10" s="8"/>
-      <c r="AN10" s="8"/>
-      <c r="AO10" s="8"/>
-      <c r="AP10" s="8"/>
-      <c r="AQ10" s="8"/>
-      <c r="AR10" s="8"/>
-      <c r="AS10" s="8"/>
-      <c r="AT10" s="8"/>
-      <c r="AU10" s="8"/>
-      <c r="AV10" s="8"/>
-      <c r="AW10" s="8"/>
-      <c r="AX10" s="8"/>
-      <c r="AY10" s="8"/>
-      <c r="AZ10" s="8"/>
-      <c r="BA10" s="8"/>
-      <c r="BB10" s="8"/>
-      <c r="BC10" s="8"/>
-      <c r="BD10" s="8"/>
-      <c r="BE10" s="8"/>
-      <c r="BF10" s="8"/>
-      <c r="BG10" s="8"/>
-      <c r="BH10" s="8"/>
-      <c r="BI10" s="8"/>
-      <c r="BJ10" s="8"/>
-      <c r="BK10" s="8"/>
-      <c r="BL10" s="8"/>
-      <c r="BM10" s="8"/>
-      <c r="BN10" s="8"/>
-      <c r="BO10" s="8"/>
+        <v>62</v>
+      </c>
+      <c r="C10" s="7" t="e">
+        <f t="shared" ref="C10" si="4">+C18/C9</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="D10" s="7" t="e">
+        <f t="shared" ref="D10" si="5">+D18/D9</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="E10" s="7" t="e">
+        <f t="shared" ref="E10" si="6">+E18/E9</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="F10" s="7">
+        <f t="shared" ref="F10" si="7">+F18/F9</f>
+        <v>3.9176184210526315</v>
+      </c>
+      <c r="G10" s="7">
+        <f t="shared" ref="G10" si="8">+G18/G9</f>
+        <v>4.0566143790849676</v>
+      </c>
+      <c r="H10" s="7" t="e">
+        <f t="shared" ref="H10" si="9">+H18/H9</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="I10" s="7"/>
+      <c r="J10" s="7"/>
+      <c r="K10" s="7"/>
+      <c r="L10" s="7"/>
+      <c r="M10" s="6"/>
+      <c r="N10" s="7">
+        <f t="shared" ref="N10:R10" si="10">+N18/N9</f>
+        <v>4.3542992125984252</v>
+      </c>
+      <c r="O10" s="7">
+        <f t="shared" si="10"/>
+        <v>4.4688308823529406</v>
+      </c>
+      <c r="P10" s="7">
+        <f t="shared" si="10"/>
+        <v>3.9421231884057972</v>
+      </c>
+      <c r="Q10" s="7">
+        <f t="shared" si="10"/>
+        <v>4.9456875000000009</v>
+      </c>
+      <c r="R10" s="7">
+        <f t="shared" si="10"/>
+        <v>6.1725369127516787</v>
+      </c>
+      <c r="S10" s="7">
+        <f>+S18/S9</f>
+        <v>7.4961842105263159</v>
+      </c>
+      <c r="T10" s="7">
+        <f t="shared" ref="T10:U10" si="11">+T18/T9</f>
+        <v>8.1435668789808915</v>
+      </c>
+      <c r="U10" s="7">
+        <f t="shared" si="11"/>
+        <v>8.5850670731707321</v>
+      </c>
+      <c r="V10" s="4"/>
+      <c r="W10" s="4"/>
+      <c r="X10" s="4"/>
+      <c r="Y10" s="4"/>
+      <c r="Z10" s="4"/>
+      <c r="AA10" s="4"/>
+      <c r="AB10" s="4"/>
+      <c r="AC10" s="4"/>
+      <c r="AD10" s="4"/>
+      <c r="AE10" s="4"/>
+      <c r="AF10" s="4"/>
+      <c r="AG10" s="4"/>
+      <c r="AH10" s="4"/>
+      <c r="AI10" s="4"/>
+      <c r="AJ10" s="4"/>
+      <c r="AK10" s="4"/>
+      <c r="AL10" s="4"/>
+      <c r="AM10" s="4"/>
+      <c r="AN10" s="4"/>
+      <c r="AO10" s="4"/>
+      <c r="AP10" s="4"/>
+      <c r="AQ10" s="4"/>
+      <c r="AR10" s="4"/>
+      <c r="AS10" s="4"/>
+      <c r="AT10" s="4"/>
+      <c r="AU10" s="4"/>
+      <c r="AV10" s="4"/>
+      <c r="AW10" s="4"/>
+      <c r="AX10" s="4"/>
+      <c r="AY10" s="4"/>
+      <c r="AZ10" s="4"/>
+      <c r="BA10" s="4"/>
+      <c r="BB10" s="4"/>
+      <c r="BC10" s="4"/>
+      <c r="BD10" s="4"/>
+      <c r="BE10" s="4"/>
+      <c r="BF10" s="4"/>
+      <c r="BG10" s="4"/>
+      <c r="BH10" s="4"/>
+      <c r="BI10" s="4"/>
+      <c r="BJ10" s="4"/>
+      <c r="BK10" s="4"/>
+      <c r="BL10" s="4"/>
+      <c r="BM10" s="4"/>
+      <c r="BN10" s="4"/>
     </row>
     <row r="11" spans="1:67" x14ac:dyDescent="0.2">
-      <c r="B11" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="C11" s="8"/>
-      <c r="D11" s="8"/>
-      <c r="E11" s="8">
-        <v>60.887999999999998</v>
-      </c>
-      <c r="F11" s="8">
-        <f t="shared" ref="F11:F32" si="11">+S11-E11</f>
-        <v>67.963999999999999</v>
-      </c>
-      <c r="G11" s="8">
-        <v>68.093000000000004</v>
-      </c>
-      <c r="H11" s="8"/>
-      <c r="I11" s="16" t="s">
-        <v>72</v>
-      </c>
-      <c r="J11" s="8"/>
-      <c r="K11" s="16" t="s">
-        <v>72</v>
-      </c>
-      <c r="L11" s="8"/>
-      <c r="M11" s="8"/>
-      <c r="N11" s="8">
-        <v>88.22</v>
-      </c>
-      <c r="O11" s="8">
-        <v>89.72</v>
-      </c>
-      <c r="P11" s="8">
-        <v>68.322999999999993</v>
-      </c>
-      <c r="Q11" s="8">
-        <v>84.222999999999999</v>
-      </c>
-      <c r="R11" s="8">
-        <v>102.753</v>
-      </c>
-      <c r="S11" s="8">
-        <v>128.852</v>
-      </c>
-      <c r="T11" s="8">
-        <v>140.92099999999999</v>
-      </c>
-      <c r="U11" s="8">
-        <v>0</v>
-      </c>
-      <c r="V11" s="8"/>
-      <c r="W11" s="8"/>
-      <c r="X11" s="8"/>
-      <c r="Y11" s="8"/>
-      <c r="Z11" s="8"/>
-      <c r="AA11" s="8"/>
-      <c r="AB11" s="8"/>
-      <c r="AC11" s="8"/>
-      <c r="AD11" s="8"/>
-      <c r="AE11" s="8"/>
-      <c r="AF11" s="8"/>
-      <c r="AG11" s="8"/>
-      <c r="AH11" s="8"/>
-      <c r="AI11" s="8"/>
-      <c r="AJ11" s="8"/>
-      <c r="AK11" s="8"/>
-      <c r="AL11" s="8"/>
-      <c r="AM11" s="8"/>
-      <c r="AN11" s="8"/>
-      <c r="AO11" s="8"/>
-      <c r="AP11" s="8"/>
-      <c r="AQ11" s="8"/>
-      <c r="AR11" s="8"/>
-      <c r="AS11" s="8"/>
-      <c r="AT11" s="8"/>
-      <c r="AU11" s="8"/>
-      <c r="AV11" s="8"/>
-      <c r="AW11" s="8"/>
-      <c r="AX11" s="8"/>
-      <c r="AY11" s="8"/>
-      <c r="AZ11" s="8"/>
-      <c r="BA11" s="8"/>
-      <c r="BB11" s="8"/>
-      <c r="BC11" s="8"/>
-      <c r="BD11" s="8"/>
-      <c r="BE11" s="8"/>
-      <c r="BF11" s="8"/>
-      <c r="BG11" s="8"/>
-      <c r="BH11" s="8"/>
-      <c r="BI11" s="8"/>
-      <c r="BJ11" s="8"/>
-      <c r="BK11" s="8"/>
-      <c r="BL11" s="8"/>
-      <c r="BM11" s="8"/>
-      <c r="BN11" s="8"/>
-      <c r="BO11" s="8"/>
+      <c r="C11" s="4"/>
+      <c r="D11" s="4"/>
+      <c r="E11" s="4"/>
+      <c r="F11" s="4"/>
+      <c r="G11" s="4"/>
+      <c r="H11" s="4"/>
+      <c r="I11" s="4"/>
+      <c r="J11" s="4"/>
+      <c r="K11" s="4"/>
+      <c r="L11" s="4"/>
+      <c r="M11" s="4"/>
+      <c r="N11" s="4"/>
+      <c r="O11" s="4"/>
+      <c r="P11" s="4"/>
+      <c r="Q11" s="4"/>
+      <c r="R11" s="4"/>
+      <c r="S11" s="4"/>
+      <c r="T11" s="4"/>
+      <c r="U11" s="4"/>
+      <c r="V11" s="4"/>
+      <c r="W11" s="4"/>
+      <c r="X11" s="4"/>
+      <c r="Y11" s="4"/>
+      <c r="Z11" s="4"/>
+      <c r="AA11" s="4"/>
+      <c r="AB11" s="4"/>
+      <c r="AC11" s="4"/>
+      <c r="AD11" s="4"/>
+      <c r="AE11" s="4"/>
+      <c r="AF11" s="4"/>
+      <c r="AG11" s="4"/>
+      <c r="AH11" s="4"/>
+      <c r="AI11" s="4"/>
+      <c r="AJ11" s="4"/>
+      <c r="AK11" s="4"/>
+      <c r="AL11" s="4"/>
+      <c r="AM11" s="4"/>
+      <c r="AN11" s="4"/>
+      <c r="AO11" s="4"/>
+      <c r="AP11" s="4"/>
+      <c r="AQ11" s="4"/>
+      <c r="AR11" s="4"/>
+      <c r="AS11" s="4"/>
+      <c r="AT11" s="4"/>
+      <c r="AU11" s="4"/>
+      <c r="AV11" s="4"/>
+      <c r="AW11" s="4"/>
+      <c r="AX11" s="4"/>
+      <c r="AY11" s="4"/>
+      <c r="AZ11" s="4"/>
+      <c r="BA11" s="4"/>
+      <c r="BB11" s="4"/>
+      <c r="BC11" s="4"/>
+      <c r="BD11" s="4"/>
+      <c r="BE11" s="4"/>
+      <c r="BF11" s="4"/>
+      <c r="BG11" s="4"/>
+      <c r="BH11" s="4"/>
+      <c r="BI11" s="4"/>
+      <c r="BJ11" s="4"/>
+      <c r="BK11" s="4"/>
+      <c r="BL11" s="4"/>
+      <c r="BM11" s="4"/>
+      <c r="BN11" s="4"/>
     </row>
     <row r="12" spans="1:67" x14ac:dyDescent="0.2">
       <c r="B12" s="2" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C12" s="8"/>
       <c r="D12" s="8"/>
       <c r="E12" s="8">
-        <v>189.00700000000001</v>
+        <v>141.881</v>
       </c>
       <c r="F12" s="8">
-        <f t="shared" si="11"/>
-        <v>215.44599999999997</v>
+        <f>+S12-E12</f>
+        <v>157.499</v>
       </c>
       <c r="G12" s="8">
-        <v>225.61600000000001</v>
+        <v>152.959</v>
       </c>
       <c r="H12" s="8"/>
       <c r="I12" s="8">
-        <v>245.23699999999999</v>
+        <v>243.21299999999999</v>
       </c>
       <c r="J12" s="8"/>
       <c r="K12" s="8">
-        <v>278.67099999999999</v>
+        <v>255.58199999999999</v>
       </c>
       <c r="L12" s="8"/>
       <c r="M12" s="8"/>
       <c r="N12" s="8">
-        <v>187.23599999999999</v>
+        <v>163.70699999999999</v>
       </c>
       <c r="O12" s="8">
-        <v>205.768</v>
+        <v>176.9</v>
       </c>
       <c r="P12" s="8">
-        <v>174.24199999999999</v>
+        <v>173.078</v>
       </c>
       <c r="Q12" s="8">
-        <v>238.238</v>
+        <v>219.15</v>
       </c>
       <c r="R12" s="8">
-        <v>334.69299999999998</v>
+        <v>263.81400000000002</v>
       </c>
       <c r="S12" s="8">
-        <v>404.45299999999997</v>
+        <v>299.38</v>
       </c>
       <c r="T12" s="8">
-        <v>476.55900000000003</v>
+        <v>315.666</v>
       </c>
       <c r="U12" s="8">
-        <v>520.48800000000006</v>
+        <v>494.92</v>
       </c>
       <c r="V12" s="8"/>
       <c r="W12" s="8"/>
@@ -1895,54 +1886,53 @@
     </row>
     <row r="13" spans="1:67" x14ac:dyDescent="0.2">
       <c r="B13" s="2" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C13" s="8"/>
       <c r="D13" s="8"/>
       <c r="E13" s="8">
-        <v>152.166</v>
+        <v>60.887999999999998</v>
       </c>
       <c r="F13" s="8">
-        <f t="shared" si="11"/>
-        <v>154.56900000000002</v>
+        <f t="shared" ref="F13:F34" si="12">+S13-E13</f>
+        <v>67.963999999999999</v>
       </c>
       <c r="G13" s="8">
-        <v>173.994</v>
+        <v>68.093000000000004</v>
       </c>
       <c r="H13" s="8"/>
-      <c r="I13" s="8">
-        <v>195.66200000000001</v>
+      <c r="I13" s="16" t="s">
+        <v>72</v>
       </c>
       <c r="J13" s="8"/>
-      <c r="K13" s="8">
-        <v>215.15799999999999</v>
+      <c r="K13" s="16" t="s">
+        <v>72</v>
       </c>
       <c r="L13" s="8"/>
       <c r="M13" s="8"/>
       <c r="N13" s="8">
-        <f>54.887+58.946</f>
-        <v>113.833</v>
+        <v>88.22</v>
       </c>
       <c r="O13" s="8">
-        <v>135.37299999999999</v>
+        <v>89.72</v>
       </c>
       <c r="P13" s="8">
-        <v>128.37</v>
+        <v>68.322999999999993</v>
       </c>
       <c r="Q13" s="8">
-        <v>170.56800000000001</v>
+        <v>84.222999999999999</v>
       </c>
       <c r="R13" s="8">
-        <v>218.44800000000001</v>
+        <v>102.753</v>
       </c>
       <c r="S13" s="8">
-        <v>306.73500000000001</v>
+        <v>128.852</v>
       </c>
       <c r="T13" s="8">
-        <v>345.39400000000001</v>
+        <v>140.92099999999999</v>
       </c>
       <c r="U13" s="8">
-        <v>392.54300000000001</v>
+        <v>0</v>
       </c>
       <c r="V13" s="8"/>
       <c r="W13" s="8"/>
@@ -1993,53 +1983,53 @@
     </row>
     <row r="14" spans="1:67" x14ac:dyDescent="0.2">
       <c r="B14" s="2" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C14" s="8"/>
       <c r="D14" s="8"/>
       <c r="E14" s="8">
-        <v>344.64800000000002</v>
+        <v>189.00700000000001</v>
       </c>
       <c r="F14" s="8">
-        <f t="shared" si="11"/>
-        <v>402.16800000000001</v>
+        <f t="shared" si="12"/>
+        <v>215.44599999999997</v>
       </c>
       <c r="G14" s="8">
-        <v>395.18400000000003</v>
+        <v>225.61600000000001</v>
       </c>
       <c r="H14" s="8"/>
       <c r="I14" s="8">
-        <v>435.80599999999998</v>
+        <v>245.23699999999999</v>
       </c>
       <c r="J14" s="8"/>
       <c r="K14" s="8">
-        <v>499.76499999999999</v>
+        <v>278.67099999999999</v>
       </c>
       <c r="L14" s="8"/>
       <c r="M14" s="8"/>
       <c r="N14" s="8">
-        <v>296.26499999999999</v>
+        <v>187.23599999999999</v>
       </c>
       <c r="O14" s="8">
-        <v>339.435</v>
+        <v>205.768</v>
       </c>
       <c r="P14" s="8">
-        <v>268.77300000000002</v>
+        <v>174.24199999999999</v>
       </c>
       <c r="Q14" s="8">
-        <v>419.81700000000001</v>
+        <v>238.238</v>
       </c>
       <c r="R14" s="8">
-        <v>573.32000000000005</v>
+        <v>334.69299999999998</v>
       </c>
       <c r="S14" s="8">
-        <v>746.81600000000003</v>
+        <v>404.45299999999997</v>
       </c>
       <c r="T14" s="8">
-        <v>851.24300000000005</v>
+        <v>476.55900000000003</v>
       </c>
       <c r="U14" s="8">
-        <v>947.00900000000001</v>
+        <v>520.48800000000006</v>
       </c>
       <c r="V14" s="8"/>
       <c r="W14" s="8"/>
@@ -2090,54 +2080,54 @@
     </row>
     <row r="15" spans="1:67" x14ac:dyDescent="0.2">
       <c r="B15" s="2" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="C15" s="8"/>
       <c r="D15" s="8"/>
       <c r="E15" s="8">
-        <v>199.29400000000001</v>
+        <v>152.166</v>
       </c>
       <c r="F15" s="8">
-        <f t="shared" si="11"/>
-        <v>193.30999999999997</v>
+        <f t="shared" si="12"/>
+        <v>154.56900000000002</v>
       </c>
       <c r="G15" s="8">
-        <v>225.47800000000001</v>
+        <v>173.994</v>
       </c>
       <c r="H15" s="8"/>
       <c r="I15" s="8">
-        <v>248.24100000000001</v>
+        <v>195.66200000000001</v>
       </c>
       <c r="J15" s="8"/>
       <c r="K15" s="8">
-        <v>249.64599999999999</v>
+        <v>215.15799999999999</v>
       </c>
       <c r="L15" s="8"/>
       <c r="M15" s="8"/>
       <c r="N15" s="8">
-        <f>30.205+226.526</f>
-        <v>256.73099999999999</v>
+        <f>54.887+58.946</f>
+        <v>113.833</v>
       </c>
       <c r="O15" s="8">
-        <v>268.32600000000002</v>
+        <v>135.37299999999999</v>
       </c>
       <c r="P15" s="8">
-        <v>275.24</v>
+        <v>128.37</v>
       </c>
       <c r="Q15" s="8">
-        <v>292.36200000000002</v>
+        <v>170.56800000000001</v>
       </c>
       <c r="R15" s="8">
-        <v>346.38799999999998</v>
+        <v>218.44800000000001</v>
       </c>
       <c r="S15" s="8">
-        <v>392.60399999999998</v>
+        <v>306.73500000000001</v>
       </c>
       <c r="T15" s="8">
-        <v>427.29700000000003</v>
+        <v>345.39400000000001</v>
       </c>
       <c r="U15" s="8">
-        <v>460.94200000000001</v>
+        <v>392.54300000000001</v>
       </c>
       <c r="V15" s="8"/>
       <c r="W15" s="8"/>
@@ -2187,69 +2177,54 @@
       <c r="BO15" s="8"/>
     </row>
     <row r="16" spans="1:67" x14ac:dyDescent="0.2">
-      <c r="B16" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="C16" s="9">
-        <f t="shared" ref="C16:D16" si="12">+C14+C15</f>
-        <v>0</v>
-      </c>
-      <c r="D16" s="9">
+      <c r="B16" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="C16" s="8"/>
+      <c r="D16" s="8"/>
+      <c r="E16" s="8">
+        <v>344.64800000000002</v>
+      </c>
+      <c r="F16" s="8">
         <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="E16" s="9">
-        <f>+E14+E15</f>
-        <v>543.94200000000001</v>
-      </c>
-      <c r="F16" s="9">
-        <f t="shared" ref="F16:G16" si="13">+F14+F15</f>
-        <v>595.47799999999995</v>
-      </c>
-      <c r="G16" s="9">
-        <f t="shared" si="13"/>
-        <v>620.66200000000003</v>
-      </c>
-      <c r="H16" s="9"/>
-      <c r="I16" s="9">
-        <v>684.13499999999999</v>
-      </c>
-      <c r="J16" s="9"/>
-      <c r="K16" s="9">
-        <v>749.41099999999994</v>
-      </c>
-      <c r="L16" s="9"/>
+        <v>402.16800000000001</v>
+      </c>
+      <c r="G16" s="8">
+        <v>395.18400000000003</v>
+      </c>
+      <c r="H16" s="8"/>
+      <c r="I16" s="8">
+        <v>435.80599999999998</v>
+      </c>
+      <c r="J16" s="8"/>
+      <c r="K16" s="8">
+        <v>499.76499999999999</v>
+      </c>
+      <c r="L16" s="8"/>
       <c r="M16" s="8"/>
-      <c r="N16" s="9">
-        <f t="shared" ref="N16:R16" si="14">+N14+N15</f>
-        <v>552.99599999999998</v>
-      </c>
-      <c r="O16" s="9">
-        <f t="shared" si="14"/>
-        <v>607.76099999999997</v>
-      </c>
-      <c r="P16" s="9">
-        <f t="shared" si="14"/>
-        <v>544.01300000000003</v>
-      </c>
-      <c r="Q16" s="9">
-        <f t="shared" si="14"/>
-        <v>712.17900000000009</v>
-      </c>
-      <c r="R16" s="9">
-        <f t="shared" si="14"/>
-        <v>919.70800000000008</v>
-      </c>
-      <c r="S16" s="9">
-        <f>+S14+S15</f>
-        <v>1139.42</v>
-      </c>
-      <c r="T16" s="9">
-        <f>+T14+T15</f>
-        <v>1278.54</v>
-      </c>
-      <c r="U16" s="9">
-        <v>1407.951</v>
+      <c r="N16" s="8">
+        <v>296.26499999999999</v>
+      </c>
+      <c r="O16" s="8">
+        <v>339.435</v>
+      </c>
+      <c r="P16" s="8">
+        <v>268.77300000000002</v>
+      </c>
+      <c r="Q16" s="8">
+        <v>419.81700000000001</v>
+      </c>
+      <c r="R16" s="8">
+        <v>573.32000000000005</v>
+      </c>
+      <c r="S16" s="8">
+        <v>746.81600000000003</v>
+      </c>
+      <c r="T16" s="8">
+        <v>851.24300000000005</v>
+      </c>
+      <c r="U16" s="8">
+        <v>947.00900000000001</v>
       </c>
       <c r="V16" s="8"/>
       <c r="W16" s="8"/>
@@ -2300,53 +2275,54 @@
     </row>
     <row r="17" spans="2:67" x14ac:dyDescent="0.2">
       <c r="B17" s="2" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="C17" s="8"/>
       <c r="D17" s="8"/>
       <c r="E17" s="8">
-        <v>54</v>
+        <v>199.29400000000001</v>
       </c>
       <c r="F17" s="8">
-        <f t="shared" si="11"/>
-        <v>60.343000000000004</v>
+        <f t="shared" si="12"/>
+        <v>193.30999999999997</v>
       </c>
       <c r="G17" s="8">
-        <v>39.276000000000003</v>
+        <v>225.47800000000001</v>
       </c>
       <c r="H17" s="8"/>
       <c r="I17" s="8">
-        <v>58.384</v>
+        <v>248.24100000000001</v>
       </c>
       <c r="J17" s="8"/>
       <c r="K17" s="8">
-        <v>68.566999999999993</v>
+        <v>249.64599999999999</v>
       </c>
       <c r="L17" s="8"/>
       <c r="M17" s="8"/>
       <c r="N17" s="8">
-        <v>88.055999999999997</v>
+        <f>30.205+226.526</f>
+        <v>256.73099999999999</v>
       </c>
       <c r="O17" s="8">
-        <v>72.278999999999996</v>
+        <v>268.32600000000002</v>
       </c>
       <c r="P17" s="8">
-        <v>53.725000000000001</v>
+        <v>275.24</v>
       </c>
       <c r="Q17" s="8">
-        <v>113.61</v>
+        <v>292.36200000000002</v>
       </c>
       <c r="R17" s="8">
-        <v>95.537000000000006</v>
+        <v>346.38799999999998</v>
       </c>
       <c r="S17" s="8">
-        <v>114.343</v>
+        <v>392.60399999999998</v>
       </c>
       <c r="T17" s="8">
-        <v>101.8</v>
+        <v>427.29700000000003</v>
       </c>
       <c r="U17" s="8">
-        <v>121.099</v>
+        <v>460.94200000000001</v>
       </c>
       <c r="V17" s="8"/>
       <c r="W17" s="8"/>
@@ -2396,78 +2372,69 @@
       <c r="BO17" s="8"/>
     </row>
     <row r="18" spans="2:67" x14ac:dyDescent="0.2">
-      <c r="B18" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="C18" s="8">
-        <f t="shared" ref="C18:F18" si="15">+C16-C17</f>
+      <c r="B18" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="C18" s="9">
+        <f t="shared" ref="C18:D18" si="13">+C16+C17</f>
         <v>0</v>
       </c>
-      <c r="D18" s="8">
+      <c r="D18" s="9">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+      <c r="E18" s="9">
+        <f>+E16+E17</f>
+        <v>543.94200000000001</v>
+      </c>
+      <c r="F18" s="9">
+        <f t="shared" ref="F18:G18" si="14">+F16+F17</f>
+        <v>595.47799999999995</v>
+      </c>
+      <c r="G18" s="9">
+        <f t="shared" si="14"/>
+        <v>620.66200000000003</v>
+      </c>
+      <c r="H18" s="9"/>
+      <c r="I18" s="9">
+        <v>684.13499999999999</v>
+      </c>
+      <c r="J18" s="9"/>
+      <c r="K18" s="9">
+        <v>749.41099999999994</v>
+      </c>
+      <c r="L18" s="9"/>
+      <c r="M18" s="8"/>
+      <c r="N18" s="9">
+        <f t="shared" ref="N18:R18" si="15">+N16+N17</f>
+        <v>552.99599999999998</v>
+      </c>
+      <c r="O18" s="9">
         <f t="shared" si="15"/>
-        <v>0</v>
-      </c>
-      <c r="E18" s="8">
+        <v>607.76099999999997</v>
+      </c>
+      <c r="P18" s="9">
         <f t="shared" si="15"/>
-        <v>489.94200000000001</v>
-      </c>
-      <c r="F18" s="8">
+        <v>544.01300000000003</v>
+      </c>
+      <c r="Q18" s="9">
         <f t="shared" si="15"/>
-        <v>535.13499999999999</v>
-      </c>
-      <c r="G18" s="8">
-        <f>+G16-G17</f>
-        <v>581.38600000000008</v>
-      </c>
-      <c r="H18" s="8">
-        <f t="shared" ref="H18:K18" si="16">+H16-H17</f>
-        <v>0</v>
-      </c>
-      <c r="I18" s="8">
-        <f t="shared" si="16"/>
-        <v>625.75099999999998</v>
-      </c>
-      <c r="J18" s="8">
-        <f t="shared" si="16"/>
-        <v>0</v>
-      </c>
-      <c r="K18" s="8">
-        <f t="shared" si="16"/>
-        <v>680.84399999999994</v>
-      </c>
-      <c r="L18" s="8"/>
-      <c r="M18" s="8"/>
-      <c r="N18" s="8">
-        <f t="shared" ref="N18:Q18" si="17">+N16-N17</f>
-        <v>464.94</v>
-      </c>
-      <c r="O18" s="8">
-        <f t="shared" si="17"/>
-        <v>535.48199999999997</v>
-      </c>
-      <c r="P18" s="8">
-        <f t="shared" si="17"/>
-        <v>490.28800000000001</v>
-      </c>
-      <c r="Q18" s="8">
-        <f t="shared" si="17"/>
-        <v>598.56900000000007</v>
-      </c>
-      <c r="R18" s="8">
-        <f>+R16-R17</f>
-        <v>824.17100000000005</v>
-      </c>
-      <c r="S18" s="8">
-        <f>+S16-S17</f>
-        <v>1025.077</v>
-      </c>
-      <c r="T18" s="8">
-        <f>+T16-T17</f>
-        <v>1176.74</v>
-      </c>
-      <c r="U18" s="8">
-        <f>+U16-U17</f>
-        <v>1286.8520000000001</v>
+        <v>712.17900000000009</v>
+      </c>
+      <c r="R18" s="9">
+        <f t="shared" si="15"/>
+        <v>919.70800000000008</v>
+      </c>
+      <c r="S18" s="9">
+        <f>+S16+S17</f>
+        <v>1139.42</v>
+      </c>
+      <c r="T18" s="9">
+        <f>+T16+T17</f>
+        <v>1278.54</v>
+      </c>
+      <c r="U18" s="9">
+        <v>1407.951</v>
       </c>
       <c r="V18" s="8"/>
       <c r="W18" s="8"/>
@@ -2518,53 +2485,53 @@
     </row>
     <row r="19" spans="2:67" x14ac:dyDescent="0.2">
       <c r="B19" s="2" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="C19" s="8"/>
       <c r="D19" s="8"/>
       <c r="E19" s="8">
-        <v>227.84</v>
+        <v>54</v>
       </c>
       <c r="F19" s="8">
-        <f t="shared" si="11"/>
-        <v>247.929</v>
+        <f t="shared" si="12"/>
+        <v>60.343000000000004</v>
       </c>
       <c r="G19" s="8">
-        <v>281.505</v>
+        <v>39.276000000000003</v>
       </c>
       <c r="H19" s="8"/>
       <c r="I19" s="8">
-        <v>291.43700000000001</v>
+        <v>58.384</v>
       </c>
       <c r="J19" s="8"/>
       <c r="K19" s="8">
-        <v>303.24099999999999</v>
+        <v>68.566999999999993</v>
       </c>
       <c r="L19" s="8"/>
       <c r="M19" s="8"/>
       <c r="N19" s="8">
-        <v>268.32799999999997</v>
+        <v>88.055999999999997</v>
       </c>
       <c r="O19" s="8">
-        <v>248.06700000000001</v>
+        <v>72.278999999999996</v>
       </c>
       <c r="P19" s="8">
-        <v>243.29599999999999</v>
+        <v>53.725000000000001</v>
       </c>
       <c r="Q19" s="8">
-        <v>271.084</v>
+        <v>113.61</v>
       </c>
       <c r="R19" s="8">
-        <v>372.22399999999999</v>
+        <v>95.537000000000006</v>
       </c>
       <c r="S19" s="8">
-        <v>475.76900000000001</v>
+        <v>114.343</v>
       </c>
       <c r="T19" s="8">
-        <v>560.36099999999999</v>
+        <v>101.8</v>
       </c>
       <c r="U19" s="8">
-        <v>595.73699999999997</v>
+        <v>121.099</v>
       </c>
       <c r="V19" s="8"/>
       <c r="W19" s="8"/>
@@ -2615,53 +2582,77 @@
     </row>
     <row r="20" spans="2:67" x14ac:dyDescent="0.2">
       <c r="B20" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="C20" s="8"/>
-      <c r="D20" s="8"/>
+        <v>35</v>
+      </c>
+      <c r="C20" s="8">
+        <f t="shared" ref="C20:F20" si="16">+C18-C19</f>
+        <v>0</v>
+      </c>
+      <c r="D20" s="8">
+        <f t="shared" si="16"/>
+        <v>0</v>
+      </c>
       <c r="E20" s="8">
-        <v>93.332999999999998</v>
+        <f t="shared" si="16"/>
+        <v>489.94200000000001</v>
       </c>
       <c r="F20" s="8">
-        <f t="shared" si="11"/>
-        <v>101.636</v>
+        <f t="shared" si="16"/>
+        <v>535.13499999999999</v>
       </c>
       <c r="G20" s="8">
-        <v>113.197</v>
-      </c>
-      <c r="H20" s="8"/>
+        <f>+G18-G19</f>
+        <v>581.38600000000008</v>
+      </c>
+      <c r="H20" s="8">
+        <f t="shared" ref="H20:K20" si="17">+H18-H19</f>
+        <v>0</v>
+      </c>
       <c r="I20" s="8">
-        <v>125.614</v>
-      </c>
-      <c r="J20" s="8"/>
+        <f t="shared" si="17"/>
+        <v>625.75099999999998</v>
+      </c>
+      <c r="J20" s="8">
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
       <c r="K20" s="8">
-        <v>138.36699999999999</v>
+        <f t="shared" si="17"/>
+        <v>680.84399999999994</v>
       </c>
       <c r="L20" s="8"/>
       <c r="M20" s="8"/>
       <c r="N20" s="8">
-        <v>98.328999999999994</v>
+        <f t="shared" ref="N20:Q20" si="18">+N18-N19</f>
+        <v>464.94</v>
       </c>
       <c r="O20" s="8">
-        <v>112.199</v>
+        <f t="shared" si="18"/>
+        <v>535.48199999999997</v>
       </c>
       <c r="P20" s="8">
-        <v>119.569</v>
+        <f t="shared" si="18"/>
+        <v>490.28800000000001</v>
       </c>
       <c r="Q20" s="8">
-        <v>132.94800000000001</v>
+        <f t="shared" si="18"/>
+        <v>598.56900000000007</v>
       </c>
       <c r="R20" s="8">
-        <v>164.71299999999999</v>
+        <f>+R18-R19</f>
+        <v>824.17100000000005</v>
       </c>
       <c r="S20" s="8">
-        <v>194.96899999999999</v>
+        <f>+S18-S19</f>
+        <v>1025.077</v>
       </c>
       <c r="T20" s="8">
-        <v>233.49199999999999</v>
+        <f>+T18-T19</f>
+        <v>1176.74</v>
       </c>
       <c r="U20" s="8">
-        <v>255.36699999999999</v>
+        <f>+U18-U19</f>
+        <v>1286.8520000000001</v>
       </c>
       <c r="V20" s="8"/>
       <c r="W20" s="8"/>
@@ -2712,53 +2703,53 @@
     </row>
     <row r="21" spans="2:67" x14ac:dyDescent="0.2">
       <c r="B21" s="2" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C21" s="8"/>
       <c r="D21" s="8"/>
       <c r="E21" s="8">
-        <v>13.581</v>
+        <v>227.84</v>
       </c>
       <c r="F21" s="8">
-        <f t="shared" si="11"/>
-        <v>7.9879999999999995</v>
+        <f t="shared" si="12"/>
+        <v>247.929</v>
       </c>
       <c r="G21" s="8">
-        <v>10.613</v>
+        <v>281.505</v>
       </c>
       <c r="H21" s="8"/>
       <c r="I21" s="8">
-        <v>8.9450000000000003</v>
+        <v>291.43700000000001</v>
       </c>
       <c r="J21" s="8"/>
       <c r="K21" s="8">
-        <v>13.019</v>
+        <v>303.24099999999999</v>
       </c>
       <c r="L21" s="8"/>
       <c r="M21" s="8"/>
       <c r="N21" s="8">
-        <v>5.9160000000000004</v>
+        <v>268.32799999999997</v>
       </c>
       <c r="O21" s="8">
-        <v>7.53</v>
+        <v>248.06700000000001</v>
       </c>
       <c r="P21" s="8">
-        <v>8.9019999999999992</v>
+        <v>243.29599999999999</v>
       </c>
       <c r="Q21" s="8">
-        <v>9.8130000000000006</v>
+        <v>271.084</v>
       </c>
       <c r="R21" s="8">
-        <v>16.491</v>
+        <v>372.22399999999999</v>
       </c>
       <c r="S21" s="8">
-        <v>21.568999999999999</v>
+        <v>475.76900000000001</v>
       </c>
       <c r="T21" s="8">
-        <v>21.079000000000001</v>
+        <v>560.36099999999999</v>
       </c>
       <c r="U21" s="8">
-        <v>25.614000000000001</v>
+        <v>595.73699999999997</v>
       </c>
       <c r="V21" s="8"/>
       <c r="W21" s="8"/>
@@ -2809,53 +2800,53 @@
     </row>
     <row r="22" spans="2:67" x14ac:dyDescent="0.2">
       <c r="B22" s="2" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C22" s="8"/>
       <c r="D22" s="8"/>
       <c r="E22" s="8">
-        <v>0.98299999999999998</v>
+        <v>93.332999999999998</v>
       </c>
       <c r="F22" s="8">
-        <f t="shared" si="11"/>
-        <v>1.3860000000000001</v>
+        <f t="shared" si="12"/>
+        <v>101.636</v>
       </c>
       <c r="G22" s="8">
-        <v>1.7669999999999999</v>
+        <v>113.197</v>
       </c>
       <c r="H22" s="8"/>
       <c r="I22" s="8">
-        <v>1.556</v>
+        <v>125.614</v>
       </c>
       <c r="J22" s="8"/>
       <c r="K22" s="8">
-        <v>1.716</v>
+        <v>138.36699999999999</v>
       </c>
       <c r="L22" s="8"/>
       <c r="M22" s="8"/>
       <c r="N22" s="8">
-        <v>1.448</v>
+        <v>98.328999999999994</v>
       </c>
       <c r="O22" s="8">
-        <v>0.82599999999999996</v>
+        <v>112.199</v>
       </c>
       <c r="P22" s="8">
-        <v>2.7719999999999998</v>
+        <v>119.569</v>
       </c>
       <c r="Q22" s="8">
-        <v>10.054</v>
+        <v>132.94800000000001</v>
       </c>
       <c r="R22" s="8">
-        <v>1.9470000000000001</v>
+        <v>164.71299999999999</v>
       </c>
       <c r="S22" s="8">
-        <v>2.3690000000000002</v>
+        <v>194.96899999999999</v>
       </c>
       <c r="T22" s="8">
-        <v>3.2709999999999999</v>
+        <v>233.49199999999999</v>
       </c>
       <c r="U22" s="8">
-        <v>5.4039999999999999</v>
+        <v>255.36699999999999</v>
       </c>
       <c r="V22" s="8"/>
       <c r="W22" s="8"/>
@@ -2906,53 +2897,53 @@
     </row>
     <row r="23" spans="2:67" x14ac:dyDescent="0.2">
       <c r="B23" s="2" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="C23" s="8"/>
       <c r="D23" s="8"/>
       <c r="E23" s="8">
-        <v>0.76200000000000001</v>
+        <v>13.581</v>
       </c>
       <c r="F23" s="8">
-        <f t="shared" si="11"/>
-        <v>1.67</v>
+        <f t="shared" si="12"/>
+        <v>7.9879999999999995</v>
       </c>
       <c r="G23" s="8">
-        <v>0.78900000000000003</v>
+        <v>10.613</v>
       </c>
       <c r="H23" s="8"/>
       <c r="I23" s="8">
-        <v>0.82099999999999995</v>
+        <v>8.9450000000000003</v>
       </c>
       <c r="J23" s="8"/>
       <c r="K23" s="8">
-        <v>0.55800000000000005</v>
+        <v>13.019</v>
       </c>
       <c r="L23" s="8"/>
       <c r="M23" s="8"/>
       <c r="N23" s="8">
-        <v>2.4700000000000002</v>
+        <v>5.9160000000000004</v>
       </c>
       <c r="O23" s="8">
-        <v>2.3820000000000001</v>
+        <v>7.53</v>
       </c>
       <c r="P23" s="8">
-        <v>3.258</v>
+        <v>8.9019999999999992</v>
       </c>
       <c r="Q23" s="8">
-        <v>3.4449999999999998</v>
+        <v>9.8130000000000006</v>
       </c>
       <c r="R23" s="8">
-        <v>2.153</v>
+        <v>16.491</v>
       </c>
       <c r="S23" s="8">
-        <v>2.4319999999999999</v>
+        <v>21.568999999999999</v>
       </c>
       <c r="T23" s="8">
-        <v>2.4169999999999998</v>
+        <v>21.079000000000001</v>
       </c>
       <c r="U23" s="8">
-        <v>1.7350000000000001</v>
+        <v>25.614000000000001</v>
       </c>
       <c r="V23" s="8"/>
       <c r="W23" s="8"/>
@@ -3003,53 +2994,53 @@
     </row>
     <row r="24" spans="2:67" x14ac:dyDescent="0.2">
       <c r="B24" s="2" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C24" s="8"/>
       <c r="D24" s="8"/>
       <c r="E24" s="8">
-        <v>67.114999999999995</v>
+        <v>0.98299999999999998</v>
       </c>
       <c r="F24" s="8">
-        <f t="shared" si="11"/>
-        <v>71.73</v>
+        <f t="shared" si="12"/>
+        <v>1.3860000000000001</v>
       </c>
       <c r="G24" s="8">
-        <v>73.167000000000002</v>
+        <v>1.7669999999999999</v>
       </c>
       <c r="H24" s="8"/>
       <c r="I24" s="8">
-        <v>86.778000000000006</v>
+        <v>1.556</v>
       </c>
       <c r="J24" s="8"/>
       <c r="K24" s="8">
-        <v>98.343000000000004</v>
+        <v>1.716</v>
       </c>
       <c r="L24" s="8"/>
       <c r="M24" s="8"/>
       <c r="N24" s="8">
-        <v>25.605</v>
+        <v>1.448</v>
       </c>
       <c r="O24" s="8">
-        <v>86.25</v>
+        <v>0.82599999999999996</v>
       </c>
       <c r="P24" s="8">
-        <v>104.28400000000001</v>
+        <v>2.7719999999999998</v>
       </c>
       <c r="Q24" s="8">
-        <v>116.27500000000001</v>
+        <v>10.054</v>
       </c>
       <c r="R24" s="8">
-        <v>131.94499999999999</v>
+        <v>1.9470000000000001</v>
       </c>
       <c r="S24" s="8">
-        <v>138.845</v>
+        <v>2.3690000000000002</v>
       </c>
       <c r="T24" s="8">
-        <v>153.00399999999999</v>
+        <v>3.2709999999999999</v>
       </c>
       <c r="U24" s="8">
-        <v>180.61199999999999</v>
+        <v>5.4039999999999999</v>
       </c>
       <c r="V24" s="8"/>
       <c r="W24" s="8"/>
@@ -3100,53 +3091,53 @@
     </row>
     <row r="25" spans="2:67" x14ac:dyDescent="0.2">
       <c r="B25" s="2" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="C25" s="8"/>
       <c r="D25" s="8"/>
       <c r="E25" s="8">
-        <v>2.125</v>
+        <v>0.76200000000000001</v>
       </c>
       <c r="F25" s="8">
-        <f t="shared" si="11"/>
-        <v>9.1950000000000003</v>
+        <f t="shared" si="12"/>
+        <v>1.67</v>
       </c>
       <c r="G25" s="8">
-        <v>0.873</v>
+        <v>0.78900000000000003</v>
       </c>
       <c r="H25" s="8"/>
       <c r="I25" s="8">
-        <v>1.5169999999999999</v>
+        <v>0.82099999999999995</v>
       </c>
       <c r="J25" s="8"/>
       <c r="K25" s="8">
-        <v>1.9490000000000001</v>
+        <v>0.55800000000000005</v>
       </c>
       <c r="L25" s="8"/>
       <c r="M25" s="8"/>
       <c r="N25" s="8">
-        <v>1.1419999999999999</v>
+        <v>2.4700000000000002</v>
       </c>
       <c r="O25" s="8">
-        <v>1.268</v>
+        <v>2.3820000000000001</v>
       </c>
       <c r="P25" s="8">
-        <v>35.085000000000001</v>
+        <v>3.258</v>
       </c>
       <c r="Q25" s="8">
-        <v>4.9119999999999999</v>
+        <v>3.4449999999999998</v>
       </c>
       <c r="R25" s="8">
-        <v>8.4860000000000007</v>
+        <v>2.153</v>
       </c>
       <c r="S25" s="8">
-        <v>11.32</v>
+        <v>2.4319999999999999</v>
       </c>
       <c r="T25" s="8">
-        <v>2.8210000000000002</v>
+        <v>2.4169999999999998</v>
       </c>
       <c r="U25" s="8">
-        <v>8.8770000000000007</v>
+        <v>1.7350000000000001</v>
       </c>
       <c r="V25" s="8"/>
       <c r="W25" s="8"/>
@@ -3197,77 +3188,53 @@
     </row>
     <row r="26" spans="2:67" x14ac:dyDescent="0.2">
       <c r="B26" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="C26" s="8">
-        <f t="shared" ref="C26:F26" si="18">+C18-SUM(C19:C21)+C22+C23-C24-C25</f>
-        <v>0</v>
-      </c>
-      <c r="D26" s="8">
-        <f t="shared" si="18"/>
-        <v>0</v>
-      </c>
+        <v>41</v>
+      </c>
+      <c r="C26" s="8"/>
+      <c r="D26" s="8"/>
       <c r="E26" s="8">
-        <f t="shared" si="18"/>
-        <v>87.692999999999998</v>
+        <v>67.114999999999995</v>
       </c>
       <c r="F26" s="8">
-        <f t="shared" si="18"/>
-        <v>99.712999999999965</v>
+        <f t="shared" si="12"/>
+        <v>71.73</v>
       </c>
       <c r="G26" s="8">
-        <f>+G18-SUM(G19:G21)+G22+G23-G24-G25</f>
-        <v>104.58700000000006</v>
-      </c>
-      <c r="H26" s="8">
-        <f t="shared" ref="H26:U26" si="19">+H18-SUM(H19:H21)+H22+H23-H24-H25</f>
-        <v>0</v>
-      </c>
+        <v>73.167000000000002</v>
+      </c>
+      <c r="H26" s="8"/>
       <c r="I26" s="8">
-        <f t="shared" si="19"/>
-        <v>113.83699999999995</v>
-      </c>
-      <c r="J26" s="8">
-        <f t="shared" si="19"/>
-        <v>0</v>
-      </c>
+        <v>86.778000000000006</v>
+      </c>
+      <c r="J26" s="8"/>
       <c r="K26" s="8">
-        <f t="shared" si="19"/>
-        <v>128.19899999999996</v>
+        <v>98.343000000000004</v>
       </c>
       <c r="L26" s="8"/>
       <c r="M26" s="8"/>
       <c r="N26" s="8">
-        <f t="shared" si="19"/>
-        <v>69.538000000000011</v>
+        <v>25.605</v>
       </c>
       <c r="O26" s="8">
-        <f t="shared" si="19"/>
-        <v>83.375999999999976</v>
+        <v>86.25</v>
       </c>
       <c r="P26" s="8">
-        <f t="shared" si="19"/>
-        <v>-14.817999999999991</v>
+        <v>104.28400000000001</v>
       </c>
       <c r="Q26" s="8">
-        <f t="shared" si="19"/>
-        <v>77.03600000000003</v>
+        <v>116.27500000000001</v>
       </c>
       <c r="R26" s="8">
-        <f t="shared" si="19"/>
-        <v>134.41200000000009</v>
+        <v>131.94499999999999</v>
       </c>
       <c r="S26" s="8">
-        <f t="shared" si="19"/>
-        <v>187.40600000000003</v>
+        <v>138.845</v>
       </c>
       <c r="T26" s="8">
-        <f t="shared" si="19"/>
-        <v>211.67100000000011</v>
+        <v>153.00399999999999</v>
       </c>
       <c r="U26" s="8">
-        <f t="shared" si="19"/>
-        <v>227.78400000000013</v>
+        <v>180.61199999999999</v>
       </c>
       <c r="V26" s="8"/>
       <c r="W26" s="8"/>
@@ -3318,53 +3285,53 @@
     </row>
     <row r="27" spans="2:67" x14ac:dyDescent="0.2">
       <c r="B27" s="2" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="C27" s="8"/>
       <c r="D27" s="8"/>
       <c r="E27" s="8">
-        <v>49.067</v>
+        <v>2.125</v>
       </c>
       <c r="F27" s="8">
-        <f t="shared" si="11"/>
-        <v>12.271000000000001</v>
+        <f t="shared" si="12"/>
+        <v>9.1950000000000003</v>
       </c>
       <c r="G27" s="8">
-        <v>28.606000000000002</v>
+        <v>0.873</v>
       </c>
       <c r="H27" s="8"/>
       <c r="I27" s="8">
-        <v>53.683999999999997</v>
+        <v>1.5169999999999999</v>
       </c>
       <c r="J27" s="8"/>
       <c r="K27" s="8">
-        <v>40.207000000000001</v>
+        <v>1.9490000000000001</v>
       </c>
       <c r="L27" s="8"/>
       <c r="M27" s="8"/>
       <c r="N27" s="8">
-        <v>26.33</v>
+        <v>1.1419999999999999</v>
       </c>
       <c r="O27" s="8">
-        <v>41.401000000000003</v>
+        <v>1.268</v>
       </c>
       <c r="P27" s="8">
-        <v>46.956000000000003</v>
+        <v>35.085000000000001</v>
       </c>
       <c r="Q27" s="8">
-        <v>34.908000000000001</v>
+        <v>4.9119999999999999</v>
       </c>
       <c r="R27" s="8">
-        <v>80.917000000000002</v>
+        <v>8.4860000000000007</v>
       </c>
       <c r="S27" s="8">
-        <v>61.338000000000001</v>
+        <v>11.32</v>
       </c>
       <c r="T27" s="8">
-        <v>67.558999999999997</v>
+        <v>2.8210000000000002</v>
       </c>
       <c r="U27" s="8">
-        <v>84.634</v>
+        <v>8.8770000000000007</v>
       </c>
       <c r="V27" s="8"/>
       <c r="W27" s="8"/>
@@ -3415,53 +3382,77 @@
     </row>
     <row r="28" spans="2:67" x14ac:dyDescent="0.2">
       <c r="B28" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="C28" s="8"/>
-      <c r="D28" s="8"/>
+        <v>43</v>
+      </c>
+      <c r="C28" s="8">
+        <f t="shared" ref="C28:F28" si="19">+C20-SUM(C21:C23)+C24+C25-C26-C27</f>
+        <v>0</v>
+      </c>
+      <c r="D28" s="8">
+        <f t="shared" si="19"/>
+        <v>0</v>
+      </c>
       <c r="E28" s="8">
-        <v>46.637999999999998</v>
+        <f t="shared" si="19"/>
+        <v>87.692999999999998</v>
       </c>
       <c r="F28" s="8">
-        <f t="shared" si="11"/>
-        <v>0.63500000000000512</v>
+        <f t="shared" si="19"/>
+        <v>99.712999999999965</v>
       </c>
       <c r="G28" s="8">
-        <v>19.265999999999998</v>
-      </c>
-      <c r="H28" s="8"/>
+        <f>+G20-SUM(G21:G23)+G24+G25-G26-G27</f>
+        <v>104.58700000000006</v>
+      </c>
+      <c r="H28" s="8">
+        <f t="shared" ref="H28:U28" si="20">+H20-SUM(H21:H23)+H24+H25-H26-H27</f>
+        <v>0</v>
+      </c>
       <c r="I28" s="8">
-        <v>47.203000000000003</v>
-      </c>
-      <c r="J28" s="8"/>
+        <f t="shared" si="20"/>
+        <v>113.83699999999995</v>
+      </c>
+      <c r="J28" s="8">
+        <f t="shared" si="20"/>
+        <v>0</v>
+      </c>
       <c r="K28" s="8">
-        <v>21.797000000000001</v>
+        <f t="shared" si="20"/>
+        <v>128.19899999999996</v>
       </c>
       <c r="L28" s="8"/>
       <c r="M28" s="8"/>
       <c r="N28" s="8">
-        <v>22.074000000000002</v>
+        <f t="shared" si="20"/>
+        <v>69.538000000000011</v>
       </c>
       <c r="O28" s="8">
-        <v>27.201000000000001</v>
+        <f t="shared" si="20"/>
+        <v>83.375999999999976</v>
       </c>
       <c r="P28" s="8">
-        <v>27.992000000000001</v>
+        <f t="shared" si="20"/>
+        <v>-14.817999999999991</v>
       </c>
       <c r="Q28" s="8">
-        <v>21.898</v>
+        <f t="shared" si="20"/>
+        <v>77.03600000000003</v>
       </c>
       <c r="R28" s="8">
-        <v>70.471999999999994</v>
+        <f t="shared" si="20"/>
+        <v>134.41200000000009</v>
       </c>
       <c r="S28" s="8">
-        <v>47.273000000000003</v>
+        <f t="shared" si="20"/>
+        <v>187.40600000000003</v>
       </c>
       <c r="T28" s="8">
-        <v>35.625</v>
+        <f t="shared" si="20"/>
+        <v>211.67100000000011</v>
       </c>
       <c r="U28" s="8">
-        <v>55.545999999999999</v>
+        <f t="shared" si="20"/>
+        <v>227.78400000000013</v>
       </c>
       <c r="V28" s="8"/>
       <c r="W28" s="8"/>
@@ -3512,77 +3503,53 @@
     </row>
     <row r="29" spans="2:67" x14ac:dyDescent="0.2">
       <c r="B29" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="C29" s="8">
-        <f t="shared" ref="C29:F29" si="20">+C26-C27+C28</f>
-        <v>0</v>
-      </c>
-      <c r="D29" s="8">
-        <f t="shared" si="20"/>
-        <v>0</v>
-      </c>
+        <v>44</v>
+      </c>
+      <c r="C29" s="8"/>
+      <c r="D29" s="8"/>
       <c r="E29" s="8">
-        <f t="shared" si="20"/>
-        <v>85.263999999999996</v>
+        <v>49.067</v>
       </c>
       <c r="F29" s="8">
-        <f t="shared" si="20"/>
-        <v>88.07699999999997</v>
+        <f t="shared" si="12"/>
+        <v>12.271000000000001</v>
       </c>
       <c r="G29" s="8">
-        <f>+G26-G27+G28</f>
-        <v>95.247000000000043</v>
-      </c>
-      <c r="H29" s="8">
-        <f t="shared" ref="H29:K29" si="21">+H26-H27+H28</f>
-        <v>0</v>
-      </c>
+        <v>28.606000000000002</v>
+      </c>
+      <c r="H29" s="8"/>
       <c r="I29" s="8">
-        <f t="shared" si="21"/>
-        <v>107.35599999999995</v>
-      </c>
-      <c r="J29" s="8">
-        <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
+        <v>53.683999999999997</v>
+      </c>
+      <c r="J29" s="8"/>
       <c r="K29" s="8">
-        <f t="shared" si="21"/>
-        <v>109.78899999999996</v>
+        <v>40.207000000000001</v>
       </c>
       <c r="L29" s="8"/>
       <c r="M29" s="8"/>
       <c r="N29" s="8">
-        <f t="shared" ref="N29:R29" si="22">+N26-N27+N28</f>
-        <v>65.282000000000011</v>
+        <v>26.33</v>
       </c>
       <c r="O29" s="8">
-        <f t="shared" si="22"/>
-        <v>69.175999999999974</v>
+        <v>41.401000000000003</v>
       </c>
       <c r="P29" s="8">
-        <f t="shared" si="22"/>
-        <v>-33.781999999999996</v>
+        <v>46.956000000000003</v>
       </c>
       <c r="Q29" s="8">
-        <f t="shared" si="22"/>
-        <v>64.026000000000025</v>
+        <v>34.908000000000001</v>
       </c>
       <c r="R29" s="8">
-        <f t="shared" si="22"/>
-        <v>123.96700000000008</v>
+        <v>80.917000000000002</v>
       </c>
       <c r="S29" s="8">
-        <f>+S26-S27+S28</f>
-        <v>173.34100000000004</v>
+        <v>61.338000000000001</v>
       </c>
       <c r="T29" s="8">
-        <f>+T26-T27+T28</f>
-        <v>179.73700000000011</v>
+        <v>67.558999999999997</v>
       </c>
       <c r="U29" s="8">
-        <f>+U26-U27+U28</f>
-        <v>198.69600000000014</v>
+        <v>84.634</v>
       </c>
       <c r="V29" s="8"/>
       <c r="W29" s="8"/>
@@ -3633,53 +3600,53 @@
     </row>
     <row r="30" spans="2:67" x14ac:dyDescent="0.2">
       <c r="B30" s="2" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="C30" s="8"/>
       <c r="D30" s="8"/>
       <c r="E30" s="8">
-        <v>18.577000000000002</v>
+        <v>46.637999999999998</v>
       </c>
       <c r="F30" s="8">
-        <f t="shared" si="11"/>
-        <v>30.954999999999995</v>
+        <f t="shared" si="12"/>
+        <v>0.63500000000000512</v>
       </c>
       <c r="G30" s="8">
-        <v>29.17</v>
+        <v>19.265999999999998</v>
       </c>
       <c r="H30" s="8"/>
       <c r="I30" s="8">
-        <v>30.706</v>
+        <v>47.203000000000003</v>
       </c>
       <c r="J30" s="8"/>
       <c r="K30" s="8">
-        <v>31.62</v>
+        <v>21.797000000000001</v>
       </c>
       <c r="L30" s="8"/>
       <c r="M30" s="8"/>
       <c r="N30" s="8">
-        <v>14.24</v>
+        <v>22.074000000000002</v>
       </c>
       <c r="O30" s="8">
-        <v>16.093</v>
+        <v>27.201000000000001</v>
       </c>
       <c r="P30" s="8">
-        <v>-1.7130000000000001</v>
+        <v>27.992000000000001</v>
       </c>
       <c r="Q30" s="8">
-        <v>7.7309999999999999</v>
+        <v>21.898</v>
       </c>
       <c r="R30" s="8">
-        <v>36.762</v>
+        <v>70.471999999999994</v>
       </c>
       <c r="S30" s="8">
-        <v>49.531999999999996</v>
+        <v>47.273000000000003</v>
       </c>
       <c r="T30" s="8">
-        <v>51.223999999999997</v>
+        <v>35.625</v>
       </c>
       <c r="U30" s="8">
-        <v>56.707000000000001</v>
+        <v>55.545999999999999</v>
       </c>
       <c r="V30" s="8"/>
       <c r="W30" s="8"/>
@@ -3730,77 +3697,77 @@
     </row>
     <row r="31" spans="2:67" x14ac:dyDescent="0.2">
       <c r="B31" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C31" s="8">
-        <f t="shared" ref="C31:F31" si="23">+C29-C30</f>
+        <f t="shared" ref="C31:F31" si="21">+C28-C29+C30</f>
         <v>0</v>
       </c>
       <c r="D31" s="8">
-        <f t="shared" si="23"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="E31" s="8">
-        <f t="shared" si="23"/>
-        <v>66.686999999999998</v>
+        <f t="shared" si="21"/>
+        <v>85.263999999999996</v>
       </c>
       <c r="F31" s="8">
-        <f t="shared" si="23"/>
-        <v>57.121999999999971</v>
+        <f t="shared" si="21"/>
+        <v>88.07699999999997</v>
       </c>
       <c r="G31" s="8">
-        <f>+G29-G30</f>
-        <v>66.077000000000041</v>
+        <f>+G28-G29+G30</f>
+        <v>95.247000000000043</v>
       </c>
       <c r="H31" s="8">
-        <f t="shared" ref="H31:K31" si="24">+H29-H30</f>
+        <f t="shared" ref="H31:K31" si="22">+H28-H29+H30</f>
         <v>0</v>
       </c>
       <c r="I31" s="8">
-        <f t="shared" si="24"/>
-        <v>76.649999999999949</v>
+        <f t="shared" si="22"/>
+        <v>107.35599999999995</v>
       </c>
       <c r="J31" s="8">
-        <f t="shared" si="24"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="K31" s="8">
-        <f t="shared" si="24"/>
-        <v>78.168999999999954</v>
+        <f t="shared" si="22"/>
+        <v>109.78899999999996</v>
       </c>
       <c r="L31" s="8"/>
       <c r="M31" s="8"/>
       <c r="N31" s="8">
-        <f t="shared" ref="N31:R31" si="25">+N29-N30</f>
-        <v>51.042000000000009</v>
+        <f t="shared" ref="N31:R31" si="23">+N28-N29+N30</f>
+        <v>65.282000000000011</v>
       </c>
       <c r="O31" s="8">
-        <f t="shared" si="25"/>
-        <v>53.08299999999997</v>
+        <f t="shared" si="23"/>
+        <v>69.175999999999974</v>
       </c>
       <c r="P31" s="8">
-        <f t="shared" si="25"/>
-        <v>-32.068999999999996</v>
+        <f t="shared" si="23"/>
+        <v>-33.781999999999996</v>
       </c>
       <c r="Q31" s="8">
-        <f t="shared" si="25"/>
-        <v>56.295000000000023</v>
+        <f t="shared" si="23"/>
+        <v>64.026000000000025</v>
       </c>
       <c r="R31" s="8">
-        <f t="shared" si="25"/>
-        <v>87.205000000000084</v>
+        <f t="shared" si="23"/>
+        <v>123.96700000000008</v>
       </c>
       <c r="S31" s="8">
-        <f>+S29-S30</f>
-        <v>123.80900000000004</v>
+        <f>+S28-S29+S30</f>
+        <v>173.34100000000004</v>
       </c>
       <c r="T31" s="8">
-        <f>+T29-T30</f>
-        <v>128.51300000000012</v>
+        <f>+T28-T29+T30</f>
+        <v>179.73700000000011</v>
       </c>
       <c r="U31" s="8">
-        <f>+U29-U30</f>
-        <v>141.98900000000015</v>
+        <f>+U28-U29+U30</f>
+        <v>198.69600000000014</v>
       </c>
       <c r="V31" s="8"/>
       <c r="W31" s="8"/>
@@ -3851,53 +3818,53 @@
     </row>
     <row r="32" spans="2:67" x14ac:dyDescent="0.2">
       <c r="B32" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C32" s="8"/>
       <c r="D32" s="8"/>
       <c r="E32" s="8">
-        <v>4.9050000000000002</v>
+        <v>18.577000000000002</v>
       </c>
       <c r="F32" s="8">
-        <f t="shared" si="11"/>
-        <v>4.2869999999999999</v>
+        <f t="shared" si="12"/>
+        <v>30.954999999999995</v>
       </c>
       <c r="G32" s="8">
-        <v>5.1379999999999999</v>
+        <v>29.17</v>
       </c>
       <c r="H32" s="8"/>
       <c r="I32" s="8">
-        <v>3.387</v>
+        <v>30.706</v>
       </c>
       <c r="J32" s="8"/>
       <c r="K32" s="8">
-        <v>2.0470000000000002</v>
+        <v>31.62</v>
       </c>
       <c r="L32" s="8"/>
       <c r="M32" s="8"/>
       <c r="N32" s="8">
-        <v>0.35</v>
+        <v>14.24</v>
       </c>
       <c r="O32" s="8">
-        <v>0.53</v>
+        <v>16.093</v>
       </c>
       <c r="P32" s="8">
-        <v>1.147</v>
+        <v>-1.7130000000000001</v>
       </c>
       <c r="Q32" s="8">
-        <v>2.9729999999999999</v>
+        <v>7.7309999999999999</v>
       </c>
       <c r="R32" s="8">
-        <v>6.6059999999999999</v>
+        <v>36.762</v>
       </c>
       <c r="S32" s="8">
-        <v>9.1920000000000002</v>
+        <v>49.531999999999996</v>
       </c>
       <c r="T32" s="8">
-        <v>9.0340000000000007</v>
+        <v>51.223999999999997</v>
       </c>
       <c r="U32" s="8">
-        <v>6.9550000000000001</v>
+        <v>56.707000000000001</v>
       </c>
       <c r="V32" s="8"/>
       <c r="W32" s="8"/>
@@ -3948,77 +3915,77 @@
     </row>
     <row r="33" spans="2:67" x14ac:dyDescent="0.2">
       <c r="B33" s="2" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="C33" s="8">
-        <f t="shared" ref="C33:F33" si="26">+C31-C32</f>
+        <f t="shared" ref="C33:F33" si="24">+C31-C32</f>
         <v>0</v>
       </c>
       <c r="D33" s="8">
-        <f t="shared" si="26"/>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="E33" s="8">
-        <f t="shared" si="26"/>
-        <v>61.781999999999996</v>
+        <f t="shared" si="24"/>
+        <v>66.686999999999998</v>
       </c>
       <c r="F33" s="8">
-        <f t="shared" si="26"/>
-        <v>52.834999999999972</v>
+        <f t="shared" si="24"/>
+        <v>57.121999999999971</v>
       </c>
       <c r="G33" s="8">
         <f>+G31-G32</f>
-        <v>60.939000000000043</v>
+        <v>66.077000000000041</v>
       </c>
       <c r="H33" s="8">
-        <f t="shared" ref="H33:K33" si="27">+H31-H32</f>
+        <f t="shared" ref="H33:K33" si="25">+H31-H32</f>
         <v>0</v>
       </c>
       <c r="I33" s="8">
-        <f t="shared" si="27"/>
-        <v>73.262999999999948</v>
+        <f t="shared" si="25"/>
+        <v>76.649999999999949</v>
       </c>
       <c r="J33" s="8">
-        <f t="shared" si="27"/>
+        <f t="shared" si="25"/>
         <v>0</v>
       </c>
       <c r="K33" s="8">
-        <f t="shared" si="27"/>
-        <v>76.121999999999957</v>
+        <f t="shared" si="25"/>
+        <v>78.168999999999954</v>
       </c>
       <c r="L33" s="8"/>
       <c r="M33" s="8"/>
       <c r="N33" s="8">
-        <f t="shared" ref="N33:Q33" si="28">+N31-N32</f>
-        <v>50.692000000000007</v>
+        <f t="shared" ref="N33:R33" si="26">+N31-N32</f>
+        <v>51.042000000000009</v>
       </c>
       <c r="O33" s="8">
-        <f t="shared" si="28"/>
-        <v>52.552999999999969</v>
+        <f t="shared" si="26"/>
+        <v>53.08299999999997</v>
       </c>
       <c r="P33" s="8">
-        <f>+P31-P32</f>
-        <v>-33.215999999999994</v>
+        <f t="shared" si="26"/>
+        <v>-32.068999999999996</v>
       </c>
       <c r="Q33" s="8">
-        <f t="shared" si="28"/>
-        <v>53.322000000000024</v>
+        <f t="shared" si="26"/>
+        <v>56.295000000000023</v>
       </c>
       <c r="R33" s="8">
-        <f>+R31-R32</f>
-        <v>80.599000000000089</v>
+        <f t="shared" si="26"/>
+        <v>87.205000000000084</v>
       </c>
       <c r="S33" s="8">
         <f>+S31-S32</f>
-        <v>114.61700000000005</v>
+        <v>123.80900000000004</v>
       </c>
       <c r="T33" s="8">
         <f>+T31-T32</f>
-        <v>119.47900000000011</v>
+        <v>128.51300000000012</v>
       </c>
       <c r="U33" s="8">
         <f>+U31-U32</f>
-        <v>135.03400000000013</v>
+        <v>141.98900000000015</v>
       </c>
       <c r="V33" s="8"/>
       <c r="W33" s="8"/>
@@ -4068,25 +4035,55 @@
       <c r="BO33" s="8"/>
     </row>
     <row r="34" spans="2:67" x14ac:dyDescent="0.2">
+      <c r="B34" s="2" t="s">
+        <v>49</v>
+      </c>
       <c r="C34" s="8"/>
       <c r="D34" s="8"/>
-      <c r="E34" s="8"/>
-      <c r="F34" s="8"/>
-      <c r="G34" s="8"/>
+      <c r="E34" s="8">
+        <v>4.9050000000000002</v>
+      </c>
+      <c r="F34" s="8">
+        <f t="shared" si="12"/>
+        <v>4.2869999999999999</v>
+      </c>
+      <c r="G34" s="8">
+        <v>5.1379999999999999</v>
+      </c>
       <c r="H34" s="8"/>
-      <c r="I34" s="8"/>
+      <c r="I34" s="8">
+        <v>3.387</v>
+      </c>
       <c r="J34" s="8"/>
-      <c r="K34" s="8"/>
+      <c r="K34" s="8">
+        <v>2.0470000000000002</v>
+      </c>
       <c r="L34" s="8"/>
       <c r="M34" s="8"/>
-      <c r="N34" s="8"/>
-      <c r="O34" s="8"/>
-      <c r="P34" s="8"/>
-      <c r="Q34" s="8"/>
-      <c r="R34" s="8"/>
-      <c r="S34" s="8"/>
-      <c r="T34" s="8"/>
-      <c r="U34" s="8"/>
+      <c r="N34" s="8">
+        <v>0.35</v>
+      </c>
+      <c r="O34" s="8">
+        <v>0.53</v>
+      </c>
+      <c r="P34" s="8">
+        <v>1.147</v>
+      </c>
+      <c r="Q34" s="8">
+        <v>2.9729999999999999</v>
+      </c>
+      <c r="R34" s="8">
+        <v>6.6059999999999999</v>
+      </c>
+      <c r="S34" s="8">
+        <v>9.1920000000000002</v>
+      </c>
+      <c r="T34" s="8">
+        <v>9.0340000000000007</v>
+      </c>
+      <c r="U34" s="8">
+        <v>6.9550000000000001</v>
+      </c>
       <c r="V34" s="8"/>
       <c r="W34" s="8"/>
       <c r="X34" s="8"/>
@@ -4136,77 +4133,77 @@
     </row>
     <row r="35" spans="2:67" x14ac:dyDescent="0.2">
       <c r="B35" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="C35" s="7" t="e">
-        <f t="shared" ref="C35:D35" si="29">+C33/C36</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="D35" s="7" t="e">
+        <v>50</v>
+      </c>
+      <c r="C35" s="8">
+        <f t="shared" ref="C35:F35" si="27">+C33-C34</f>
+        <v>0</v>
+      </c>
+      <c r="D35" s="8">
+        <f t="shared" si="27"/>
+        <v>0</v>
+      </c>
+      <c r="E35" s="8">
+        <f t="shared" si="27"/>
+        <v>61.781999999999996</v>
+      </c>
+      <c r="F35" s="8">
+        <f t="shared" si="27"/>
+        <v>52.834999999999972</v>
+      </c>
+      <c r="G35" s="8">
+        <f>+G33-G34</f>
+        <v>60.939000000000043</v>
+      </c>
+      <c r="H35" s="8">
+        <f t="shared" ref="H35:K35" si="28">+H33-H34</f>
+        <v>0</v>
+      </c>
+      <c r="I35" s="8">
+        <f t="shared" si="28"/>
+        <v>73.262999999999948</v>
+      </c>
+      <c r="J35" s="8">
+        <f t="shared" si="28"/>
+        <v>0</v>
+      </c>
+      <c r="K35" s="8">
+        <f t="shared" si="28"/>
+        <v>76.121999999999957</v>
+      </c>
+      <c r="L35" s="8"/>
+      <c r="M35" s="8"/>
+      <c r="N35" s="8">
+        <f t="shared" ref="N35:Q35" si="29">+N33-N34</f>
+        <v>50.692000000000007</v>
+      </c>
+      <c r="O35" s="8">
         <f t="shared" si="29"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="E35" s="7">
-        <f>+E33/E36</f>
-        <v>0.90879845229778977</v>
-      </c>
-      <c r="F35" s="7">
-        <f t="shared" ref="F35:K35" si="30">+F33/F36</f>
-        <v>0.77719022089206724</v>
-      </c>
-      <c r="G35" s="7">
-        <f t="shared" si="30"/>
-        <v>0.89703669208184811</v>
-      </c>
-      <c r="H35" s="7">
-        <f t="shared" si="30"/>
-        <v>0</v>
-      </c>
-      <c r="I35" s="7">
-        <f t="shared" si="30"/>
-        <v>1.0784489271565394</v>
-      </c>
-      <c r="J35" s="7" t="e">
-        <f t="shared" si="30"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="K35" s="7">
-        <f t="shared" si="30"/>
-        <v>1.1205340926935847</v>
-      </c>
-      <c r="L35" s="7"/>
-      <c r="M35" s="8"/>
-      <c r="N35" s="7">
-        <f t="shared" ref="N35" si="31">+N33/N36</f>
-        <v>0.74547058823529422</v>
-      </c>
-      <c r="O35" s="7">
-        <f t="shared" ref="O35" si="32">+O33/O36</f>
-        <v>0.77283823529411722</v>
-      </c>
-      <c r="P35" s="7">
-        <f t="shared" ref="P35" si="33">+P33/P36</f>
-        <v>-0.48847058823529405</v>
-      </c>
-      <c r="Q35" s="7">
-        <f t="shared" ref="Q35" si="34">+Q33/Q36</f>
-        <v>0.78414705882352975</v>
-      </c>
-      <c r="R35" s="7">
-        <f t="shared" ref="R35" si="35">+R33/R36</f>
-        <v>1.1852794117647072</v>
-      </c>
-      <c r="S35" s="7">
-        <f>+S33/S36</f>
-        <v>1.6857645313595349</v>
-      </c>
-      <c r="T35" s="7">
-        <f>+T33/T36</f>
-        <v>1.7572738812070285</v>
-      </c>
-      <c r="U35" s="7">
-        <f>+U33/U36</f>
-        <v>1.98605379418065</v>
+        <v>52.552999999999969</v>
+      </c>
+      <c r="P35" s="8">
+        <f>+P33-P34</f>
+        <v>-33.215999999999994</v>
+      </c>
+      <c r="Q35" s="8">
+        <f t="shared" si="29"/>
+        <v>53.322000000000024</v>
+      </c>
+      <c r="R35" s="8">
+        <f>+R33-R34</f>
+        <v>80.599000000000089</v>
+      </c>
+      <c r="S35" s="8">
+        <f>+S33-S34</f>
+        <v>114.61700000000005</v>
+      </c>
+      <c r="T35" s="8">
+        <f>+T33-T34</f>
+        <v>119.47900000000011</v>
+      </c>
+      <c r="U35" s="8">
+        <f>+U33-U34</f>
+        <v>135.03400000000013</v>
       </c>
       <c r="V35" s="8"/>
       <c r="W35" s="8"/>
@@ -4256,56 +4253,25 @@
       <c r="BO35" s="8"/>
     </row>
     <row r="36" spans="2:67" x14ac:dyDescent="0.2">
-      <c r="B36" s="2" t="s">
-        <v>2</v>
-      </c>
       <c r="C36" s="8"/>
       <c r="D36" s="8"/>
-      <c r="E36" s="8">
-        <v>67.982069999999993</v>
-      </c>
-      <c r="F36" s="8">
-        <v>67.982069999999993</v>
-      </c>
-      <c r="G36" s="8">
-        <v>67.933676000000006</v>
-      </c>
-      <c r="H36" s="8">
-        <v>67.933676000000006</v>
-      </c>
-      <c r="I36" s="8">
-        <v>67.933676000000006</v>
-      </c>
+      <c r="E36" s="8"/>
+      <c r="F36" s="8"/>
+      <c r="G36" s="8"/>
+      <c r="H36" s="8"/>
+      <c r="I36" s="8"/>
       <c r="J36" s="8"/>
-      <c r="K36" s="8">
-        <v>67.933676000000006</v>
-      </c>
+      <c r="K36" s="8"/>
       <c r="L36" s="8"/>
       <c r="M36" s="8"/>
-      <c r="N36" s="8">
-        <v>68</v>
-      </c>
-      <c r="O36" s="8">
-        <v>68</v>
-      </c>
-      <c r="P36" s="8">
-        <v>68</v>
-      </c>
-      <c r="Q36" s="8">
-        <v>68</v>
-      </c>
-      <c r="R36" s="8">
-        <v>68</v>
-      </c>
-      <c r="S36" s="8">
-        <v>67.991108999999994</v>
-      </c>
-      <c r="T36" s="8">
-        <v>67.991108999999994</v>
-      </c>
-      <c r="U36" s="8">
-        <v>67.991108999999994</v>
-      </c>
+      <c r="N36" s="8"/>
+      <c r="O36" s="8"/>
+      <c r="P36" s="8"/>
+      <c r="Q36" s="8"/>
+      <c r="R36" s="8"/>
+      <c r="S36" s="8"/>
+      <c r="T36" s="8"/>
+      <c r="U36" s="8"/>
       <c r="V36" s="8"/>
       <c r="W36" s="8"/>
       <c r="X36" s="8"/>
@@ -4354,25 +4320,79 @@
       <c r="BO36" s="8"/>
     </row>
     <row r="37" spans="2:67" x14ac:dyDescent="0.2">
-      <c r="C37" s="8"/>
-      <c r="D37" s="8"/>
-      <c r="E37" s="8"/>
-      <c r="F37" s="8"/>
-      <c r="G37" s="8"/>
-      <c r="H37" s="8"/>
-      <c r="I37" s="8"/>
-      <c r="J37" s="8"/>
-      <c r="K37" s="8"/>
-      <c r="L37" s="8"/>
+      <c r="B37" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="C37" s="7" t="e">
+        <f t="shared" ref="C37:D37" si="30">+C35/C38</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="D37" s="7" t="e">
+        <f t="shared" si="30"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="E37" s="7">
+        <f>+E35/E38</f>
+        <v>0.90879845229778977</v>
+      </c>
+      <c r="F37" s="7">
+        <f t="shared" ref="F37:K37" si="31">+F35/F38</f>
+        <v>0.77719022089206724</v>
+      </c>
+      <c r="G37" s="7">
+        <f t="shared" si="31"/>
+        <v>0.89703669208184811</v>
+      </c>
+      <c r="H37" s="7">
+        <f t="shared" si="31"/>
+        <v>0</v>
+      </c>
+      <c r="I37" s="7">
+        <f t="shared" si="31"/>
+        <v>1.0784489271565394</v>
+      </c>
+      <c r="J37" s="7" t="e">
+        <f t="shared" si="31"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="K37" s="7">
+        <f t="shared" si="31"/>
+        <v>1.1205340926935847</v>
+      </c>
+      <c r="L37" s="7"/>
       <c r="M37" s="8"/>
-      <c r="N37" s="8"/>
-      <c r="O37" s="8"/>
-      <c r="P37" s="8"/>
-      <c r="Q37" s="8"/>
-      <c r="R37" s="8"/>
-      <c r="S37" s="8"/>
-      <c r="T37" s="8"/>
-      <c r="U37" s="8"/>
+      <c r="N37" s="7">
+        <f t="shared" ref="N37" si="32">+N35/N38</f>
+        <v>0.74547058823529422</v>
+      </c>
+      <c r="O37" s="7">
+        <f t="shared" ref="O37" si="33">+O35/O38</f>
+        <v>0.77283823529411722</v>
+      </c>
+      <c r="P37" s="7">
+        <f t="shared" ref="P37" si="34">+P35/P38</f>
+        <v>-0.48847058823529405</v>
+      </c>
+      <c r="Q37" s="7">
+        <f t="shared" ref="Q37" si="35">+Q35/Q38</f>
+        <v>0.78414705882352975</v>
+      </c>
+      <c r="R37" s="7">
+        <f t="shared" ref="R37" si="36">+R35/R38</f>
+        <v>1.1852794117647072</v>
+      </c>
+      <c r="S37" s="7">
+        <f>+S35/S38</f>
+        <v>1.6857645313595349</v>
+      </c>
+      <c r="T37" s="7">
+        <f>+T35/T38</f>
+        <v>1.7572738812070285</v>
+      </c>
+      <c r="U37" s="7">
+        <f>+U35/U38</f>
+        <v>1.98605379418065</v>
+      </c>
       <c r="V37" s="8"/>
       <c r="W37" s="8"/>
       <c r="X37" s="8"/>
@@ -4422,47 +4442,54 @@
     </row>
     <row r="38" spans="2:67" x14ac:dyDescent="0.2">
       <c r="B38" s="2" t="s">
-        <v>54</v>
+        <v>2</v>
       </c>
       <c r="C38" s="8"/>
       <c r="D38" s="8"/>
-      <c r="E38" s="8"/>
-      <c r="F38" s="8"/>
-      <c r="G38" s="8"/>
-      <c r="H38" s="8"/>
-      <c r="I38" s="8"/>
+      <c r="E38" s="8">
+        <v>67.982069999999993</v>
+      </c>
+      <c r="F38" s="8">
+        <v>67.982069999999993</v>
+      </c>
+      <c r="G38" s="8">
+        <v>67.933676000000006</v>
+      </c>
+      <c r="H38" s="8">
+        <v>67.933676000000006</v>
+      </c>
+      <c r="I38" s="8">
+        <v>67.933676000000006</v>
+      </c>
       <c r="J38" s="8"/>
-      <c r="K38" s="8"/>
+      <c r="K38" s="8">
+        <v>67.933676000000006</v>
+      </c>
       <c r="L38" s="8"/>
       <c r="M38" s="8"/>
-      <c r="N38" s="8"/>
-      <c r="O38" s="10">
-        <f t="shared" ref="O38:R38" si="36">+O7/N7-1</f>
-        <v>7.0866141732283561E-2</v>
-      </c>
-      <c r="P38" s="10">
-        <f t="shared" si="36"/>
-        <v>1.4705882352941124E-2</v>
-      </c>
-      <c r="Q38" s="10">
-        <f t="shared" si="36"/>
-        <v>4.3478260869565188E-2</v>
-      </c>
-      <c r="R38" s="10">
-        <f t="shared" si="36"/>
-        <v>3.4722222222222321E-2</v>
-      </c>
-      <c r="S38" s="10">
-        <f>+S7/R7-1</f>
-        <v>2.0134228187919545E-2</v>
-      </c>
-      <c r="T38" s="10">
-        <f>+T7/S7-1</f>
-        <v>-1</v>
-      </c>
-      <c r="U38" s="10" t="e">
-        <f>+U7/T7-1</f>
-        <v>#DIV/0!</v>
+      <c r="N38" s="8">
+        <v>68</v>
+      </c>
+      <c r="O38" s="8">
+        <v>68</v>
+      </c>
+      <c r="P38" s="8">
+        <v>68</v>
+      </c>
+      <c r="Q38" s="8">
+        <v>68</v>
+      </c>
+      <c r="R38" s="8">
+        <v>68</v>
+      </c>
+      <c r="S38" s="8">
+        <v>67.991108999999994</v>
+      </c>
+      <c r="T38" s="8">
+        <v>67.991108999999994</v>
+      </c>
+      <c r="U38" s="8">
+        <v>67.991108999999994</v>
       </c>
       <c r="V38" s="8"/>
       <c r="W38" s="8"/>
@@ -4512,9 +4539,6 @@
       <c r="BO38" s="8"/>
     </row>
     <row r="39" spans="2:67" x14ac:dyDescent="0.2">
-      <c r="B39" s="2" t="s">
-        <v>55</v>
-      </c>
       <c r="C39" s="8"/>
       <c r="D39" s="8"/>
       <c r="E39" s="8"/>
@@ -4527,34 +4551,13 @@
       <c r="L39" s="8"/>
       <c r="M39" s="8"/>
       <c r="N39" s="8"/>
-      <c r="O39" s="10">
-        <f t="shared" ref="O39:R42" si="37">+O10/N10-1</f>
-        <v>8.0589101260178264E-2</v>
-      </c>
-      <c r="P39" s="10">
-        <f t="shared" si="37"/>
-        <v>-2.1605426794799376E-2</v>
-      </c>
-      <c r="Q39" s="10">
-        <f t="shared" si="37"/>
-        <v>0.26619212147124416</v>
-      </c>
-      <c r="R39" s="10">
-        <f t="shared" si="37"/>
-        <v>0.20380561259411367</v>
-      </c>
-      <c r="S39" s="10">
-        <f>+S10/R10-1</f>
-        <v>0.13481468003972474</v>
-      </c>
-      <c r="T39" s="10">
-        <f>+T10/S10-1</f>
-        <v>5.4399091455675119E-2</v>
-      </c>
-      <c r="U39" s="10">
-        <f>+U10/T10-1</f>
-        <v>0.56785969980929218</v>
-      </c>
+      <c r="O39" s="8"/>
+      <c r="P39" s="8"/>
+      <c r="Q39" s="8"/>
+      <c r="R39" s="8"/>
+      <c r="S39" s="8"/>
+      <c r="T39" s="8"/>
+      <c r="U39" s="8"/>
       <c r="V39" s="8"/>
       <c r="W39" s="8"/>
       <c r="X39" s="8"/>
@@ -4604,7 +4607,7 @@
     </row>
     <row r="40" spans="2:67" x14ac:dyDescent="0.2">
       <c r="B40" s="2" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="C40" s="8"/>
       <c r="D40" s="8"/>
@@ -4619,32 +4622,32 @@
       <c r="M40" s="8"/>
       <c r="N40" s="8"/>
       <c r="O40" s="10">
-        <f t="shared" si="37"/>
-        <v>1.700294717751083E-2</v>
+        <f t="shared" ref="O40:R40" si="37">+O9/N9-1</f>
+        <v>7.0866141732283561E-2</v>
       </c>
       <c r="P40" s="10">
         <f t="shared" si="37"/>
-        <v>-0.23848640213999117</v>
+        <v>1.4705882352941124E-2</v>
       </c>
       <c r="Q40" s="10">
         <f t="shared" si="37"/>
-        <v>0.2327181183496041</v>
+        <v>4.3478260869565188E-2</v>
       </c>
       <c r="R40" s="10">
         <f t="shared" si="37"/>
-        <v>0.22001116084679961</v>
+        <v>3.4722222222222321E-2</v>
       </c>
       <c r="S40" s="10">
-        <f t="shared" ref="S40:U42" si="38">+S11/R11-1</f>
-        <v>0.25399745019610132</v>
+        <f>+S9/R9-1</f>
+        <v>2.0134228187919545E-2</v>
       </c>
       <c r="T40" s="10">
-        <f t="shared" si="38"/>
-        <v>9.3665600844379471E-2</v>
+        <f>+T9/S9-1</f>
+        <v>3.289473684210531E-2</v>
       </c>
       <c r="U40" s="10">
-        <f t="shared" si="38"/>
-        <v>-1</v>
+        <f>+U9/T9-1</f>
+        <v>4.4585987261146487E-2</v>
       </c>
       <c r="V40" s="8"/>
       <c r="W40" s="8"/>
@@ -4695,7 +4698,7 @@
     </row>
     <row r="41" spans="2:67" x14ac:dyDescent="0.2">
       <c r="B41" s="2" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="C41" s="8"/>
       <c r="D41" s="8"/>
@@ -4710,32 +4713,32 @@
       <c r="M41" s="8"/>
       <c r="N41" s="8"/>
       <c r="O41" s="10">
-        <f t="shared" si="37"/>
-        <v>9.8976692516396403E-2</v>
+        <f t="shared" ref="O41:R44" si="38">+O12/N12-1</f>
+        <v>8.0589101260178264E-2</v>
       </c>
       <c r="P41" s="10">
-        <f t="shared" si="37"/>
-        <v>-0.15321138369425769</v>
+        <f t="shared" si="38"/>
+        <v>-2.1605426794799376E-2</v>
       </c>
       <c r="Q41" s="10">
-        <f t="shared" si="37"/>
-        <v>0.36728228555686915</v>
+        <f t="shared" si="38"/>
+        <v>0.26619212147124416</v>
       </c>
       <c r="R41" s="10">
-        <f t="shared" si="37"/>
-        <v>0.4048682410026947</v>
+        <f t="shared" si="38"/>
+        <v>0.20380561259411367</v>
       </c>
       <c r="S41" s="10">
-        <f t="shared" si="38"/>
-        <v>0.20842981478548994</v>
+        <f>+S12/R12-1</f>
+        <v>0.13481468003972474</v>
       </c>
       <c r="T41" s="10">
-        <f t="shared" si="38"/>
-        <v>0.17828029462014139</v>
+        <f>+T12/S12-1</f>
+        <v>5.4399091455675119E-2</v>
       </c>
       <c r="U41" s="10">
-        <f t="shared" si="38"/>
-        <v>9.2179562236784918E-2</v>
+        <f>+U12/T12-1</f>
+        <v>0.56785969980929218</v>
       </c>
       <c r="V41" s="8"/>
       <c r="W41" s="8"/>
@@ -4786,7 +4789,7 @@
     </row>
     <row r="42" spans="2:67" x14ac:dyDescent="0.2">
       <c r="B42" s="2" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="C42" s="8"/>
       <c r="D42" s="8"/>
@@ -4801,32 +4804,32 @@
       <c r="M42" s="8"/>
       <c r="N42" s="8"/>
       <c r="O42" s="10">
-        <f t="shared" si="37"/>
-        <v>0.18922456581132008</v>
+        <f t="shared" si="38"/>
+        <v>1.700294717751083E-2</v>
       </c>
       <c r="P42" s="10">
-        <f t="shared" si="37"/>
-        <v>-5.1731142842368794E-2</v>
+        <f t="shared" si="38"/>
+        <v>-0.23848640213999117</v>
       </c>
       <c r="Q42" s="10">
-        <f t="shared" si="37"/>
-        <v>0.32872166394017288</v>
+        <f t="shared" si="38"/>
+        <v>0.2327181183496041</v>
       </c>
       <c r="R42" s="10">
-        <f t="shared" si="37"/>
-        <v>0.2807091599831153</v>
+        <f t="shared" si="38"/>
+        <v>0.22001116084679961</v>
       </c>
       <c r="S42" s="10">
-        <f t="shared" si="38"/>
-        <v>0.40415568007031433</v>
+        <f t="shared" ref="S42:U44" si="39">+S13/R13-1</f>
+        <v>0.25399745019610132</v>
       </c>
       <c r="T42" s="10">
-        <f t="shared" si="38"/>
-        <v>0.12603387288701962</v>
+        <f t="shared" si="39"/>
+        <v>9.3665600844379471E-2</v>
       </c>
       <c r="U42" s="10">
-        <f t="shared" si="38"/>
-        <v>0.13650787216917482</v>
+        <f t="shared" si="39"/>
+        <v>-1</v>
       </c>
       <c r="V42" s="8"/>
       <c r="W42" s="8"/>
@@ -4876,69 +4879,48 @@
       <c r="BO42" s="8"/>
     </row>
     <row r="43" spans="2:67" x14ac:dyDescent="0.2">
-      <c r="B43" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="C43" s="9"/>
-      <c r="D43" s="9"/>
-      <c r="E43" s="11" t="e">
-        <f t="shared" ref="E43" si="39">+E16/C16-1</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="F43" s="11" t="e">
-        <f t="shared" ref="F43" si="40">+F16/D16-1</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="G43" s="11">
-        <f t="shared" ref="G43:H43" si="41">+G16/E16-1</f>
-        <v>0.1410444495920522</v>
-      </c>
-      <c r="H43" s="11">
-        <f t="shared" si="41"/>
-        <v>-1</v>
-      </c>
-      <c r="I43" s="11">
-        <f>+I16/G16-1</f>
-        <v>0.10226661210127252</v>
-      </c>
-      <c r="J43" s="11" t="e">
-        <f t="shared" ref="J43:K43" si="42">+J16/H16-1</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="K43" s="11">
-        <f t="shared" si="42"/>
-        <v>9.5413916843897661E-2</v>
-      </c>
-      <c r="L43" s="11"/>
-      <c r="M43" s="9"/>
-      <c r="N43" s="9"/>
-      <c r="O43" s="11">
-        <f t="shared" ref="O43:S43" si="43">+O16/N16-1</f>
-        <v>9.9033266063407233E-2</v>
-      </c>
-      <c r="P43" s="11">
-        <f t="shared" si="43"/>
-        <v>-0.10488991560827354</v>
-      </c>
-      <c r="Q43" s="11">
-        <f t="shared" si="43"/>
-        <v>0.30912128938095229</v>
-      </c>
-      <c r="R43" s="11">
-        <f t="shared" si="43"/>
-        <v>0.29140005532317015</v>
-      </c>
-      <c r="S43" s="11">
-        <f t="shared" si="43"/>
-        <v>0.23889321393311791</v>
-      </c>
-      <c r="T43" s="11">
-        <f>+T16/S16-1</f>
-        <v>0.12209720735110841</v>
-      </c>
-      <c r="U43" s="11">
-        <f>+U16/T16-1</f>
-        <v>0.10121779529776154</v>
+      <c r="B43" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="C43" s="8"/>
+      <c r="D43" s="8"/>
+      <c r="E43" s="8"/>
+      <c r="F43" s="8"/>
+      <c r="G43" s="8"/>
+      <c r="H43" s="8"/>
+      <c r="I43" s="8"/>
+      <c r="J43" s="8"/>
+      <c r="K43" s="8"/>
+      <c r="L43" s="8"/>
+      <c r="M43" s="8"/>
+      <c r="N43" s="8"/>
+      <c r="O43" s="10">
+        <f t="shared" si="38"/>
+        <v>9.8976692516396403E-2</v>
+      </c>
+      <c r="P43" s="10">
+        <f t="shared" si="38"/>
+        <v>-0.15321138369425769</v>
+      </c>
+      <c r="Q43" s="10">
+        <f t="shared" si="38"/>
+        <v>0.36728228555686915</v>
+      </c>
+      <c r="R43" s="10">
+        <f t="shared" si="38"/>
+        <v>0.4048682410026947</v>
+      </c>
+      <c r="S43" s="10">
+        <f t="shared" si="39"/>
+        <v>0.20842981478548994</v>
+      </c>
+      <c r="T43" s="10">
+        <f t="shared" si="39"/>
+        <v>0.17828029462014139</v>
+      </c>
+      <c r="U43" s="10">
+        <f t="shared" si="39"/>
+        <v>9.2179562236784918E-2</v>
       </c>
       <c r="V43" s="8"/>
       <c r="W43" s="8"/>
@@ -4989,77 +4971,47 @@
     </row>
     <row r="44" spans="2:67" x14ac:dyDescent="0.2">
       <c r="B44" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="C44" s="10" t="e">
-        <f t="shared" ref="C44:J44" si="44">+C18/C16</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="D44" s="10" t="e">
-        <f t="shared" si="44"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="E44" s="10">
-        <f t="shared" si="44"/>
-        <v>0.90072470961977569</v>
-      </c>
-      <c r="F44" s="10">
-        <f t="shared" si="44"/>
-        <v>0.8986646022187218</v>
-      </c>
-      <c r="G44" s="10">
-        <f t="shared" si="44"/>
-        <v>0.93671918048793068</v>
-      </c>
-      <c r="H44" s="10" t="e">
-        <f t="shared" si="44"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="I44" s="10">
-        <f t="shared" si="44"/>
-        <v>0.91466011825151461</v>
-      </c>
-      <c r="J44" s="10" t="e">
-        <f t="shared" ref="J44:K44" si="45">+J18/J16</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="K44" s="10">
-        <f t="shared" si="45"/>
-        <v>0.90850547963667461</v>
-      </c>
-      <c r="L44" s="10"/>
+        <v>58</v>
+      </c>
+      <c r="C44" s="8"/>
+      <c r="D44" s="8"/>
+      <c r="E44" s="8"/>
+      <c r="F44" s="8"/>
+      <c r="G44" s="8"/>
+      <c r="H44" s="8"/>
+      <c r="I44" s="8"/>
+      <c r="J44" s="8"/>
+      <c r="K44" s="8"/>
+      <c r="L44" s="8"/>
       <c r="M44" s="8"/>
-      <c r="N44" s="10">
-        <f t="shared" ref="N44:R44" si="46">+N18/N16</f>
-        <v>0.84076557515786732</v>
-      </c>
+      <c r="N44" s="8"/>
       <c r="O44" s="10">
-        <f t="shared" si="46"/>
-        <v>0.88107331664914335</v>
+        <f t="shared" si="38"/>
+        <v>0.18922456581132008</v>
       </c>
       <c r="P44" s="10">
-        <f t="shared" si="46"/>
-        <v>0.90124316882133326</v>
+        <f t="shared" si="38"/>
+        <v>-5.1731142842368794E-2</v>
       </c>
       <c r="Q44" s="10">
-        <f t="shared" si="46"/>
-        <v>0.8404754984350844</v>
+        <f t="shared" si="38"/>
+        <v>0.32872166394017288</v>
       </c>
       <c r="R44" s="10">
-        <f t="shared" si="46"/>
-        <v>0.89612246495626868</v>
+        <f t="shared" si="38"/>
+        <v>0.2807091599831153</v>
       </c>
       <c r="S44" s="10">
-        <f>+S18/S16</f>
-        <v>0.8996480665601797</v>
+        <f t="shared" si="39"/>
+        <v>0.40415568007031433</v>
       </c>
       <c r="T44" s="10">
-        <f>+T18/T16</f>
-        <v>0.92037793107763544</v>
+        <f t="shared" si="39"/>
+        <v>0.12603387288701962</v>
       </c>
       <c r="U44" s="10">
-        <f>+U18/U16</f>
-        <v>0.9139891942262196</v>
+        <f t="shared" si="39"/>
+        <v>0.13650787216917482</v>
       </c>
       <c r="V44" s="8"/>
       <c r="W44" s="8"/>
@@ -5109,78 +5061,69 @@
       <c r="BO44" s="8"/>
     </row>
     <row r="45" spans="2:67" x14ac:dyDescent="0.2">
-      <c r="B45" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="C45" s="10" t="e">
-        <f t="shared" ref="C45:J45" si="47">+C26/C16</f>
+      <c r="B45" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="C45" s="9"/>
+      <c r="D45" s="9"/>
+      <c r="E45" s="11" t="e">
+        <f t="shared" ref="E45" si="40">+E18/C18-1</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="D45" s="10" t="e">
-        <f t="shared" si="47"/>
+      <c r="F45" s="11" t="e">
+        <f t="shared" ref="F45" si="41">+F18/D18-1</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="E45" s="10">
-        <f t="shared" si="47"/>
-        <v>0.16121755628357434</v>
-      </c>
-      <c r="F45" s="10">
-        <f t="shared" si="47"/>
-        <v>0.16745035081060924</v>
-      </c>
-      <c r="G45" s="10">
-        <f t="shared" si="47"/>
-        <v>0.16850878578034431</v>
-      </c>
-      <c r="H45" s="10" t="e">
-        <f t="shared" si="47"/>
+      <c r="G45" s="11">
+        <f t="shared" ref="G45:H45" si="42">+G18/E18-1</f>
+        <v>0.1410444495920522</v>
+      </c>
+      <c r="H45" s="11">
+        <f t="shared" si="42"/>
+        <v>-1</v>
+      </c>
+      <c r="I45" s="11">
+        <f>+I18/G18-1</f>
+        <v>0.10226661210127252</v>
+      </c>
+      <c r="J45" s="11" t="e">
+        <f t="shared" ref="J45:K45" si="43">+J18/H18-1</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="I45" s="10">
-        <f t="shared" si="47"/>
-        <v>0.1663955213517799</v>
-      </c>
-      <c r="J45" s="10" t="e">
-        <f t="shared" ref="J45:K45" si="48">+J26/J16</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="K45" s="10">
-        <f t="shared" si="48"/>
-        <v>0.1710663441022349</v>
-      </c>
-      <c r="L45" s="10"/>
-      <c r="M45" s="8"/>
-      <c r="N45" s="10">
-        <f t="shared" ref="N45:R45" si="49">+N26/N16</f>
-        <v>0.12574774501081384</v>
-      </c>
-      <c r="O45" s="10">
-        <f t="shared" si="49"/>
-        <v>0.13718550548653169</v>
-      </c>
-      <c r="P45" s="10">
-        <f t="shared" si="49"/>
-        <v>-2.7238319672507807E-2</v>
-      </c>
-      <c r="Q45" s="10">
-        <f t="shared" si="49"/>
-        <v>0.10816943493138666</v>
-      </c>
-      <c r="R45" s="10">
-        <f t="shared" si="49"/>
-        <v>0.14614638559194884</v>
-      </c>
-      <c r="S45" s="10">
-        <f>+S26/S16</f>
-        <v>0.16447490828667219</v>
-      </c>
-      <c r="T45" s="10">
-        <f>+T26/T16</f>
-        <v>0.16555680698296504</v>
-      </c>
-      <c r="U45" s="10">
-        <f>+U26/U16</f>
-        <v>0.16178403935932439</v>
+      <c r="K45" s="11">
+        <f t="shared" si="43"/>
+        <v>9.5413916843897661E-2</v>
+      </c>
+      <c r="L45" s="11"/>
+      <c r="M45" s="9"/>
+      <c r="N45" s="9"/>
+      <c r="O45" s="11">
+        <f t="shared" ref="O45:S45" si="44">+O18/N18-1</f>
+        <v>9.9033266063407233E-2</v>
+      </c>
+      <c r="P45" s="11">
+        <f t="shared" si="44"/>
+        <v>-0.10488991560827354</v>
+      </c>
+      <c r="Q45" s="11">
+        <f t="shared" si="44"/>
+        <v>0.30912128938095229</v>
+      </c>
+      <c r="R45" s="11">
+        <f t="shared" si="44"/>
+        <v>0.29140005532317015</v>
+      </c>
+      <c r="S45" s="11">
+        <f t="shared" si="44"/>
+        <v>0.23889321393311791</v>
+      </c>
+      <c r="T45" s="11">
+        <f>+T18/S18-1</f>
+        <v>0.12209720735110841</v>
+      </c>
+      <c r="U45" s="11">
+        <f>+U18/T18-1</f>
+        <v>0.10121779529776154</v>
       </c>
       <c r="V45" s="8"/>
       <c r="W45" s="8"/>
@@ -5231,77 +5174,77 @@
     </row>
     <row r="46" spans="2:67" x14ac:dyDescent="0.2">
       <c r="B46" s="2" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C46" s="10" t="e">
-        <f t="shared" ref="C46:J46" si="50">+C30/C29</f>
+        <f t="shared" ref="C46:I46" si="45">+C20/C18</f>
         <v>#DIV/0!</v>
       </c>
       <c r="D46" s="10" t="e">
-        <f t="shared" si="50"/>
+        <f t="shared" si="45"/>
         <v>#DIV/0!</v>
       </c>
       <c r="E46" s="10">
-        <f t="shared" si="50"/>
-        <v>0.21787624319759807</v>
+        <f t="shared" si="45"/>
+        <v>0.90072470961977569</v>
       </c>
       <c r="F46" s="10">
-        <f t="shared" si="50"/>
-        <v>0.35145384152502929</v>
+        <f t="shared" si="45"/>
+        <v>0.8986646022187218</v>
       </c>
       <c r="G46" s="10">
-        <f t="shared" si="50"/>
-        <v>0.30625636502986958</v>
+        <f t="shared" si="45"/>
+        <v>0.93671918048793068</v>
       </c>
       <c r="H46" s="10" t="e">
-        <f t="shared" si="50"/>
+        <f t="shared" si="45"/>
         <v>#DIV/0!</v>
       </c>
       <c r="I46" s="10">
-        <f t="shared" si="50"/>
-        <v>0.28602034352993788</v>
+        <f t="shared" si="45"/>
+        <v>0.91466011825151461</v>
       </c>
       <c r="J46" s="10" t="e">
-        <f t="shared" ref="J46:K46" si="51">+J30/J29</f>
+        <f t="shared" ref="J46:K46" si="46">+J20/J18</f>
         <v>#DIV/0!</v>
       </c>
       <c r="K46" s="10">
-        <f t="shared" si="51"/>
-        <v>0.28800699523631706</v>
+        <f t="shared" si="46"/>
+        <v>0.90850547963667461</v>
       </c>
       <c r="L46" s="10"/>
       <c r="M46" s="8"/>
       <c r="N46" s="10">
-        <f t="shared" ref="N46:R46" si="52">+N30/N29</f>
-        <v>0.21813057198002508</v>
+        <f t="shared" ref="N46:R46" si="47">+N20/N18</f>
+        <v>0.84076557515786732</v>
       </c>
       <c r="O46" s="10">
-        <f t="shared" si="52"/>
-        <v>0.23263848733664863</v>
+        <f t="shared" si="47"/>
+        <v>0.88107331664914335</v>
       </c>
       <c r="P46" s="10">
-        <f t="shared" si="52"/>
-        <v>5.0707477354804339E-2</v>
+        <f t="shared" si="47"/>
+        <v>0.90124316882133326</v>
       </c>
       <c r="Q46" s="10">
-        <f t="shared" si="52"/>
-        <v>0.12074782119763841</v>
+        <f t="shared" si="47"/>
+        <v>0.8404754984350844</v>
       </c>
       <c r="R46" s="10">
-        <f t="shared" si="52"/>
-        <v>0.29654666161155774</v>
+        <f t="shared" si="47"/>
+        <v>0.89612246495626868</v>
       </c>
       <c r="S46" s="10">
-        <f>+S30/S29</f>
-        <v>0.28574889956790367</v>
+        <f>+S20/S18</f>
+        <v>0.8996480665601797</v>
       </c>
       <c r="T46" s="10">
-        <f>+T30/T29</f>
-        <v>0.2849941859494704</v>
+        <f>+T20/T18</f>
+        <v>0.92037793107763544</v>
       </c>
       <c r="U46" s="10">
-        <f>+U30/U29</f>
-        <v>0.28539578048878667</v>
+        <f>+U20/U18</f>
+        <v>0.9139891942262196</v>
       </c>
       <c r="V46" s="8"/>
       <c r="W46" s="8"/>
@@ -5351,25 +5294,79 @@
       <c r="BO46" s="8"/>
     </row>
     <row r="47" spans="2:67" x14ac:dyDescent="0.2">
-      <c r="C47" s="8"/>
-      <c r="D47" s="8"/>
-      <c r="E47" s="8"/>
-      <c r="F47" s="8"/>
-      <c r="G47" s="8"/>
-      <c r="H47" s="8"/>
-      <c r="I47" s="8"/>
-      <c r="J47" s="8"/>
-      <c r="K47" s="8"/>
-      <c r="L47" s="8"/>
+      <c r="B47" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="C47" s="10" t="e">
+        <f t="shared" ref="C47:I47" si="48">+C28/C18</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="D47" s="10" t="e">
+        <f t="shared" si="48"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="E47" s="10">
+        <f t="shared" si="48"/>
+        <v>0.16121755628357434</v>
+      </c>
+      <c r="F47" s="10">
+        <f t="shared" si="48"/>
+        <v>0.16745035081060924</v>
+      </c>
+      <c r="G47" s="10">
+        <f t="shared" si="48"/>
+        <v>0.16850878578034431</v>
+      </c>
+      <c r="H47" s="10" t="e">
+        <f t="shared" si="48"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="I47" s="10">
+        <f t="shared" si="48"/>
+        <v>0.1663955213517799</v>
+      </c>
+      <c r="J47" s="10" t="e">
+        <f t="shared" ref="J47:K47" si="49">+J28/J18</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="K47" s="10">
+        <f t="shared" si="49"/>
+        <v>0.1710663441022349</v>
+      </c>
+      <c r="L47" s="10"/>
       <c r="M47" s="8"/>
-      <c r="N47" s="8"/>
-      <c r="O47" s="8"/>
-      <c r="P47" s="8"/>
-      <c r="Q47" s="8"/>
-      <c r="R47" s="8"/>
-      <c r="S47" s="8"/>
-      <c r="T47" s="8"/>
-      <c r="U47" s="8"/>
+      <c r="N47" s="10">
+        <f t="shared" ref="N47:R47" si="50">+N28/N18</f>
+        <v>0.12574774501081384</v>
+      </c>
+      <c r="O47" s="10">
+        <f t="shared" si="50"/>
+        <v>0.13718550548653169</v>
+      </c>
+      <c r="P47" s="10">
+        <f t="shared" si="50"/>
+        <v>-2.7238319672507807E-2</v>
+      </c>
+      <c r="Q47" s="10">
+        <f t="shared" si="50"/>
+        <v>0.10816943493138666</v>
+      </c>
+      <c r="R47" s="10">
+        <f t="shared" si="50"/>
+        <v>0.14614638559194884</v>
+      </c>
+      <c r="S47" s="10">
+        <f>+S28/S18</f>
+        <v>0.16447490828667219</v>
+      </c>
+      <c r="T47" s="10">
+        <f>+T28/T18</f>
+        <v>0.16555680698296504</v>
+      </c>
+      <c r="U47" s="10">
+        <f>+U28/U18</f>
+        <v>0.16178403935932439</v>
+      </c>
       <c r="V47" s="8"/>
       <c r="W47" s="8"/>
       <c r="X47" s="8"/>
@@ -5418,25 +5415,79 @@
       <c r="BO47" s="8"/>
     </row>
     <row r="48" spans="2:67" x14ac:dyDescent="0.2">
-      <c r="C48" s="8"/>
-      <c r="D48" s="8"/>
-      <c r="E48" s="8"/>
-      <c r="F48" s="8"/>
-      <c r="G48" s="8"/>
-      <c r="H48" s="8"/>
-      <c r="I48" s="8"/>
-      <c r="J48" s="8"/>
-      <c r="K48" s="8"/>
-      <c r="L48" s="8"/>
+      <c r="B48" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="C48" s="10" t="e">
+        <f t="shared" ref="C48:I48" si="51">+C32/C31</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="D48" s="10" t="e">
+        <f t="shared" si="51"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="E48" s="10">
+        <f t="shared" si="51"/>
+        <v>0.21787624319759807</v>
+      </c>
+      <c r="F48" s="10">
+        <f t="shared" si="51"/>
+        <v>0.35145384152502929</v>
+      </c>
+      <c r="G48" s="10">
+        <f t="shared" si="51"/>
+        <v>0.30625636502986958</v>
+      </c>
+      <c r="H48" s="10" t="e">
+        <f t="shared" si="51"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="I48" s="10">
+        <f t="shared" si="51"/>
+        <v>0.28602034352993788</v>
+      </c>
+      <c r="J48" s="10" t="e">
+        <f t="shared" ref="J48:K48" si="52">+J32/J31</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="K48" s="10">
+        <f t="shared" si="52"/>
+        <v>0.28800699523631706</v>
+      </c>
+      <c r="L48" s="10"/>
       <c r="M48" s="8"/>
-      <c r="N48" s="8"/>
-      <c r="O48" s="8"/>
-      <c r="P48" s="8"/>
-      <c r="Q48" s="8"/>
-      <c r="R48" s="8"/>
-      <c r="S48" s="8"/>
-      <c r="T48" s="8"/>
-      <c r="U48" s="8"/>
+      <c r="N48" s="10">
+        <f t="shared" ref="N48:R48" si="53">+N32/N31</f>
+        <v>0.21813057198002508</v>
+      </c>
+      <c r="O48" s="10">
+        <f t="shared" si="53"/>
+        <v>0.23263848733664863</v>
+      </c>
+      <c r="P48" s="10">
+        <f t="shared" si="53"/>
+        <v>5.0707477354804339E-2</v>
+      </c>
+      <c r="Q48" s="10">
+        <f t="shared" si="53"/>
+        <v>0.12074782119763841</v>
+      </c>
+      <c r="R48" s="10">
+        <f t="shared" si="53"/>
+        <v>0.29654666161155774</v>
+      </c>
+      <c r="S48" s="10">
+        <f>+S32/S31</f>
+        <v>0.28574889956790367</v>
+      </c>
+      <c r="T48" s="10">
+        <f>+T32/T31</f>
+        <v>0.2849941859494704</v>
+      </c>
+      <c r="U48" s="10">
+        <f>+U32/U31</f>
+        <v>0.28539578048878667</v>
+      </c>
       <c r="V48" s="8"/>
       <c r="W48" s="8"/>
       <c r="X48" s="8"/>
@@ -12587,136 +12638,138 @@
       <c r="BO154" s="8"/>
     </row>
     <row r="155" spans="3:67" x14ac:dyDescent="0.2">
-      <c r="C155" s="4"/>
-      <c r="D155" s="4"/>
-      <c r="E155" s="4"/>
-      <c r="F155" s="4"/>
-      <c r="G155" s="4"/>
-      <c r="H155" s="4"/>
-      <c r="I155" s="4"/>
-      <c r="J155" s="4"/>
-      <c r="K155" s="4"/>
-      <c r="L155" s="4"/>
-      <c r="M155" s="4"/>
-      <c r="N155" s="4"/>
-      <c r="O155" s="4"/>
-      <c r="P155" s="4"/>
-      <c r="Q155" s="4"/>
-      <c r="R155" s="4"/>
-      <c r="S155" s="4"/>
-      <c r="T155" s="4"/>
-      <c r="U155" s="4"/>
-      <c r="V155" s="4"/>
-      <c r="W155" s="4"/>
-      <c r="X155" s="4"/>
-      <c r="Y155" s="4"/>
-      <c r="Z155" s="4"/>
-      <c r="AA155" s="4"/>
-      <c r="AB155" s="4"/>
-      <c r="AC155" s="4"/>
-      <c r="AD155" s="4"/>
-      <c r="AE155" s="4"/>
-      <c r="AF155" s="4"/>
-      <c r="AG155" s="4"/>
-      <c r="AH155" s="4"/>
-      <c r="AI155" s="4"/>
-      <c r="AJ155" s="4"/>
-      <c r="AK155" s="4"/>
-      <c r="AL155" s="4"/>
-      <c r="AM155" s="4"/>
-      <c r="AN155" s="4"/>
-      <c r="AO155" s="4"/>
-      <c r="AP155" s="4"/>
-      <c r="AQ155" s="4"/>
-      <c r="AR155" s="4"/>
-      <c r="AS155" s="4"/>
-      <c r="AT155" s="4"/>
-      <c r="AU155" s="4"/>
-      <c r="AV155" s="4"/>
-      <c r="AW155" s="4"/>
-      <c r="AX155" s="4"/>
-      <c r="AY155" s="4"/>
-      <c r="AZ155" s="4"/>
-      <c r="BA155" s="4"/>
-      <c r="BB155" s="4"/>
-      <c r="BC155" s="4"/>
-      <c r="BD155" s="4"/>
-      <c r="BE155" s="4"/>
-      <c r="BF155" s="4"/>
-      <c r="BG155" s="4"/>
-      <c r="BH155" s="4"/>
-      <c r="BI155" s="4"/>
-      <c r="BJ155" s="4"/>
-      <c r="BK155" s="4"/>
-      <c r="BL155" s="4"/>
-      <c r="BM155" s="4"/>
-      <c r="BN155" s="4"/>
+      <c r="C155" s="8"/>
+      <c r="D155" s="8"/>
+      <c r="E155" s="8"/>
+      <c r="F155" s="8"/>
+      <c r="G155" s="8"/>
+      <c r="H155" s="8"/>
+      <c r="I155" s="8"/>
+      <c r="J155" s="8"/>
+      <c r="K155" s="8"/>
+      <c r="L155" s="8"/>
+      <c r="M155" s="8"/>
+      <c r="N155" s="8"/>
+      <c r="O155" s="8"/>
+      <c r="P155" s="8"/>
+      <c r="Q155" s="8"/>
+      <c r="R155" s="8"/>
+      <c r="S155" s="8"/>
+      <c r="T155" s="8"/>
+      <c r="U155" s="8"/>
+      <c r="V155" s="8"/>
+      <c r="W155" s="8"/>
+      <c r="X155" s="8"/>
+      <c r="Y155" s="8"/>
+      <c r="Z155" s="8"/>
+      <c r="AA155" s="8"/>
+      <c r="AB155" s="8"/>
+      <c r="AC155" s="8"/>
+      <c r="AD155" s="8"/>
+      <c r="AE155" s="8"/>
+      <c r="AF155" s="8"/>
+      <c r="AG155" s="8"/>
+      <c r="AH155" s="8"/>
+      <c r="AI155" s="8"/>
+      <c r="AJ155" s="8"/>
+      <c r="AK155" s="8"/>
+      <c r="AL155" s="8"/>
+      <c r="AM155" s="8"/>
+      <c r="AN155" s="8"/>
+      <c r="AO155" s="8"/>
+      <c r="AP155" s="8"/>
+      <c r="AQ155" s="8"/>
+      <c r="AR155" s="8"/>
+      <c r="AS155" s="8"/>
+      <c r="AT155" s="8"/>
+      <c r="AU155" s="8"/>
+      <c r="AV155" s="8"/>
+      <c r="AW155" s="8"/>
+      <c r="AX155" s="8"/>
+      <c r="AY155" s="8"/>
+      <c r="AZ155" s="8"/>
+      <c r="BA155" s="8"/>
+      <c r="BB155" s="8"/>
+      <c r="BC155" s="8"/>
+      <c r="BD155" s="8"/>
+      <c r="BE155" s="8"/>
+      <c r="BF155" s="8"/>
+      <c r="BG155" s="8"/>
+      <c r="BH155" s="8"/>
+      <c r="BI155" s="8"/>
+      <c r="BJ155" s="8"/>
+      <c r="BK155" s="8"/>
+      <c r="BL155" s="8"/>
+      <c r="BM155" s="8"/>
+      <c r="BN155" s="8"/>
+      <c r="BO155" s="8"/>
     </row>
     <row r="156" spans="3:67" x14ac:dyDescent="0.2">
-      <c r="C156" s="4"/>
-      <c r="D156" s="4"/>
-      <c r="E156" s="4"/>
-      <c r="F156" s="4"/>
-      <c r="G156" s="4"/>
-      <c r="H156" s="4"/>
-      <c r="I156" s="4"/>
-      <c r="J156" s="4"/>
-      <c r="K156" s="4"/>
-      <c r="L156" s="4"/>
-      <c r="M156" s="4"/>
-      <c r="N156" s="4"/>
-      <c r="O156" s="4"/>
-      <c r="P156" s="4"/>
-      <c r="Q156" s="4"/>
-      <c r="R156" s="4"/>
-      <c r="S156" s="4"/>
-      <c r="T156" s="4"/>
-      <c r="U156" s="4"/>
-      <c r="V156" s="4"/>
-      <c r="W156" s="4"/>
-      <c r="X156" s="4"/>
-      <c r="Y156" s="4"/>
-      <c r="Z156" s="4"/>
-      <c r="AA156" s="4"/>
-      <c r="AB156" s="4"/>
-      <c r="AC156" s="4"/>
-      <c r="AD156" s="4"/>
-      <c r="AE156" s="4"/>
-      <c r="AF156" s="4"/>
-      <c r="AG156" s="4"/>
-      <c r="AH156" s="4"/>
-      <c r="AI156" s="4"/>
-      <c r="AJ156" s="4"/>
-      <c r="AK156" s="4"/>
-      <c r="AL156" s="4"/>
-      <c r="AM156" s="4"/>
-      <c r="AN156" s="4"/>
-      <c r="AO156" s="4"/>
-      <c r="AP156" s="4"/>
-      <c r="AQ156" s="4"/>
-      <c r="AR156" s="4"/>
-      <c r="AS156" s="4"/>
-      <c r="AT156" s="4"/>
-      <c r="AU156" s="4"/>
-      <c r="AV156" s="4"/>
-      <c r="AW156" s="4"/>
-      <c r="AX156" s="4"/>
-      <c r="AY156" s="4"/>
-      <c r="AZ156" s="4"/>
-      <c r="BA156" s="4"/>
-      <c r="BB156" s="4"/>
-      <c r="BC156" s="4"/>
-      <c r="BD156" s="4"/>
-      <c r="BE156" s="4"/>
-      <c r="BF156" s="4"/>
-      <c r="BG156" s="4"/>
-      <c r="BH156" s="4"/>
-      <c r="BI156" s="4"/>
-      <c r="BJ156" s="4"/>
-      <c r="BK156" s="4"/>
-      <c r="BL156" s="4"/>
-      <c r="BM156" s="4"/>
-      <c r="BN156" s="4"/>
+      <c r="C156" s="8"/>
+      <c r="D156" s="8"/>
+      <c r="E156" s="8"/>
+      <c r="F156" s="8"/>
+      <c r="G156" s="8"/>
+      <c r="H156" s="8"/>
+      <c r="I156" s="8"/>
+      <c r="J156" s="8"/>
+      <c r="K156" s="8"/>
+      <c r="L156" s="8"/>
+      <c r="M156" s="8"/>
+      <c r="N156" s="8"/>
+      <c r="O156" s="8"/>
+      <c r="P156" s="8"/>
+      <c r="Q156" s="8"/>
+      <c r="R156" s="8"/>
+      <c r="S156" s="8"/>
+      <c r="T156" s="8"/>
+      <c r="U156" s="8"/>
+      <c r="V156" s="8"/>
+      <c r="W156" s="8"/>
+      <c r="X156" s="8"/>
+      <c r="Y156" s="8"/>
+      <c r="Z156" s="8"/>
+      <c r="AA156" s="8"/>
+      <c r="AB156" s="8"/>
+      <c r="AC156" s="8"/>
+      <c r="AD156" s="8"/>
+      <c r="AE156" s="8"/>
+      <c r="AF156" s="8"/>
+      <c r="AG156" s="8"/>
+      <c r="AH156" s="8"/>
+      <c r="AI156" s="8"/>
+      <c r="AJ156" s="8"/>
+      <c r="AK156" s="8"/>
+      <c r="AL156" s="8"/>
+      <c r="AM156" s="8"/>
+      <c r="AN156" s="8"/>
+      <c r="AO156" s="8"/>
+      <c r="AP156" s="8"/>
+      <c r="AQ156" s="8"/>
+      <c r="AR156" s="8"/>
+      <c r="AS156" s="8"/>
+      <c r="AT156" s="8"/>
+      <c r="AU156" s="8"/>
+      <c r="AV156" s="8"/>
+      <c r="AW156" s="8"/>
+      <c r="AX156" s="8"/>
+      <c r="AY156" s="8"/>
+      <c r="AZ156" s="8"/>
+      <c r="BA156" s="8"/>
+      <c r="BB156" s="8"/>
+      <c r="BC156" s="8"/>
+      <c r="BD156" s="8"/>
+      <c r="BE156" s="8"/>
+      <c r="BF156" s="8"/>
+      <c r="BG156" s="8"/>
+      <c r="BH156" s="8"/>
+      <c r="BI156" s="8"/>
+      <c r="BJ156" s="8"/>
+      <c r="BK156" s="8"/>
+      <c r="BL156" s="8"/>
+      <c r="BM156" s="8"/>
+      <c r="BN156" s="8"/>
+      <c r="BO156" s="8"/>
     </row>
     <row r="157" spans="3:67" x14ac:dyDescent="0.2">
       <c r="C157" s="4"/>
@@ -20176,6 +20229,138 @@
       <c r="BM269" s="4"/>
       <c r="BN269" s="4"/>
     </row>
+    <row r="270" spans="3:66" x14ac:dyDescent="0.2">
+      <c r="C270" s="4"/>
+      <c r="D270" s="4"/>
+      <c r="E270" s="4"/>
+      <c r="F270" s="4"/>
+      <c r="G270" s="4"/>
+      <c r="H270" s="4"/>
+      <c r="I270" s="4"/>
+      <c r="J270" s="4"/>
+      <c r="K270" s="4"/>
+      <c r="L270" s="4"/>
+      <c r="M270" s="4"/>
+      <c r="N270" s="4"/>
+      <c r="O270" s="4"/>
+      <c r="P270" s="4"/>
+      <c r="Q270" s="4"/>
+      <c r="R270" s="4"/>
+      <c r="S270" s="4"/>
+      <c r="T270" s="4"/>
+      <c r="U270" s="4"/>
+      <c r="V270" s="4"/>
+      <c r="W270" s="4"/>
+      <c r="X270" s="4"/>
+      <c r="Y270" s="4"/>
+      <c r="Z270" s="4"/>
+      <c r="AA270" s="4"/>
+      <c r="AB270" s="4"/>
+      <c r="AC270" s="4"/>
+      <c r="AD270" s="4"/>
+      <c r="AE270" s="4"/>
+      <c r="AF270" s="4"/>
+      <c r="AG270" s="4"/>
+      <c r="AH270" s="4"/>
+      <c r="AI270" s="4"/>
+      <c r="AJ270" s="4"/>
+      <c r="AK270" s="4"/>
+      <c r="AL270" s="4"/>
+      <c r="AM270" s="4"/>
+      <c r="AN270" s="4"/>
+      <c r="AO270" s="4"/>
+      <c r="AP270" s="4"/>
+      <c r="AQ270" s="4"/>
+      <c r="AR270" s="4"/>
+      <c r="AS270" s="4"/>
+      <c r="AT270" s="4"/>
+      <c r="AU270" s="4"/>
+      <c r="AV270" s="4"/>
+      <c r="AW270" s="4"/>
+      <c r="AX270" s="4"/>
+      <c r="AY270" s="4"/>
+      <c r="AZ270" s="4"/>
+      <c r="BA270" s="4"/>
+      <c r="BB270" s="4"/>
+      <c r="BC270" s="4"/>
+      <c r="BD270" s="4"/>
+      <c r="BE270" s="4"/>
+      <c r="BF270" s="4"/>
+      <c r="BG270" s="4"/>
+      <c r="BH270" s="4"/>
+      <c r="BI270" s="4"/>
+      <c r="BJ270" s="4"/>
+      <c r="BK270" s="4"/>
+      <c r="BL270" s="4"/>
+      <c r="BM270" s="4"/>
+      <c r="BN270" s="4"/>
+    </row>
+    <row r="271" spans="3:66" x14ac:dyDescent="0.2">
+      <c r="C271" s="4"/>
+      <c r="D271" s="4"/>
+      <c r="E271" s="4"/>
+      <c r="F271" s="4"/>
+      <c r="G271" s="4"/>
+      <c r="H271" s="4"/>
+      <c r="I271" s="4"/>
+      <c r="J271" s="4"/>
+      <c r="K271" s="4"/>
+      <c r="L271" s="4"/>
+      <c r="M271" s="4"/>
+      <c r="N271" s="4"/>
+      <c r="O271" s="4"/>
+      <c r="P271" s="4"/>
+      <c r="Q271" s="4"/>
+      <c r="R271" s="4"/>
+      <c r="S271" s="4"/>
+      <c r="T271" s="4"/>
+      <c r="U271" s="4"/>
+      <c r="V271" s="4"/>
+      <c r="W271" s="4"/>
+      <c r="X271" s="4"/>
+      <c r="Y271" s="4"/>
+      <c r="Z271" s="4"/>
+      <c r="AA271" s="4"/>
+      <c r="AB271" s="4"/>
+      <c r="AC271" s="4"/>
+      <c r="AD271" s="4"/>
+      <c r="AE271" s="4"/>
+      <c r="AF271" s="4"/>
+      <c r="AG271" s="4"/>
+      <c r="AH271" s="4"/>
+      <c r="AI271" s="4"/>
+      <c r="AJ271" s="4"/>
+      <c r="AK271" s="4"/>
+      <c r="AL271" s="4"/>
+      <c r="AM271" s="4"/>
+      <c r="AN271" s="4"/>
+      <c r="AO271" s="4"/>
+      <c r="AP271" s="4"/>
+      <c r="AQ271" s="4"/>
+      <c r="AR271" s="4"/>
+      <c r="AS271" s="4"/>
+      <c r="AT271" s="4"/>
+      <c r="AU271" s="4"/>
+      <c r="AV271" s="4"/>
+      <c r="AW271" s="4"/>
+      <c r="AX271" s="4"/>
+      <c r="AY271" s="4"/>
+      <c r="AZ271" s="4"/>
+      <c r="BA271" s="4"/>
+      <c r="BB271" s="4"/>
+      <c r="BC271" s="4"/>
+      <c r="BD271" s="4"/>
+      <c r="BE271" s="4"/>
+      <c r="BF271" s="4"/>
+      <c r="BG271" s="4"/>
+      <c r="BH271" s="4"/>
+      <c r="BI271" s="4"/>
+      <c r="BJ271" s="4"/>
+      <c r="BK271" s="4"/>
+      <c r="BL271" s="4"/>
+      <c r="BM271" s="4"/>
+      <c r="BN271" s="4"/>
+    </row>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="A1" location="Main!A1" display="Main" xr:uid="{C142CE63-C4C9-4B20-8ADA-397E84BD03DD}"/>
